--- a/p6_deployment/data/usa/data_preparation/df_selected_nan.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG12"/>
+  <dimension ref="A1:AL14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,364 +436,419 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>id_team_home</t>
+          <t>id_team_away</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_away</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>id_competition</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>h2h_27_segun_loc</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>h2h_27</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>h2h_3</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days_against</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_away_against</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_rat_player_miss</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ld9fFUZA</t>
+          <t>raSHWV4o</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.460084169459398</v>
+        <v>1.478905089706689</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.45543627987601</v>
+        <v>0.1179228887362348</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04189012234472871</v>
+        <v>-0.3453479375006582</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1836643234828613</v>
+        <v>-0.7879341964219815</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7908729184216404</v>
+        <v>-0.1866428846285344</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0165929558735042</v>
+        <v>-3.508839939872629</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04841519308848754</v>
+        <v>-2.601667227297925</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1673860338306378</v>
+        <v>-1.428924454594495</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.2915937914119306</v>
+        <v>-0.8454993764064265</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.5269887911968246</v>
+        <v>0.06756744051202709</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6031870400550668</v>
+        <v>0.2821324176088609</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6529264770224178</v>
+        <v>0.8712402491462187</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2072900472299593</v>
+        <v>0.4055568391480161</v>
       </c>
       <c r="O2" t="n">
-        <v>0.079555897867046</v>
+        <v>1.227091147769222</v>
       </c>
       <c r="P2" t="n">
-        <v>0.119359589088676</v>
+        <v>0.285212905239171</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1740879773663997</v>
+        <v>0.42321590581795</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.4556713360123117</v>
+        <v>1.16844254055233</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4937312485953447</v>
+        <v>0.510341112054692</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01442255656847457</v>
+        <v>0.9469709525855335</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4429753776484975</v>
+        <v>-1.622467902136241</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5973884952528805</v>
+        <v>0.2873520075695938</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.2800320507982393</v>
+        <v>0.05854295245257338</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.3576264311601438</v>
+        <v>-0.08088550194072099</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.07979119458999985</v>
+        <v>0.1019297983199359</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.1804107754069568</v>
+        <v>0.4486839326758646</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.2102276414088625</v>
+        <v>0.2684179351042131</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.2095472302310904</v>
+        <v>0.2524755054039861</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.2229651933572648</v>
+        <v>-0.5135585697640845</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.1559439947652304</v>
+        <v>-0.3093423106366343</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.7260845081056182</v>
+        <v>1.000737278874041</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.4305894193179637</v>
+        <v>-0.05270870765075047</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.09291524077887976</v>
+        <v>-0.6305832108557028</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-0.2828896934744227</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-0.4288731251378783</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>-0.0683560770435197</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.4207970946347819</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>-0.0261540161937875</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>vo27CSJT</t>
+          <t>tflZ7nSp</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.460084169459398</v>
+        <v>1.458702379218771</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.399376691994678</v>
+        <v>1.146954844852498</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.4934198077701384</v>
+        <v>-1.294667010094943</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1836643234828613</v>
+        <v>1.71562365163292</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5438223698884542</v>
+        <v>-0.1866428846285344</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2548796543283627</v>
+        <v>-1.284984803452413</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5405326056126</v>
+        <v>-0.4589507751121535</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.699085451947081</v>
+        <v>0.5401364280158796</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.706491356350486</v>
+        <v>-1.123964206553655</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.5269887911968246</v>
+        <v>0.03464760469607751</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1807728387461859</v>
+        <v>0.6146076310998881</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9979018762551325</v>
+        <v>-1.154843284940914</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1464392237850662</v>
+        <v>-0.3989423228265515</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2009441726954501</v>
+        <v>0.1422723631183374</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.664356383225282</v>
+        <v>0.2690223460664039</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.6838710394827836</v>
+        <v>-0.2949667698683329</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02968782187826523</v>
+        <v>0.1957833264460038</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6662201825830166</v>
+        <v>0.1189455117890282</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8721414814830002</v>
+        <v>0.9469709525855335</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2170904918554574</v>
+        <v>2.928919532007165</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7096395699843441</v>
+        <v>-1.135738939652862</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2275508171183145</v>
+        <v>-0.8654174566634364</v>
       </c>
       <c r="X3" t="n">
-        <v>1.74116226290259</v>
+        <v>0.1097606332550612</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.7032376011231433</v>
+        <v>0.5600545879654736</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.5216923149111168</v>
+        <v>-0.4348021125100266</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.7984383233356781</v>
+        <v>-1.072171269538378</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>0.231761533529996</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.02671333834620911</v>
+        <v>0.7006840986701457</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.8320534374028581</v>
+        <v>1.138315870640532</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.1221576287044293</v>
+        <v>-0.9382452260133701</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.1023558180299468</v>
+        <v>0.191691448954647</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.6190286351907448</v>
+        <v>0.9744986269861858</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.526874426582576</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>2.10051399677661</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.765835680987572</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-0.2711255531097304</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.1530440469529679</v>
       </c>
     </row>
     <row r="4">
@@ -803,924 +858,1295 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.460084169459398</v>
+        <v>1.478905089706689</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.096654917435488</v>
+        <v>-0.1393351002928309</v>
       </c>
       <c r="D4" t="n">
-        <v>1.181582231621543</v>
+        <v>-1.294667010094943</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1836643234828613</v>
+        <v>1.180380249634975</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.284974015488013</v>
+        <v>-0.1866428846285344</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4599804410362127</v>
+        <v>-1.284984803452413</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9358196319597374</v>
+        <v>-0.4589507751121535</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3941926675919563</v>
+        <v>-0.9366592339419015</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.2585795148966978</v>
+        <v>0.08848671606035875</v>
       </c>
       <c r="K4" t="n">
-        <v>1.484138772914619</v>
+        <v>0.009597817092687642</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5055535689978252</v>
+        <v>-1.324436518385424</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1493452460657376</v>
+        <v>-0.6083472267955337</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1312265179238432</v>
+        <v>-0.9870184184512784</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3049629488623762</v>
+        <v>0.5404521780391354</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1358754777212123</v>
+        <v>1.848573298961572</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2766478852071537</v>
+        <v>-0.02167283698896399</v>
       </c>
       <c r="R4" t="n">
-        <v>1.248603251556089</v>
+        <v>-0.1119885969772687</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2502414564285778</v>
+        <v>-1.016998507387612</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1154948267785093</v>
+        <v>0.4773650584207642</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0704427125971486</v>
+        <v>0.1276788681200073</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3789044227742222</v>
+        <v>-0.9357767279074951</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.131731128709059</v>
+        <v>-0.3550646619308234</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2197439536640619</v>
+        <v>-0.2102797881231637</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.4058080585654377</v>
+        <v>-1.264121386029013</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.276723726398409</v>
+        <v>-0.9471699192247562</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.2197687175789543</v>
+        <v>0.4090588225548755</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.649537815154528</v>
+        <v>-0.07007062806243125</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.3521204776276272</v>
+        <v>0.07951802791192147</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.3639310665313146</v>
+        <v>-0.3153742194680474</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.2537460045626768</v>
+        <v>0.4156441210335863</v>
       </c>
       <c r="AF4" t="n">
-        <v>-1.06795690788527</v>
+        <v>0.2354335224379994</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.414923893253315</v>
+        <v>0.3605108868395803</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.3220981792413752</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-0.6488198313913121</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.514815002810262</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-0.4046544851306011</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.3802564267716809</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>WKbaElkH</t>
+          <t>ld9fFUZA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.460084169459398</v>
+        <v>1.478905089706689</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.511495867757341</v>
+        <v>1.35827390726923</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04189012234472871</v>
+        <v>1.733333480076482</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1836643234828613</v>
+        <v>0.04082978086515811</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.755479500819876</v>
+        <v>-0.1866428846285344</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.842847425584798</v>
+        <v>-0.7907947731368096</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.920054457007962</v>
+        <v>0.01720843648468454</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4591371432666784</v>
+        <v>0.04787120736328582</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3576223444423968</v>
+        <v>-0.7717438267998633</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4037809905407029</v>
+        <v>0.248002692214604</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6242051675216811</v>
+        <v>-0.1920590872888206</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7600488814293167</v>
+        <v>1.359038582527836</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1654212463700057</v>
+        <v>-0.426945946427729</v>
       </c>
       <c r="O5" t="n">
-        <v>1.748531317713899</v>
+        <v>-0.2113113125313311</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4827091390044816</v>
+        <v>0.1932505291378532</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.490760372602008</v>
+        <v>-0.9686605712739248</v>
       </c>
       <c r="R5" t="n">
-        <v>-1.378272149071546</v>
+        <v>-0.3227912842534829</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5752472205447419</v>
+        <v>1.213533964794821</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6328470952437698</v>
+        <v>0.4773650584207642</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06556127623112167</v>
+        <v>-2.140471112873004</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.7449278545770404</v>
+        <v>-0.7778619361138784</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3076392145001919</v>
+        <v>-0.2263792474720257</v>
       </c>
       <c r="X5" t="n">
-        <v>0.334363924254017</v>
+        <v>0.2324593815073706</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.0112586653766447</v>
+        <v>0.6085347345555058</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.04960359697569098</v>
+        <v>-0.2282211555908524</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.6860144541010506</v>
+        <v>-0.2421648794448967</v>
       </c>
       <c r="AB5" t="n">
-        <v>-1.749514277463122</v>
+        <v>-0.4429221217942532</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.09965243238199058</v>
+        <v>-0.2901481427314492</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.2765206759367791</v>
+        <v>0.8646132489930842</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.3303296889376238</v>
+        <v>0.3974200871374582</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.8197272239825599</v>
+        <v>0.2770926400411931</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.1592077841816825</v>
+        <v>0.007589885482252197</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.7613377255607501</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-0.2089264188844446</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-0.1481649456273065</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.08090526767256535</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.1870204621170657</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>zg5jGAK4</t>
+          <t>WKbaElkH</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.460084169459398</v>
+        <v>1.478905089706689</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.7827212253000312</v>
+        <v>-1.333747192213493</v>
       </c>
       <c r="D6" t="n">
-        <v>0.05915818460649862</v>
+        <v>0.8167495479164834</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1836643234828613</v>
+        <v>0.04082978086515811</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.779075112554385</v>
+        <v>-0.1866428846285344</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9365538379459297</v>
+        <v>-3.755934955030431</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.42793704448385</v>
+        <v>-2.839746833096344</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9270726736559549</v>
+        <v>-1.921189675247089</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6877651095947264</v>
+        <v>1.483821297392686</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5557434038856054</v>
+        <v>0.4368838493160255</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6749177534848766</v>
+        <v>1.674943128856116</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9721880389766652</v>
+        <v>0.4370794918418328</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2133751295744473</v>
+        <v>-0.09090246321359942</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.729669557261055</v>
+        <v>0.4576307765356095</v>
       </c>
       <c r="P6" t="n">
-        <v>1.563320138104736</v>
+        <v>0.717824646335511</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.06507776282578916</v>
+        <v>-0.9436490555232296</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.2071447026671482</v>
+        <v>0.6595492384536753</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.171494565265137</v>
+        <v>-0.1476422507854078</v>
       </c>
       <c r="T6" t="n">
-        <v>1.10743818949957</v>
+        <v>-1.401058518238313</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2123599183309958</v>
+        <v>1.036127570444763</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.087742989466713</v>
+        <v>-0.6041177504249652</v>
       </c>
       <c r="W6" t="n">
-        <v>-1.950142369811862</v>
+        <v>-0.8090604098351336</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.4676193148078245</v>
+        <v>0.06219846249261354</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.7335875544453581</v>
+        <v>-0.7932461100190917</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.5267437724198676</v>
+        <v>-0.3662921180493023</v>
       </c>
       <c r="AA6" t="n">
-        <v>-1.121679056362678</v>
+        <v>0.3120263859334382</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>0.06604975853807515</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.825562076202246</v>
+        <v>0.5535997175186055</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.4551064114109585</v>
+        <v>-0.2470851215063114</v>
       </c>
       <c r="AE6" t="n">
-        <v>-1.355932102073933</v>
+        <v>0.09894010835134115</v>
       </c>
       <c r="AF6" t="n">
-        <v>-2.529956129229555</v>
+        <v>-0.4322371877575378</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.1419829832316338</v>
+        <v>0.8271113205165762</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-0.5906707504412668</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-1.748553362658481</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-0.07888638849595256</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0.01013718597802836</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.2398823806875968</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>MTkoJCzn</t>
+          <t>vo27CSJT</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.460084169459398</v>
+        <v>1.478905089706689</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.24240984592695</v>
+        <v>0.5956877255044997</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.166874235979165</v>
+        <v>1.733333480076482</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1836643234828613</v>
+        <v>-0.4944136211327863</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.532024564021199</v>
+        <v>-0.1866428846285344</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6982671394910712</v>
+        <v>-0.5436997579790078</v>
       </c>
       <c r="H7" t="n">
-        <v>0.04841519308848754</v>
+        <v>0.2552880422831036</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1993592405677908</v>
+        <v>0.5401364280158796</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.480107745960318</v>
+        <v>2.140941850966467</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6697152138942823</v>
+        <v>-0.8806773929036449</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1568626009362494</v>
+        <v>-0.3545762186036108</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4369302438832997</v>
+        <v>0.0084848980926322</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7610325405784785</v>
+        <v>-1.018825003282245</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2149691762235754</v>
+        <v>-0.558524111142267</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4752124016826434</v>
+        <v>0.0731165800759208</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.6902834050439965</v>
+        <v>0.1734601091694802</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.7488018751693684</v>
+        <v>1.147362271824708</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.665225181865724</v>
+        <v>-0.3449335001524207</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1831206347437738</v>
+        <v>-0.4618467299087743</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.07694725119328326</v>
+        <v>0.8921107907606681</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.0145477312923496</v>
+        <v>1.035693712978119</v>
       </c>
       <c r="W7" t="n">
-        <v>-1.235562855186448</v>
+        <v>-0.6319506440625692</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.171820628811741</v>
+        <v>0.5334700316775707</v>
       </c>
       <c r="Y7" t="n">
-        <v>-1.08564701298305</v>
+        <v>0.1353125618650876</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.1834889146504154</v>
+        <v>0.267354766010393</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.4162617237338292</v>
+        <v>1.061662084079493</v>
       </c>
       <c r="AB7" t="n">
+        <v>-0.2168439144838469</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.510006156074815</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.1890631572924218</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.7735763908552361</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.8082463894819021</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.7187025253973343</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.8252552939806891</v>
+      </c>
+      <c r="AI7" t="n">
         <v>0</v>
       </c>
-      <c r="AC7" t="n">
-        <v>-0.6114100526751943</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>-0.1836758334371403</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0.5902519194641448</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>-0.139534565140213</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>-0.06002732830439406</v>
+      <c r="AJ7" t="n">
+        <v>0.6660357083233522</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>-0.7020598337225405</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>-0.0261540161937875</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hK8xvrmh</t>
+          <t>zg5jGAK4</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.460084169459398</v>
+        <v>1.478905089706689</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5514969662756597</v>
+        <v>1.110203703562631</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8215129907437667</v>
+        <v>0.8331171181336262</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1836643234828613</v>
+        <v>0.05809569705864018</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.284974015488013</v>
+        <v>-0.1866428846285344</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4599804410362127</v>
+        <v>-1.779174833768017</v>
       </c>
       <c r="H8" t="n">
-        <v>0.04841519308848754</v>
+        <v>-0.9351099867089916</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1870331021019821</v>
+        <v>-1.428924454594495</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.857552817387353</v>
+        <v>0.01021552055951569</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1568420688552364</v>
+        <v>0.149723065755328</v>
       </c>
       <c r="L8" t="n">
-        <v>0.228593314366059</v>
+        <v>-2.395256992355508</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7763528959590575</v>
+        <v>1.502072118733788</v>
       </c>
       <c r="N8" t="n">
-        <v>1.089626987180896</v>
+        <v>-1.596875110210255</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.042444384382939</v>
+        <v>1.166213878287998</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6289927240355204</v>
+        <v>1.558438478585584</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2991291058100414</v>
+        <v>0.232754650819837</v>
       </c>
       <c r="R8" t="n">
-        <v>1.248028508331989</v>
+        <v>-1.351820698438855</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5737962670709632</v>
+        <v>1.187742321376444</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1563710852837522</v>
+        <v>-0.9314526240735437</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4233108990185282</v>
+        <v>-0.01313753868221913</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.115599815955837</v>
+        <v>0.05303906320356474</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3218383865498712</v>
+        <v>0.1720202219750463</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3485518027591962</v>
+        <v>-0.6874873371988682</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1526310825633155</v>
+        <v>-2.475458351039507</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.5207043832020153</v>
+        <v>-1.956779840193948</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.4606405955100039</v>
+        <v>0.4053129699804209</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.183756288693129</v>
+        <v>-0.2121092923412206</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.09529802025239915</v>
+        <v>-0.6833095359577341</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.00575995514148486</v>
+        <v>-1.356697465426155</v>
       </c>
       <c r="AE8" t="n">
-        <v>-1.178782785089408</v>
+        <v>-0.328771769454771</v>
       </c>
       <c r="AF8" t="n">
-        <v>-1.288984213292757</v>
+        <v>-1.066245582994694</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.3330729319993808</v>
+        <v>0.8972725022391365</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-2.039855393382399</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.05941773381613496</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-0.7324073182727385</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.603841235554683</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>rwisKhLu</t>
+          <t>MTkoJCzn</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.460084169459398</v>
+        <v>1.478905089706689</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.4575756155883082</v>
+        <v>-0.3047152360972302</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05915818460649862</v>
+        <v>-0.3453479375006582</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1836643234828613</v>
+        <v>-1.167784352678587</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7908729184216404</v>
+        <v>-0.1866428846285344</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0165929558735042</v>
+        <v>-1.532079818610215</v>
       </c>
       <c r="H9" t="n">
-        <v>0.04841519308848754</v>
+        <v>-0.6970303809105726</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9939740017643872</v>
+        <v>0.04787120736328582</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.348050639899386</v>
+        <v>0.8039343624352477</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1280874561664556</v>
+        <v>-0.07937211818831659</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5126240577419765</v>
+        <v>0.3467334000877889</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.04006143763225484</v>
+        <v>-0.403411204991016</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.017332774598497</v>
+        <v>1.038577022033893</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7712943161725262</v>
+        <v>-0.5234842874292369</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.04579929723669065</v>
+        <v>-2.00704646244121</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.536615872334639</v>
+        <v>-0.07794874742802965</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.5019113442021564</v>
+        <v>-0.8090428162372844</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2569439027788051</v>
+        <v>0.2656910691694514</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4245237318835035</v>
+        <v>-0.9314526240735437</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.02491094242420594</v>
+        <v>0.1018146301359249</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.62934103876674</v>
+        <v>-0.7014993285876233</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2985185253362519</v>
+        <v>-1.307216835682612</v>
       </c>
       <c r="X9" t="n">
-        <v>0.4163719135003463</v>
+        <v>-0.2510140115190692</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.6303977131498276</v>
+        <v>-0.03875470519178537</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.7111416463830592</v>
+        <v>-1.490676149745425</v>
       </c>
       <c r="AA9" t="n">
-        <v>-1.031618244753975</v>
+        <v>-0.09411822257983965</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>-1.366173439606384</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.4687841955501762</v>
+        <v>-1.524050424604581</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.3686332067685634</v>
+        <v>0.528596993037263</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.9866768596806771</v>
+        <v>-1.586860533774416</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.66768724360745</v>
+        <v>-0.3901475602366129</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.6066777653801648</v>
+        <v>-0.213469154150145</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-0.08971860170674331</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-0.4948571370139087</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>-0.1791923030051908</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-1.29080103399638</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>-0.5320349596394479</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>WA7tw22b</t>
+          <t>hK8xvrmh</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.460084169459398</v>
+        <v>1.458702379218771</v>
       </c>
       <c r="C10" t="n">
-        <v>1.403602702071899</v>
+        <v>1.349086121946763</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8215129907437667</v>
+        <v>-0.6235966311920865</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1836643234828613</v>
+        <v>-0.8224660288089457</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.037923466954827</v>
+        <v>-0.1866428846285344</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2216937425813543</v>
+        <v>-1.284984803452413</v>
       </c>
       <c r="H10" t="n">
-        <v>0.04841519308848754</v>
+        <v>-0.4589507751121535</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2337416100426435</v>
+        <v>0.04787120736328582</v>
       </c>
       <c r="J10" t="n">
-        <v>1.39213431086495</v>
+        <v>0.5607480158370766</v>
       </c>
       <c r="K10" t="n">
-        <v>1.268067216439836</v>
+        <v>0.4917822344085116</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.279744187477444</v>
+        <v>-1.182382001939613</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1802018507998964</v>
+        <v>1.138416099795072</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.35657611530377</v>
+        <v>-0.745011794737399</v>
       </c>
       <c r="O10" t="n">
-        <v>1.404918731274841</v>
+        <v>0.6834429737973596</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4909670833207502</v>
+        <v>0.6893292621914406</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.08400973647239823</v>
+        <v>-0.2463452457150416</v>
       </c>
       <c r="R10" t="n">
-        <v>-1.580397846124124</v>
+        <v>-0.8262193314968277</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3529031206866551</v>
+        <v>0.8681631075257448</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.889369599533429</v>
+        <v>-0.4618467299087743</v>
       </c>
       <c r="U10" t="n">
-        <v>0.006429107175351985</v>
+        <v>0.5149239868261323</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.883760009881997</v>
+        <v>-0.2375772342989843</v>
       </c>
       <c r="W10" t="n">
-        <v>0.7976830621436916</v>
+        <v>0.1262802274135222</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.983264090828635</v>
+        <v>-0.5871512642859242</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0008813159522412398</v>
+        <v>-1.434420032611147</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.2188278511156377</v>
+        <v>-0.2133041536902458</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.01082772784409354</v>
+        <v>-0.07331876257619101</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.09954958400023096</v>
+        <v>0.5099205844092917</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.3426396898525473</v>
+        <v>0.1274620181985205</v>
       </c>
       <c r="AD10" t="n">
-        <v>-1.141440099935691</v>
+        <v>-1.268940131458034</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.9138582393651414</v>
+        <v>-0.1645295315559976</v>
       </c>
       <c r="AF10" t="n">
-        <v>-1.115607103472042</v>
+        <v>-0.5526181188890658</v>
       </c>
       <c r="AG10" t="n">
-        <v>-0.7390477591658108</v>
+        <v>-0.1599994929025042</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-1.293509806232533</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1.367358309265164</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.2714135046238903</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.548256529745613</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-0.1235239944962589</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>tW5nHj5b</t>
+          <t>rwisKhLu</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.460084169459398</v>
+        <v>1.478905089706689</v>
       </c>
       <c r="C11" t="n">
-        <v>-1.646038878672537</v>
+        <v>0.9723869237256315</v>
       </c>
       <c r="D11" t="n">
-        <v>1.71689216173641</v>
+        <v>-1.3928724313978</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1836643234828613</v>
+        <v>0.05809569705864018</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5438223698884542</v>
+        <v>-0.1866428846285344</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2548796543283627</v>
+        <v>-0.7907947731368096</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5405326056126</v>
+        <v>0.01720843648468454</v>
       </c>
       <c r="I11" t="n">
-        <v>1.326563061839957</v>
+        <v>0.04787120736328582</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.008614278424219969</v>
+        <v>0.8049691979526868</v>
       </c>
       <c r="K11" t="n">
-        <v>1.353546073946343</v>
+        <v>-0.0994311435105716</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.827687137288491</v>
+        <v>0.03049298847628238</v>
       </c>
       <c r="M11" t="n">
-        <v>0.9049220823513897</v>
+        <v>0.1587713140826116</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1882403051618408</v>
+        <v>0.3502410394419866</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1356559119795448</v>
+        <v>-0.5001244049538832</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7139315798599949</v>
+        <v>-1.063136862668882</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.5665402449536301</v>
+        <v>-0.09297003131278636</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.6680504521828786</v>
+        <v>-0.1666411455303612</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.264841775562993</v>
+        <v>-0.3416724877661891</v>
       </c>
       <c r="T11" t="n">
-        <v>0.06801094682655714</v>
+        <v>0.4773650584207642</v>
       </c>
       <c r="U11" t="n">
-        <v>2.753118359815853</v>
+        <v>-0.01313753868221913</v>
       </c>
       <c r="V11" t="n">
-        <v>2.357222121770927</v>
+        <v>-0.7172600020603082</v>
       </c>
       <c r="W11" t="n">
-        <v>1.347422803975033</v>
+        <v>0.8233559148350814</v>
       </c>
       <c r="X11" t="n">
-        <v>1.369865014700839</v>
+        <v>-0.9125775807165379</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.137518029836166</v>
+        <v>-0.8627304344286446</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.36825365951743</v>
+        <v>0.3013212824644006</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.425942040970397</v>
+        <v>0.3864491496151473</v>
       </c>
       <c r="AB11" t="n">
-        <v>-3.326147206772107</v>
+        <v>-0.02449988993965303</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.280031833406399</v>
+        <v>0.2797768351112428</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.7820781042431219</v>
+        <v>-0.9994126420449561</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.421606508893555</v>
+        <v>1.087681335008307</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.107457612396813</v>
+        <v>-1.081688912449614</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.7327636261813965</v>
+        <v>0.3445669967744517</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-1.780796021344785</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>-0.5522172763886989</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-0.6292258708020656</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-0.3800772470404843</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
+          <t>WA7tw22b</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.458702379218771</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-1.306183836246093</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.520555067253625</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.8224660288089457</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.1866428846285344</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-1.037889788294611</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.2208711693137345</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.04787120736328582</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.7387397248365888</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-0.965136446892085</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.012698502187314</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.5743781928697158</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.110833285399893</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.835863842581465</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.5183569573270189</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-0.2178838657228692</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.1597126444009631</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0.296018314358946</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.007759164255994911</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.7160902822578843</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-1.233407247854638</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-1.999383641115071</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.3395754202399912</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-1.297214529047344</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.8625490216434888</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-1.339214281550949</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.01574439827267061</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-0.976847749886942</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-0.9833144366537881</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-0.5202425578977945</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.06520644293170917</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-1.871955058995384</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-2.053453117281625</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.7148497473799769</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>-0.8263130012281196</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>-0.2893340438398491</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.4644964576419451</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
           <t>2u7rIWkh</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>1.460084169459398</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-0.5696947913509712</v>
-      </c>
-      <c r="D12" t="n">
-        <v>-1.115070049193855</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-0.1836643234828613</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-1.284974015488013</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-0.4599804410362127</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-1.920054457007962</v>
-      </c>
-      <c r="I12" t="n">
-        <v>-0.5202613556664164</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.161173429368407</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1.866419218985389</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.3242342656058059</v>
-      </c>
-      <c r="M12" t="n">
-        <v>-1.640747808216795</v>
-      </c>
-      <c r="N12" t="n">
-        <v>-0.005687834827163722</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.3881059754857919</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0.3741761565620983</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.3356950847499843</v>
-      </c>
-      <c r="R12" t="n">
-        <v>-0.3474586817781843</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.2300356815547174</v>
-      </c>
-      <c r="T12" t="n">
-        <v>-0.9602725613703053</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0.5267921948661252</v>
-      </c>
-      <c r="V12" t="n">
-        <v>-0.276807056568297</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0.1020192996222184</v>
-      </c>
-      <c r="X12" t="n">
-        <v>-1.5223511343671</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0.8810299622964718</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>-1.114567781939518</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>-0.3819386315375228</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.917073930232192</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>-0.1384654755518747</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0.9497675969753712</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>-1.697506777223882</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>-0.8463064177528726</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0.4258794734943285</v>
+      <c r="B13" t="n">
+        <v>1.458702379218771</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.9478602086698944</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-1.3928724313978</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-1.115986604098141</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.1866428846285344</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-1.284984803452413</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.4589507751121535</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-1.921189675247089</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.7312136483461237</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.1520264945004672</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.4580094379703407</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-0.5928294374901713</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.1566357404708832</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.9864135707504289</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.01269338353974556</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.8573238228702544</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-0.5367169743041597</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0.4323879232377233</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-0.9314526240735437</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0.8178027204092304</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-0.2661080580263878</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.5192411660055771</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-1.376966035921</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-0.8417977999105746</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.1217136101092188</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.092656746436928</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-0.614552174464457</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-1.638764209192127</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-1.581195089685514</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.974979700411604</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-0.3082179622836672</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-1.074643098212097</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-0.3859702284368242</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.2309669936224228</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.3855267506337692</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-0.1254576272687804</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>-0.1706837039322014</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>tW5nHj5b</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.458702379218771</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.8437579292110987</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-1.196461588792086</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.71562365163292</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.1866428846285344</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.5436997579790078</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.2552880422831036</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.5401364280158796</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.6559528834414672</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-2.23202225671869</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-0.06623937272253101</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-0.09356143375241623</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.6544779378251496</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.5900034438959457</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.1940276462747382</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.3750615507806918</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-0.338406298125795</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.48123343613729</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.416576846750303</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.208947706065678</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-0.02468610442595207</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.78586178950801</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.8017263477309053</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.207182676913431</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.299272748978149</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.918894423962756</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>9.325195186211651</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.059127893315651</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.748646286582195</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.6231436466909185</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>3.571634523827025</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-0.1212072018615332</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>2.523028249398892</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-2.545860172827178</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.8508989002707626</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>3.19455718252287</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.8373851700991005</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/usa/data_preparation/df_selected_nan.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_selected_nan.xlsx
@@ -700,7 +700,7 @@
         <v>0.2684179351042131</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2524755054039861</v>
+        <v>0.7614473857363144</v>
       </c>
       <c r="AC2" t="n">
         <v>-0.5135585697640845</v>
@@ -721,13 +721,13 @@
         <v>-0.2828896934744227</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.4288731251378783</v>
+        <v>0.120993640495706</v>
       </c>
       <c r="AJ2" t="n">
         <v>-0.0683560770435197</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.4207970946347819</v>
+        <v>0.4754225668251381</v>
       </c>
       <c r="AL2" t="n">
         <v>-0.0261540161937875</v>
@@ -1526,7 +1526,7 @@
         <v>-0.09411822257983965</v>
       </c>
       <c r="AB9" t="n">
-        <v>-1.366173439606384</v>
+        <v>-0.8453650039174896</v>
       </c>
       <c r="AC9" t="n">
         <v>-1.524050424604581</v>
@@ -1547,13 +1547,13 @@
         <v>-0.08971860170674331</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.4948571370139087</v>
+        <v>-0.5828358195152818</v>
       </c>
       <c r="AJ9" t="n">
         <v>-0.1791923030051908</v>
       </c>
       <c r="AK9" t="n">
-        <v>-1.29080103399638</v>
+        <v>-1.272592543266261</v>
       </c>
       <c r="AL9" t="n">
         <v>-0.5320349596394479</v>

--- a/p6_deployment/data/usa/data_preparation/df_selected_nan.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_selected_nan.xlsx
@@ -701,34 +701,34 @@
         <v>-0.7230660606979613</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3842041194631605</v>
+        <v>0.3633651908204013</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8446120468506259</v>
+        <v>0.8290949736384865</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8647099015692702</v>
+        <v>0.8712193635692365</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3289269326646644</v>
+        <v>-0.2919555105092206</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3553089046043931</v>
+        <v>0.4853996765270864</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.6182611805999491</v>
+        <v>0.6306742676790577</v>
       </c>
       <c r="R4" t="n">
-        <v>1.101740999350583</v>
+        <v>1.07436302156492</v>
       </c>
       <c r="S4" t="n">
         <v>1.450506250858605</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2327639483335292</v>
+        <v>0.2393319011057967</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1687785296886575</v>
+        <v>0.2034651948891617</v>
       </c>
     </row>
     <row r="5">
@@ -835,34 +835,34 @@
         <v>-0.6436517971841476</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.1541493401841319</v>
+        <v>-0.1690452042127522</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9278789920480939</v>
+        <v>-0.9094972283967933</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0554359275042814</v>
+        <v>-0.1186745329642373</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2881673105608871</v>
+        <v>0.2934409419183345</v>
       </c>
       <c r="P6" t="n">
         <v>0.2843503017374694</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2487288496772225</v>
+        <v>-0.2664016932492347</v>
       </c>
       <c r="R6" t="n">
-        <v>-1.463887204993606</v>
+        <v>-1.405947640316132</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2795085017569816</v>
+        <v>-0.2506255137206581</v>
       </c>
       <c r="T6" t="n">
-        <v>0.351304500561695</v>
+        <v>0.3870194189046512</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.144204809935183</v>
+        <v>-1.098889924912915</v>
       </c>
     </row>
     <row r="7">
@@ -902,34 +902,34 @@
         <v>0.1096492167184179</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1208353736979845</v>
+        <v>0.0917553577227732</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3257522251238671</v>
+        <v>0.3673553430926282</v>
       </c>
       <c r="N7" t="n">
-        <v>1.122591684751729</v>
+        <v>1.071439226908341</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3066250997509849</v>
+        <v>-0.2898357521322867</v>
       </c>
       <c r="P7" t="n">
         <v>2.170666494616522</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.3403786336390074</v>
+        <v>-0.4048707227581912</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.7991724561568991</v>
+        <v>-0.7915119562049365</v>
       </c>
       <c r="S7" t="n">
         <v>-0.54225052195838</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.439027268968885</v>
+        <v>-1.46160284646258</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9546475427171708</v>
+        <v>-0.9708504454469296</v>
       </c>
     </row>
     <row r="8">
@@ -1048,7 +1048,7 @@
         <v>0.8019667086241844</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9692516822448476</v>
+        <v>-6.586807742542967</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.3174458538428429</v>
@@ -1237,34 +1237,34 @@
         <v>-0.1650390483285127</v>
       </c>
       <c r="L12" t="n">
-        <v>0.00507298479303311</v>
+        <v>-0.04478019035086396</v>
       </c>
       <c r="M12" t="n">
-        <v>0.766881999454631</v>
+        <v>0.8217017574040804</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3821083142003463</v>
+        <v>0.3403183239294612</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.02153528316454768</v>
+        <v>0.06728415721141058</v>
       </c>
       <c r="P12" t="n">
-        <v>1.82474330564027</v>
+        <v>1.505429592739113</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.08258580893920843</v>
+        <v>0.001745584595744684</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7865633859221736</v>
+        <v>0.8432670309052079</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2147209269584128</v>
+        <v>0.2109093889477544</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6305001625688841</v>
+        <v>-0.7004332166012445</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2009079999426222</v>
+        <v>-0.1738625532809198</v>
       </c>
     </row>
     <row r="13">

--- a/p6_deployment/data/usa/data_preparation/df_selected_nan.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_selected_nan.xlsx
@@ -713,7 +713,7 @@
         <v>-0.2919555105092206</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4853996765270864</v>
+        <v>0.5445318455828561</v>
       </c>
       <c r="Q4" t="n">
         <v>0.6306742676790577</v>

--- a/p6_deployment/data/usa/data_preparation/df_selected_nan.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_selected_nan.xlsx
@@ -713,7 +713,7 @@
         <v>-0.2919555105092206</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5445318455828561</v>
+        <v>0.4972261103382403</v>
       </c>
       <c r="Q4" t="n">
         <v>0.6306742676790577</v>
@@ -1048,7 +1048,7 @@
         <v>0.8019667086241844</v>
       </c>
       <c r="P9" t="n">
-        <v>-6.586807742542967</v>
+        <v>-0.9692516822448476</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.3174458538428429</v>
@@ -1249,7 +1249,7 @@
         <v>0.06728415721141058</v>
       </c>
       <c r="P12" t="n">
-        <v>1.505429592739113</v>
+        <v>1.82474330564027</v>
       </c>
       <c r="Q12" t="n">
         <v>0.001745584595744684</v>

--- a/p6_deployment/data/usa/data_preparation/df_selected_nan.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_selected_nan.xlsx
@@ -713,7 +713,7 @@
         <v>-0.2919555105092206</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4972261103382403</v>
+        <v>0.3553089046043931</v>
       </c>
       <c r="Q4" t="n">
         <v>0.6306742676790577</v>
@@ -1048,7 +1048,7 @@
         <v>0.8019667086241844</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9692516822448476</v>
+        <v>-6.586807742542967</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.3174458538428429</v>
@@ -1249,7 +1249,7 @@
         <v>0.06728415721141058</v>
       </c>
       <c r="P12" t="n">
-        <v>1.82474330564027</v>
+        <v>1.505429592739113</v>
       </c>
       <c r="Q12" t="n">
         <v>0.001745584595744684</v>
@@ -1383,7 +1383,7 @@
         <v>-0.2551482724449938</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.2667615138623039</v>
+        <v>-0.4205051534073051</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.6010913172977284</v>
@@ -1450,7 +1450,7 @@
         <v>0.7054521872681059</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.445931986101286</v>
+        <v>0.2636540425679501</v>
       </c>
       <c r="Q15" t="n">
         <v>0.3230543998713907</v>

--- a/p6_deployment/data/usa/data_preparation/df_selected_nan.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U15"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -533,141 +533,141 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8K42rT3c</t>
+          <t>YakQgH8Q</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04472501056997844</v>
+        <v>0.06204614050032742</v>
       </c>
       <c r="C2" t="n">
         <v>-0.1807209931165159</v>
       </c>
       <c r="D2" t="n">
-        <v>1.467231000704904</v>
+        <v>-0.2753333608642887</v>
       </c>
       <c r="E2" t="n">
-        <v>1.006139778789871</v>
+        <v>-0.4305834134768635</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.902629061602736</v>
+        <v>1.509298952058975</v>
       </c>
       <c r="G2" t="n">
-        <v>1.337380321480496</v>
+        <v>-0.1497224999655234</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.02839053004854</v>
+        <v>1.286310825547314</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4310096843667015</v>
+        <v>-0.2412786367143328</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.445814724022394</v>
+        <v>1.455504713127439</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.291834004379261</v>
+        <v>-0.4451161383995819</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.09593576845612373</v>
+        <v>-0.3269985434476986</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3100339892089694</v>
+        <v>-0.3095543693281892</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1454894103596141</v>
+        <v>-0.6953269143594769</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3752503072057022</v>
+        <v>-0.7041920975508607</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.779362398308892</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.03257121544923205</v>
+        <v>-1.098405475825464</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.5999047921558401</v>
+        <v>-0.5533218183149616</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5761410600759237</v>
+        <v>-1.367575552532985</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.386038628497464</v>
+        <v>-1.007613153144537</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3150152541307285</v>
+        <v>-0.581561155885422</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ma0gz0nH</t>
+          <t>jy0LfcgK</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.007238379221068516</v>
+        <v>1.187919585973011</v>
       </c>
       <c r="C3" t="n">
         <v>-0.1807209931165159</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4714799369510795</v>
+        <v>-1.271084424618113</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.4305834134768635</v>
+        <v>0.5272320480342931</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5767502998170976</v>
+        <v>-0.7712125182123249</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1119148011152012</v>
+        <v>-0.6160174524528349</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9663896008807935</v>
+        <v>0.3190963305304753</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5150457245018297</v>
+        <v>-1.711909339079094</v>
       </c>
       <c r="J3" t="n">
-        <v>1.237905755341202</v>
+        <v>-0.5754188928774439</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.3193768878360264</v>
+        <v>-0.6434176961805969</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5419765114783058</v>
+        <v>-0.1943030848821248</v>
       </c>
       <c r="M3" t="n">
-        <v>0.07547521723561382</v>
+        <v>0.6692817791703193</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.08254869801242276</v>
+        <v>0.585342498354656</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5986483124553613</v>
+        <v>-0.4158479374693806</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.0142671519941674</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7985357660847284</v>
+        <v>-0.9255361091181474</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.01922163175775432</v>
+        <v>0.2594189010064604</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.05589827179834587</v>
+        <v>-0.3074597805018113</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8030511875260912</v>
+        <v>-1.228171446118461</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4940661278632975</v>
+        <v>-1.607244153831941</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>UT5bq9li</t>
+          <t>xYeHewvE</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -677,269 +677,269 @@
         <v>-0.1807209931165159</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2753333608642887</v>
+        <v>-1.022146658679657</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.9094911442324418</v>
+        <v>-0.4305834134768635</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.036388270569453</v>
+        <v>1.641886828237538</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3543801513721104</v>
+        <v>-0.4899917896184265</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8961218811573479</v>
+        <v>0.8151037638724443</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3259646341977893</v>
+        <v>-0.0942155664778562</v>
       </c>
       <c r="J4" t="n">
-        <v>1.818169642771169</v>
+        <v>-0.8413731746161782</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.7230660606979613</v>
+        <v>-0.7344109554856579</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3633651908204013</v>
+        <v>-0.08584673875274258</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8290949736384865</v>
+        <v>-0.3458332141574977</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8712193635692365</v>
+        <v>0.07512864782443832</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2919555105092206</v>
+        <v>0.09967864025324087</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3553089046043931</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.6306742676790577</v>
+        <v>-1.355343693518963</v>
       </c>
       <c r="R4" t="n">
-        <v>1.07436302156492</v>
+        <v>-0.1409741479492211</v>
       </c>
       <c r="S4" t="n">
-        <v>1.450506250858605</v>
+        <v>0.2760231632965051</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2393319011057967</v>
+        <v>-0.8444422381603277</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2034651948891617</v>
+        <v>-0.6496011647167784</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Sx1kytXA</t>
+          <t>OU7ZWg1D</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.170598456042662</v>
+        <v>1.361130885276501</v>
       </c>
       <c r="C5" t="n">
         <v>-0.1807209931165159</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.02639559492583261</v>
+        <v>-1.768959956495025</v>
       </c>
       <c r="E5" t="n">
+        <v>-0.4305834134768635</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.8375203794209172</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9593033329772704</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.2612287966405787</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.5360547345356125</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.7301748538399813</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.01669461118483658</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.05629458055758827</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.5288450325337151</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.666928772569279</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-0.5104423500122617</v>
+      </c>
+      <c r="P5" t="n">
         <v>0</v>
       </c>
-      <c r="F5" t="n">
-        <v>-1.593257350519421</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.7702648387256578</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-1.255727270330275</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-0.1992606166467678</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-0.2369316252099627</v>
-      </c>
-      <c r="K5" t="n">
-        <v>-1.102804900119238</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-0.459218624835031</v>
-      </c>
-      <c r="M5" t="n">
-        <v>-0.2489111876324631</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-0.8569472096538279</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-0.616641629909824</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.1944694047726996</v>
-      </c>
       <c r="Q5" t="n">
-        <v>-1.405032084091676</v>
+        <v>-0.2618285378746678</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2050056672795851</v>
+        <v>-0.2513611811913389</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.139752108032834</v>
+        <v>-0.7495981897382067</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3553626263082582</v>
+        <v>-0.4381588573122476</v>
       </c>
       <c r="U5" t="n">
-        <v>0.09169178736436154</v>
+        <v>-1.352933932819792</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2NHGKPBj</t>
+          <t>pv9VXZo7</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5643589084804479</v>
+        <v>-0.7866892260867727</v>
       </c>
       <c r="C6" t="n">
         <v>-0.1807209931165159</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.520022190556569</v>
+        <v>-0.2753333608642887</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5272320480342931</v>
+        <v>1.006139778789871</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4751135178661761</v>
+        <v>-1.619774925755134</v>
       </c>
       <c r="G6" t="n">
-        <v>0.682046874741572</v>
+        <v>0.9214956341269482</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3257133328140839</v>
+        <v>-1.082124668660586</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9562349352112579</v>
+        <v>-1.627873298943964</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7301748538399813</v>
+        <v>1.503860037079936</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6436517971841476</v>
+        <v>-0.2357655862252481</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.1690452042127522</v>
+        <v>-0.0390435628966849</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9094972283967933</v>
+        <v>-0.5470777175087497</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1186745329642373</v>
+        <v>-0.06057200377942405</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2934409419183345</v>
+        <v>0.5400478719283163</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2843503017374694</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2664016932492347</v>
+        <v>-0.2973276823386825</v>
       </c>
       <c r="R6" t="n">
-        <v>-1.405947640316132</v>
+        <v>-0.3096733340309925</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2506255137206581</v>
+        <v>0.8199084622063125</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3870194189046512</v>
+        <v>-0.6317519302597403</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.098889924912915</v>
+        <v>-0.6429571173011407</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4nxtRRYM</t>
+          <t>IHxZYFW0</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.06204614050032742</v>
+        <v>-1.219717474345497</v>
       </c>
       <c r="C7" t="n">
         <v>-0.1807209931165159</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7732088927412009</v>
+        <v>-2.266835488371937</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04832431727871479</v>
+        <v>-0.4305834134768635</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.142458571512304</v>
+        <v>0.08618908107572194</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8584828027097441</v>
+        <v>-0.7210388381481752</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.34252857116512</v>
+        <v>0.004958289413895384</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1999105739950954</v>
+        <v>-0.3043056668156794</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8752408256974724</v>
+        <v>0.7301748538399813</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1096492167184179</v>
+        <v>-1.304491918567033</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0917553577227732</v>
+        <v>-0.2066082065360321</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3673553430926282</v>
+        <v>-0.6511759382652296</v>
       </c>
       <c r="N7" t="n">
-        <v>1.071439226908341</v>
+        <v>-0.660943758565019</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2898357521322867</v>
+        <v>-0.1675097930479303</v>
       </c>
       <c r="P7" t="n">
-        <v>2.170666494616522</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.4048707227581912</v>
+        <v>0.1544185925226851</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.7915119562049365</v>
+        <v>-0.393134953877994</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.54225052195838</v>
+        <v>-0.0618273309260375</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.46160284646258</v>
+        <v>0.7504336906393443</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9708504454469296</v>
+        <v>-0.07664513690236552</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>IktpQolT</t>
+          <t>UN8LwZh9</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5643589084804479</v>
+        <v>-0.007238379221068516</v>
       </c>
       <c r="C8" t="n">
         <v>-0.1807209931165159</v>
@@ -948,61 +948,61 @@
         <v>-0.5242711268027448</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5272320480342931</v>
+        <v>0.04832431727871479</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.48718704957657</v>
+        <v>0.02431473885905853</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1371199336820828</v>
+        <v>0.682046874741572</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.747319651154757</v>
+        <v>-0.4125146336489283</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3259646341977893</v>
+        <v>0.6831178047720886</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3578199350912059</v>
+        <v>0.7301748538399813</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.03811803789124067</v>
+        <v>-0.233912013768775</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2439929303487342</v>
+        <v>0.1332529243327478</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6321674231072113</v>
+        <v>-0.8537587439681132</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.867378235009973</v>
+        <v>0.1918288426771413</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6461233511988076</v>
+        <v>0.8576836197582474</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7189717442973766</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.9880801842802897</v>
+        <v>-0.3348360205985664</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9138799633154754</v>
+        <v>-1.09717648460676</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6987862543120524</v>
+        <v>-0.05589827179834587</v>
       </c>
       <c r="T8" t="n">
-        <v>2.45605356457371</v>
+        <v>-0.07982990444872552</v>
       </c>
       <c r="U8" t="n">
-        <v>2.46511472747645</v>
+        <v>0.04558277511278901</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>OWICL5dp</t>
+          <t>vRwVZeHf</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1012,460 +1012,2269 @@
         <v>-0.1807209931165159</v>
       </c>
       <c r="D9" t="n">
+        <v>-1.271084424618113</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.006139778789871</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.588851677766113</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.2253378976661686</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.9267054363743871</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-1.921999439416916</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.3433322622200037</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.8016877987674467</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-0.8087454997276592</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.1319960090840944</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.4924016141562425</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.4844199829888502</v>
+      </c>
+      <c r="P9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.1480634232923849</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.6484400313190632</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-0.1934446839228922</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-2.762359840768208</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.165372769412456</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.8141671830339022</v>
-      </c>
-      <c r="L9" t="n">
-        <v>-0.7151897100036683</v>
-      </c>
-      <c r="M9" t="n">
-        <v>-0.2776177730749124</v>
-      </c>
-      <c r="N9" t="n">
-        <v>-0.1841637060203911</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.8019667086241844</v>
-      </c>
-      <c r="P9" t="n">
-        <v>-6.586807742542967</v>
-      </c>
       <c r="Q9" t="n">
-        <v>-0.3174458538428429</v>
+        <v>0.1051724352961188</v>
       </c>
       <c r="R9" t="n">
-        <v>-1.044644832795887</v>
+        <v>-0.4022838920711055</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1141386738993654</v>
+        <v>-0.3214354198742267</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7080537887786632</v>
+        <v>-0.1250082733027301</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2924610556933888</v>
+        <v>0.1431921790086434</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>z7pPU9Zc</t>
+          <t>naJGvFw3</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.187919585973011</v>
+        <v>-0.561514536992236</v>
       </c>
       <c r="C10" t="n">
         <v>-0.1807209931165159</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.271084424618113</v>
+        <v>-0.5242711268027448</v>
       </c>
       <c r="E10" t="n">
-        <v>0.04832431727871479</v>
+        <v>-1.38839887498802</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01673828879171205</v>
+        <v>0.9789474473447191</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8950742773004536</v>
+        <v>-0.200132765099287</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1702941005278848</v>
+        <v>-0.3009129611469855</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.190972523065403</v>
+        <v>-0.4513687370521561</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.606342498882326</v>
+        <v>-0.7688401886874321</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.048286377945056</v>
+        <v>-0.07032610081985607</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7449211304537035</v>
+        <v>-0.9355980791639588</v>
       </c>
       <c r="M10" t="n">
-        <v>1.173285411355883</v>
+        <v>-2.004687915269346</v>
       </c>
       <c r="N10" t="n">
-        <v>1.097065528964239</v>
+        <v>-0.0007968182787644678</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3023583131341103</v>
+        <v>-0.5690140505636597</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.182793833803111</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.548429084025844</v>
+        <v>-0.4683885196522137</v>
       </c>
       <c r="R10" t="n">
-        <v>1.047689458874012</v>
+        <v>-0.7459618134973137</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3074597805018113</v>
+        <v>-0.264135298447326</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3348489098639843</v>
+        <v>-0.8604706087560049</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9066821291503365</v>
+        <v>-0.2908790053537539</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>EcqTTTl4</t>
+          <t>88KCueOd</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.361130885276501</v>
+        <v>1.170598456042662</v>
       </c>
       <c r="C11" t="n">
         <v>-0.1807209931165159</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.511524318064218</v>
+        <v>1.71616876664336</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5272320480342931</v>
+        <v>1.963955240301028</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2187769572542859</v>
+        <v>-1.460669474340857</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.006893415419860975</v>
+        <v>0.6442391758912493</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.07770961614309954</v>
+        <v>-1.255727270330275</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.249711118335882</v>
+        <v>-1.753927359146658</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2852869491624603</v>
+        <v>-1.735946667737377</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1616256420975665</v>
+        <v>-1.234447697785266</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.3609223702029415</v>
+        <v>0.1189518320834169</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3074094685321985</v>
+        <v>0.4093553300020025</v>
       </c>
       <c r="N11" t="n">
-        <v>0.930433180592499</v>
+        <v>0.03222741631609424</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7034499319398777</v>
+        <v>0.03640069070217022</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2991333440014119</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.8927559516728555</v>
+        <v>-0.7486860624000781</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.4061442851936103</v>
+        <v>0.2739451085483541</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3051728576954169</v>
+        <v>-0.139752108032834</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.052499377981391</v>
+        <v>-0.6615013967428367</v>
       </c>
       <c r="U11" t="n">
-        <v>0.01131347791632062</v>
+        <v>-0.5964939062569471</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>APxxS7JG</t>
+          <t>p4vRzx2l</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.561514536992236</v>
+        <v>-1.219717474345497</v>
       </c>
       <c r="C12" t="n">
         <v>-0.1807209931165159</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.5242711268027448</v>
+        <v>-0.02639559492583261</v>
       </c>
       <c r="E12" t="n">
         <v>0.5272320480342931</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1158495873868519</v>
+        <v>-0.09059475382903026</v>
       </c>
       <c r="G12" t="n">
-        <v>2.102536131546547</v>
+        <v>-0.02789769255892875</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5471452226988911</v>
+        <v>-0.2223784508678405</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8295309176602371</v>
+        <v>1.71255929642742</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.171144583309851</v>
+        <v>1.528037699056185</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1650390483285127</v>
+        <v>-0.4689482958528863</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.04478019035086396</v>
+        <v>-0.3978066098963277</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8217017574040804</v>
+        <v>-1.390530115006406</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3403183239294612</v>
+        <v>1.497167778111243</v>
       </c>
       <c r="O12" t="n">
-        <v>0.06728415721141058</v>
+        <v>0.3037860334917161</v>
       </c>
       <c r="P12" t="n">
-        <v>1.505429592739113</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.001745584595744684</v>
+        <v>0.1361616346834112</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8432670309052079</v>
+        <v>-1.782046397094806</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2109093889477544</v>
+        <v>0.3885270602444441</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7004332166012445</v>
+        <v>-0.5350738927435134</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1738625532809198</v>
+        <v>0.8265572721833087</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>tpoLVkKi</t>
+          <t>QJcftbvR</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.007238379221068516</v>
+        <v>1.72487461381383</v>
       </c>
       <c r="C13" t="n">
         <v>-0.1807209931165159</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.520022190556569</v>
+        <v>-0.5242711268027448</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.9094911442324418</v>
+        <v>0.5272320480342931</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3292529309504454</v>
+        <v>1.111535323523282</v>
       </c>
       <c r="G13" t="n">
-        <v>1.026517019822289</v>
+        <v>0.1149313919867341</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.540931544501907</v>
+        <v>-0.3009129611469855</v>
       </c>
       <c r="I13" t="n">
-        <v>1.796595336562549</v>
+        <v>0.5150457245018297</v>
       </c>
       <c r="J13" t="n">
-        <v>1.455504713127439</v>
+        <v>0.5851088819824897</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5059642079683527</v>
+        <v>-0.1433419370470504</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.01948954508357574</v>
+        <v>-0.7929759071200888</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5657749433719278</v>
+        <v>-2.680317197872658</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.79243877023971</v>
+        <v>-1.464720782290519</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.01510156397430543</v>
+        <v>-1.092068068394335</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.8569005610388852</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.626512556677519</v>
+        <v>-0.7668746091608458</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4096692493325728</v>
+        <v>-3.541121637291685</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4961309120294122</v>
+        <v>-3.41005172117789</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4118220462759126</v>
+        <v>0.9182684684142169</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7319918647572632</v>
+        <v>-0.7903850325871659</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>WYwYSm4A</t>
+          <t>W0zNyInr</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1832940500127703</v>
+        <v>-0.8213314859474707</v>
       </c>
       <c r="C14" t="n">
         <v>-0.1807209931165159</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.7732088927412009</v>
+        <v>-0.5242711268027448</v>
       </c>
       <c r="E14" t="n">
-        <v>1.48504750954545</v>
+        <v>-0.4305834134768635</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2938961639694947</v>
+        <v>1.509298952058974</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.7546456815706843</v>
+        <v>0.3543801513721099</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.309461408942322</v>
+        <v>-0.9953233678257414</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5143957671535022</v>
+        <v>-2.51025172036282</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.4787082449724491</v>
+        <v>0.004844994552523201</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.261948563113211</v>
+        <v>-1.157575531066459</v>
       </c>
       <c r="L14" t="n">
-        <v>1.13646859289878</v>
+        <v>0.624453558597949</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3525942298574934</v>
+        <v>0.3267097055321899</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.004635792756770377</v>
+        <v>1.497951563098985</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2551482724449938</v>
+        <v>-0.6215203570887871</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.4205051534073051</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.6010913172977284</v>
+        <v>-0.1741081997006338</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2768920381336487</v>
+        <v>-0.3646742802996407</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6922642892715927</v>
+        <v>-0.8105827979087441</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5506118167234306</v>
+        <v>-1.305702931032635</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5250370898062255</v>
+        <v>-1.186611977480668</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
+          <t>YyTMIXGq</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.8414969873660316</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.1807209931165159</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.7732088927412009</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.04832431727871479</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-1.814237144150361</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.44798323534029</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-1.131725411994783</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.01082948369105488</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-0.3578199350912059</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.9191074598200377</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-0.346203646503393</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.0417753172082286</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0.2120376029873369</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-1.486609003046052</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.03449478203733201</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.2624923244547682</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0.9317050058030042</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.3001920143288114</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.06250761168737012</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>nTbjsvPK</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.1832940500127703</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.1807209931165159</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.218293234766448</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.4305834134768635</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-0.7535341347218496</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.3291750188052283</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.6563849550420631</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.766582465085718</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.3675099241962523</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0.7501362402052578</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.04144546377732209</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2040006555927049</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.208209068901333</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-0.6820354070665282</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-0.9343320285318083</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-0.4273230159611143</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.605256975435122</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-1.096835807830874</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.4285506314455576</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>IgfnrK9E</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.5643589084804479</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.1807209931165159</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-1.520022190556569</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-1.38839887498802</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.7491284619685415</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.7072520073084536</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.1190435689215968</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.05284750375861986</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-0.9139061605449238</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-0.9587648445294763</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-0.007256342624950922</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-0.7463328524994769</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-0.1638550640357313</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.9353062042378668</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.4622604278372997</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-0.7762293536243805</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0.2506255137206581</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.6946152423167712</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.2127285085355635</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>v3erq0f8</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.04472501056997844</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.1807209931165159</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-2.266835488371937</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.9094911442324418</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.8772828191551761</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.1653416571204973</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-1.057324296993488</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.5150457245018303</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.5851088819824902</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.2378465278193038</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.4184270220614752</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.8536365451406672</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-0.2703650789648879</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-0.2793157752436242</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.131548193246926</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.9928921360575318</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-0.05589827179834587</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.8583257554008269</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.3933608685969429</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>xbHaKGH7</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.8414969873660316</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.1807209931165159</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.2753333608642887</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.4305834134768635</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0.3469313144409205</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.4647866570515449</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.2017114744785917</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.52347820612338</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.2949769382675054</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-0.5781350297852402</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.023348313233422</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.54311906560004</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.200136373475204</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.2625525254399021</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.365644777478072</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.632202049173306</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.450506250858605</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.534616986174231</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.529937417194885</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>W0EiMxme</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.06204614050032742</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.1807209931165159</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-1.520022190556569</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-1.867306605743599</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-0.8242476686837503</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.967508635652538</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-1.144125597828332</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.733568306461203</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-0.09186565335247215</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-0.2342901769283554</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-0.08311665507712378</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.04072095197715034</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.2540103296360415</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-0.4207402110154927</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-0.6239305762846177</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-0.8046632578026934</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-0.2906890132549145</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-1.215548011328859</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-0.3757017200339922</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>QNDeLd21</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1.72487461381383</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.1807209931165159</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.5242711268027448</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-0.4305834134768635</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.2629729159804737</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.022316164394475</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.9457226244915447</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.3889916642991359</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-0.1402209773049685</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-0.2877057232203964</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-1.293967796026414</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-2.603686728625025</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-2.745705058650955</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-0.5264674577616056</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-0.7851983146529039</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-2.37111333460216</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-2.697294113184737</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.46049710218078</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.2039615244074821</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>hAFmNIXl</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>-0.561514536992236</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.1807209931165159</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-1.022146658679657</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-0.4305834134768635</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.5900230105542649</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.866688105385012</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.2182450555899906</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-1.438792208639923</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-1.445814724022393</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.2112118089200294</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-0.364159430460656</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-0.1542461899382798</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-0.5835745137381739</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-0.371321341358435</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-0.4000837651859042</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.1114826698388309</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.595874728024271</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-0.2555040511259764</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.4198377923558461</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>zZKrObIr</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>-1.219717474345497</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.1807209931165159</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-0.5242711268027448</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.9789474473447186</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.9940944409560601</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.497113984717651</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.342829597440888</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.528037699056185</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-0.2223150102080307</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.2132680261138195</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-0.8643819710133412</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.8924033351630787</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-0.4353532927870725</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.6834047155780243</v>
+      </c>
+      <c r="R23" t="n">
+        <v>-0.8646709285180871</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.2760231632965051</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.1121328310685442</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.2584336890426858</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>fiHVGBod</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>-1.219717474345497</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.1807209931165159</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-0.5242711268027448</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-0.4305834134768635</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.588851677766113</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-1.078111549512333</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.554981518607547</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.5143957671535022</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.9719514736024671</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-1.232168214295527</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-0.2923568606264751</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-0.8246488593034789</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.229898065302686</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.2653294602426118</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-0.2667577857134903</v>
+      </c>
+      <c r="R24" t="n">
+        <v>-1.201334667245408</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.2807790144272021</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.6501116637590253</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.9209016475581973</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>G0IRHiWk</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>-0.8213314859474707</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.1807209931165159</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-1.271084424618113</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.5272320480342931</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.279479966682797</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.791269115864726</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.7903033922053456</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.5143957671535028</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-1.735946667737377</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.3033049535534725</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.6096983466915434</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.523078892142737</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.499860860845699</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.3617292892759263</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.994712869052528</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.9885608220661676</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.19285953764801</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.9776507152121851</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.1209916153531019</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>b9cFuRmG</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.8241758574356827</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.1807209931165159</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-1.271084424618113</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.963955240301028</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.058500173051857</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.2031493559708199</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.07770961614309954</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.3259646341977893</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.5851088819824902</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.4965101289786115</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.8489161004037735</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.611347166299461</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.3799984244732368</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.5105034262770338</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.7062256437713761</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.9397135899420138</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.002799413565796021</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.02749742735349787</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-1.844588929490746</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>4nbBt7Y9</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1.72487461381383</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.1807209931165159</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-2.764711020248849</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-0.4305834134768635</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.482781376823261</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-0.2757481627999323</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.769918073055733</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.208343055616646</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.09283978348371</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-0.3028007360073505</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-0.4118404455434831</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-0.1914354937419422</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.4331872956935946</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.05880293163861388</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.3862959234553024</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.1022560764346222</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.3843343684327204</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.3532561340301507</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.4186063150250099</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>jqf7smJ3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>-0.561514536992236</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-0.1807209931165159</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-0.7732088927412009</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.006139778789871</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.297158350173272</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-0.2631455965164912</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-0.1397105453108456</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-0.8715489377278015</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-0.9380838225211729</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.2230981645953036</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-1.093561979989889</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-0.1923092369568001</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.9317174946652457</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.1734488280117444</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-0.5705947167748943</v>
+      </c>
+      <c r="R28" t="n">
+        <v>-0.8962093597441825</v>
+      </c>
+      <c r="S28" t="n">
+        <v>-1.106866352603937</v>
+      </c>
+      <c r="T28" t="n">
+        <v>-1.535990270991765</v>
+      </c>
+      <c r="U28" t="n">
+        <v>-2.02090999087257</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>UT5bq9li</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>-0.7866892260867727</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-0.1807209931165159</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-0.2753333608642887</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-0.9094911442324418</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-1.036388270569453</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.3543801513721104</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-0.8961218811573479</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.3259646341977893</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.818169642771169</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-0.7230660606979613</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.3633651908204013</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.8290949736384865</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.8712193635692365</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-0.2919555105092206</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.4942695018854518</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.6306742676790577</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.07436302156492</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.450506250858605</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.2393319011057967</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.2034651948891617</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>8K42rT3c</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.04472501056997844</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.1807209931165159</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.467231000704904</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.006139778789871</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-1.902629061602736</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.337380321480496</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-1.02839053004854</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.4310096843667015</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-1.445814724022394</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-0.291834004379261</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-0.09593576845612373</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.3100339892089694</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.1454894103596141</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-0.3752503072057022</v>
+      </c>
+      <c r="P30" t="n">
+        <v>-1.779362398308892</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>-0.03257121544923205</v>
+      </c>
+      <c r="R30" t="n">
+        <v>-0.5999047921558401</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.5761410600759237</v>
+      </c>
+      <c r="T30" t="n">
+        <v>-0.386038628497464</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0.3150152541307285</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Ma0gz0nH</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>-0.007238379221068516</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.1807209931165159</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.4714799369510795</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-0.4305834134768635</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-0.5767502998170976</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-0.1119148011152012</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-0.9663896008807935</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.5150457245018297</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.237905755341202</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-0.3193768878360264</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.5419765114783058</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.07547521723561382</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-0.08254869801242276</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.5986483124553613</v>
+      </c>
+      <c r="P31" t="n">
+        <v>-0.0142671519941674</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.7985357660847284</v>
+      </c>
+      <c r="R31" t="n">
+        <v>-0.01922163175775432</v>
+      </c>
+      <c r="S31" t="n">
+        <v>-0.05589827179834587</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.8030511875260912</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0.4940661278632975</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>2NHGKPBj</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.5643589084804479</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.1807209931165159</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-1.520022190556569</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.5272320480342931</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.4751135178661761</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.682046874741572</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-0.3257133328140839</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.9562349352112579</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.7301748538399813</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-0.6436517971841476</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-0.1690452042127522</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-0.9094972283967933</v>
+      </c>
+      <c r="N32" t="n">
+        <v>-0.1186745329642373</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.2934409419183345</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.2843503017374694</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>-0.2664016932492347</v>
+      </c>
+      <c r="R32" t="n">
+        <v>-1.405947640316132</v>
+      </c>
+      <c r="S32" t="n">
+        <v>-0.2506255137206581</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0.3870194189046512</v>
+      </c>
+      <c r="U32" t="n">
+        <v>-1.098889924912915</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Sx1kytXA</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1.170598456042662</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.1807209931165159</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-0.02639559492583261</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-1.593257350519421</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.7702648387256578</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-1.255727270330275</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-0.1992606166467678</v>
+      </c>
+      <c r="J33" t="n">
+        <v>-0.2369316252099627</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-1.102804900119238</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-0.459218624835031</v>
+      </c>
+      <c r="M33" t="n">
+        <v>-0.2489111876324631</v>
+      </c>
+      <c r="N33" t="n">
+        <v>-0.8569472096538279</v>
+      </c>
+      <c r="O33" t="n">
+        <v>-0.616641629909824</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.1944694047726996</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>-1.405032084091676</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.2050056672795851</v>
+      </c>
+      <c r="S33" t="n">
+        <v>-0.139752108032834</v>
+      </c>
+      <c r="T33" t="n">
+        <v>-0.3553626263082582</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0.09169178736436154</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>OWICL5dp</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.8241758574356827</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-0.1807209931165159</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.1480634232923849</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.6484400313190632</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-0.1934446839228922</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-2.762359840768208</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.165372769412456</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.8141671830339022</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-0.7151897100036683</v>
+      </c>
+      <c r="M34" t="n">
+        <v>-0.2776177730749124</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-0.1841637060203911</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.8019667086241844</v>
+      </c>
+      <c r="P34" t="n">
+        <v>-0.9692516822448476</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>-0.3174458538428429</v>
+      </c>
+      <c r="R34" t="n">
+        <v>-1.044644832795887</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.1141386738993654</v>
+      </c>
+      <c r="T34" t="n">
+        <v>-0.7080537887786632</v>
+      </c>
+      <c r="U34" t="n">
+        <v>-0.2924610556933888</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>4nxtRRYM</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.06204614050032742</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-0.1807209931165159</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-0.7732088927412009</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.04832431727871479</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-1.142458571512304</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.8584828027097441</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-1.34252857116512</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.1999105739950954</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.8752408256974724</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.1096492167184179</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.0917553577227732</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.3673553430926282</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.071439226908341</v>
+      </c>
+      <c r="O35" t="n">
+        <v>-0.2898357521322867</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.170666494616522</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>-0.4048707227581912</v>
+      </c>
+      <c r="R35" t="n">
+        <v>-0.7915119562049365</v>
+      </c>
+      <c r="S35" t="n">
+        <v>-0.54225052195838</v>
+      </c>
+      <c r="T35" t="n">
+        <v>-1.46160284646258</v>
+      </c>
+      <c r="U35" t="n">
+        <v>-0.9708504454469296</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>IktpQolT</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.5643589084804479</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.1807209931165159</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-0.5242711268027448</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.5272320480342931</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-1.48718704957657</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-0.1371199336820828</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-0.747319651154757</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.3259646341977893</v>
+      </c>
+      <c r="J36" t="n">
+        <v>-0.3578199350912059</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-0.03811803789124067</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-0.2439929303487342</v>
+      </c>
+      <c r="M36" t="n">
+        <v>-0.6321674231072113</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-1.867378235009973</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.6461233511988076</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.7189717442973766</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.9880801842802897</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.9138799633154754</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.6987862543120524</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.45605356457371</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2.46511472747645</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>EcqTTTl4</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1.361130885276501</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.1807209931165159</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-3.511524318064218</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.5272320480342931</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.2187769572542859</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-0.006893415419860975</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-0.07770961614309954</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-1.249711118335882</v>
+      </c>
+      <c r="J37" t="n">
+        <v>-0.2852869491624603</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.1616256420975665</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-0.3609223702029415</v>
+      </c>
+      <c r="M37" t="n">
+        <v>-0.3074094685321985</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.930433180592499</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.7034499319398777</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.2991333440014119</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>-0.8927559516728555</v>
+      </c>
+      <c r="R37" t="n">
+        <v>-0.4061442851936103</v>
+      </c>
+      <c r="S37" t="n">
+        <v>-0.3051728576954169</v>
+      </c>
+      <c r="T37" t="n">
+        <v>-1.052499377981391</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.01131347791632062</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>z7pPU9Zc</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1.187919585973011</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.1807209931165159</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-1.271084424618113</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.04832431727871479</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.01673828879171205</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-0.8950742773004536</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.1702941005278848</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-4.190972523065403</v>
+      </c>
+      <c r="J38" t="n">
+        <v>-2.606342498882326</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-1.048286377945056</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.7449211304537035</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.173285411355883</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1.097065528964239</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.3023583131341103</v>
+      </c>
+      <c r="P38" t="n">
+        <v>-0.182793833803111</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.548429084025844</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.047689458874012</v>
+      </c>
+      <c r="S38" t="n">
+        <v>-0.3074597805018113</v>
+      </c>
+      <c r="T38" t="n">
+        <v>-0.3348489098639843</v>
+      </c>
+      <c r="U38" t="n">
+        <v>-0.9066821291503365</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>tpoLVkKi</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>-0.007238379221068516</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-0.1807209931165159</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-1.520022190556569</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-0.9094911442324418</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-0.3292529309504454</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1.026517019822289</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-1.540931544501907</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.796595336562549</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.455504713127439</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.5059642079683527</v>
+      </c>
+      <c r="L39" t="n">
+        <v>-0.01948954508357574</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.5657749433719278</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-1.79243877023971</v>
+      </c>
+      <c r="O39" t="n">
+        <v>-0.01510156397430543</v>
+      </c>
+      <c r="P39" t="n">
+        <v>-0.8569005610388852</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>-1.626512556677519</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.4096692493325728</v>
+      </c>
+      <c r="S39" t="n">
+        <v>-0.4961309120294122</v>
+      </c>
+      <c r="T39" t="n">
+        <v>-0.4118220462759126</v>
+      </c>
+      <c r="U39" t="n">
+        <v>-0.7319918647572632</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>WYwYSm4A</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.1832940500127703</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.1807209931165159</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-0.7732088927412009</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.48504750954545</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-0.2938961639694947</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-0.7546456815706843</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-1.309461408942322</v>
+      </c>
+      <c r="I40" t="n">
+        <v>-0.5143957671535022</v>
+      </c>
+      <c r="J40" t="n">
+        <v>-0.4787082449724491</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-1.261948563113211</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1.13646859289878</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.3525942298574934</v>
+      </c>
+      <c r="N40" t="n">
+        <v>-0.004635792756770377</v>
+      </c>
+      <c r="O40" t="n">
+        <v>-0.2551482724449938</v>
+      </c>
+      <c r="P40" t="n">
+        <v>-0.4205051534073051</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>-0.6010913172977284</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.2768920381336487</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.6922642892715927</v>
+      </c>
+      <c r="T40" t="n">
+        <v>-0.5506118167234306</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0.5250370898062255</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
           <t>ln2oxMH4</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B41" t="n">
         <v>-0.8213314859474707</v>
       </c>
-      <c r="C15" t="n">
-        <v>-0.1807209931165159</v>
-      </c>
-      <c r="D15" t="n">
+      <c r="C41" t="n">
+        <v>-0.1807209931165159</v>
+      </c>
+      <c r="D41" t="n">
         <v>2.214044298520272</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E41" t="n">
         <v>1.48504750954545</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F41" t="n">
         <v>0.7933244206947293</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G41" t="n">
         <v>0.4425981153561957</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H41" t="n">
         <v>0.1206933571936881</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I41" t="n">
         <v>-1.144666068166971</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J41" t="n">
         <v>-1.083149794378664</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K41" t="n">
         <v>-0.04520859713353993</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L41" t="n">
         <v>0.1937590527240852</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M41" t="n">
         <v>2.480064541975865</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N41" t="n">
         <v>1.060940060448007</v>
       </c>
-      <c r="O15" t="n">
+      <c r="O41" t="n">
         <v>0.7054521872681059</v>
       </c>
-      <c r="P15" t="n">
+      <c r="P41" t="n">
         <v>0.2636540425679501</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="Q41" t="n">
         <v>0.3230543998713907</v>
       </c>
-      <c r="R15" t="n">
+      <c r="R41" t="n">
         <v>0.4938642393407378</v>
       </c>
-      <c r="S15" t="n">
+      <c r="S41" t="n">
         <v>-0.3955063085480252</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T41" t="n">
         <v>-0.02352957816750952</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U41" t="n">
         <v>-1.507333021794896</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>APxxS7JG</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>-0.561514536992236</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-0.1807209931165159</v>
+      </c>
+      <c r="D42" t="n">
+        <v>-0.5242711268027448</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.5272320480342931</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-0.1158495873868519</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2.102536131546547</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-0.5471452226988911</v>
+      </c>
+      <c r="I42" t="n">
+        <v>-0.8295309176602371</v>
+      </c>
+      <c r="J42" t="n">
+        <v>-2.171144583309851</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-0.1650390483285127</v>
+      </c>
+      <c r="L42" t="n">
+        <v>-0.04478019035086396</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.8217017574040804</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.3403183239294612</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.06728415721141058</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.505429592739113</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.001745584595744684</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.8432670309052079</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0.2109093889477544</v>
+      </c>
+      <c r="T42" t="n">
+        <v>-0.7004332166012445</v>
+      </c>
+      <c r="U42" t="n">
+        <v>-0.1738625532809198</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/usa/data_preparation/df_selected_nan.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_selected_nan.xlsx
@@ -425,108 +425,128 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U15"/>
+  <dimension ref="A1:Y15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_away</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>id_competition</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>h2h_27_segun_loc</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>h2h_3</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_shots_on_goal_against</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_away_against</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_sub</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_start</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_start</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_start</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
     </row>
@@ -537,64 +557,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04472501056997844</v>
+        <v>1.484893524923903</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.1807209931165159</v>
+        <v>-1.30482375367543</v>
       </c>
       <c r="D2" t="n">
-        <v>1.467231000704904</v>
+        <v>-0.02220836388162897</v>
       </c>
       <c r="E2" t="n">
-        <v>1.006139778789871</v>
+        <v>1.43039768118383</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.902629061602736</v>
+        <v>0.8253483575158508</v>
       </c>
       <c r="G2" t="n">
-        <v>1.337380321480496</v>
+        <v>-1.643670027246644</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.02839053004854</v>
+        <v>-0.3555223349029683</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4310096843667015</v>
+        <v>-0.6945824315454244</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.445814724022394</v>
+        <v>1.174773927758107</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.291834004379261</v>
+        <v>-1.602275721109812</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.09593576845612373</v>
+        <v>0.5096813304752958</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3100339892089694</v>
+        <v>0.4646428307760516</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1454894103596141</v>
+        <v>-0.8803654672242148</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3752503072057022</v>
+        <v>0.1318058064680049</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>0.4267867277166374</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.03257121544923205</v>
+        <v>0.1650245281777734</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.5999047921558401</v>
+        <v>0.1421652408513906</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5761410600759237</v>
+        <v>-0.3772153751680706</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.386038628497464</v>
+        <v>0.7814038786445447</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3150152541307285</v>
+        <v>-0.2542164947997497</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.4295164629720869</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.2558942269821199</v>
       </c>
     </row>
     <row r="3">
@@ -604,64 +636,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.007238379221068516</v>
+        <v>1.504520286883804</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.1807209931165159</v>
+        <v>-0.6314582141501968</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4714799369510795</v>
+        <v>-0.07274206079835104</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.4305834134768635</v>
+        <v>0.455462256487106</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5767502998170976</v>
+        <v>0.6986460817203919</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1119148011152012</v>
+        <v>0.4790107056978561</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9663896008807935</v>
+        <v>1.562295710563276</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5150457245018297</v>
+        <v>0.7066094542368555</v>
       </c>
       <c r="J3" t="n">
-        <v>1.237905755341202</v>
+        <v>-0.07805852786712188</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.3193768878360264</v>
+        <v>0.08193927720928973</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5419765114783058</v>
+        <v>-0.1634948051709595</v>
       </c>
       <c r="M3" t="n">
-        <v>0.07547521723561382</v>
+        <v>-0.1271176141648149</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.08254869801242276</v>
+        <v>0.01044881503960961</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5986483124553613</v>
+        <v>0.2469340055803715</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0.06709034043067431</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7985357660847284</v>
+        <v>-0.1124320274006492</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.01922163175775432</v>
+        <v>0.4628070268623617</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.05589827179834587</v>
+        <v>-0.1239515343624319</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8030511875260912</v>
+        <v>-0.05267552797811428</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4940661278632975</v>
+        <v>0.5862765141982367</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.001229027206602704</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-0.02378575712559158</v>
       </c>
     </row>
     <row r="4">
@@ -671,64 +715,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.7866892260867727</v>
+        <v>1.484893524923903</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.1807209931165159</v>
+        <v>1.244987089326787</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2753333608642887</v>
+        <v>-0.8307475145491819</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.9094911442324418</v>
+        <v>-0.2757393120354372</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.036388270569453</v>
+        <v>-0.8933955576225415</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3543801513721104</v>
+        <v>-0.8137497406818768</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8961218811573479</v>
+        <v>-2.467689054192751</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3259646341977893</v>
+        <v>-1.859545662218913</v>
       </c>
       <c r="J4" t="n">
-        <v>1.818169642771169</v>
+        <v>0.7689721554990351</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.7230660606979613</v>
+        <v>-0.1695786525963986</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3633651908204013</v>
+        <v>-0.2048785840016718</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8290949736384865</v>
+        <v>0.8850289693890135</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8712193635692365</v>
+        <v>-0.8418984868537167</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2919555105092206</v>
+        <v>0.2364883488219674</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.03093950304962</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.6306742676790577</v>
+        <v>0.9655289006763714</v>
       </c>
       <c r="R4" t="n">
-        <v>1.07436302156492</v>
+        <v>0.24420900486391</v>
       </c>
       <c r="S4" t="n">
-        <v>1.450506250858605</v>
+        <v>1.164842762821797</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2393319011057967</v>
+        <v>1.707802816006683</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2034651948891617</v>
+        <v>-0.2423081192723966</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.104709810019914</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.01165303335159579</v>
       </c>
     </row>
     <row r="5">
@@ -738,64 +794,76 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.170598456042662</v>
+        <v>1.484893524923903</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1807209931165159</v>
+        <v>0.6075343785762326</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.02639559492583261</v>
+        <v>1.072688402647349</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>-0.03200545586125614</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.593257350519421</v>
+        <v>-0.191024246147718</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7702648387256578</v>
+        <v>-1.5798300052032</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.255727270330275</v>
+        <v>-0.6525457798030938</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1992606166467678</v>
+        <v>-0.1121008162086799</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2369316252099627</v>
+        <v>0.4573743660858196</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.102804900119238</v>
+        <v>-1.466169499601038</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.459218624835031</v>
+        <v>1.09871044916577</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2489111876324631</v>
+        <v>-0.2915105615694395</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8569472096538279</v>
+        <v>-0.6619135102781571</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.616641629909824</v>
+        <v>-0.4185399277592944</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0.1923036253187315</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.405032084091676</v>
+        <v>-0.5953641212135954</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2050056672795851</v>
+        <v>-1.429109170801369</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.139752108032834</v>
+        <v>0.1506422359235565</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3553626263082582</v>
+        <v>-0.1530878105382049</v>
       </c>
       <c r="U5" t="n">
-        <v>0.09169178736436154</v>
+        <v>-0.6053799158050117</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-0.2919870107058845</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-0.7641180574321723</v>
       </c>
     </row>
     <row r="6">
@@ -805,64 +873,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5643589084804479</v>
+        <v>1.504520286883804</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.1807209931165159</v>
+        <v>-0.1825478544667079</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.520022190556569</v>
+        <v>0.4831286052855917</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5272320480342931</v>
+        <v>-1.494408592906343</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4751135178661761</v>
+        <v>-0.1331819028497911</v>
       </c>
       <c r="G6" t="n">
-        <v>0.682046874741572</v>
+        <v>0.1438505899697769</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3257133328140839</v>
+        <v>0.007506319974963347</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9562349352112579</v>
+        <v>-0.1121008162086799</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7301748538399813</v>
+        <v>-0.2962574966810276</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6436517971841476</v>
+        <v>-0.5564068610950201</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.1690452042127522</v>
+        <v>-0.1421131861084248</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9094972283967933</v>
+        <v>0.1662047828380386</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1186745329642373</v>
+        <v>-0.4991017181280399</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2934409419183345</v>
+        <v>-0.2799411343178443</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.7938263964356514</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2664016932492347</v>
+        <v>0.08088349147412106</v>
       </c>
       <c r="R6" t="n">
-        <v>-1.405947640316132</v>
+        <v>-0.3210273573789438</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2506255137206581</v>
+        <v>-1.538829472400337</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3870194189046512</v>
+        <v>-0.3695027037400853</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.098889924912915</v>
+        <v>0.266521634274559</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-2.1791511756188</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-0.1618181227520909</v>
       </c>
     </row>
     <row r="7">
@@ -872,64 +952,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.06204614050032742</v>
+        <v>1.504520286883804</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.1807209931165159</v>
+        <v>-0.6763492501185456</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7732088927412009</v>
+        <v>-0.005363798242721613</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04832431727871479</v>
+        <v>-0.7632070243837995</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.142458571512304</v>
+        <v>-0.6326459465652218</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8584828027097441</v>
+        <v>-0.9130564416383449</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.34252857116512</v>
+        <v>0.2605262915565519</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1999105739950954</v>
+        <v>-0.6039741802708198</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8752408256974724</v>
+        <v>1.886537353704573</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1096492167184179</v>
+        <v>-1.557702923422728</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0917553577227732</v>
+        <v>-0.9773757888416365</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3673553430926282</v>
+        <v>0.8178860508650206</v>
       </c>
       <c r="N7" t="n">
-        <v>1.071439226908341</v>
+        <v>-0.7076808804217378</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2898357521322867</v>
+        <v>0.05102754309170245</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.4712852381781211</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.4048707227581912</v>
+        <v>0.8789097844390735</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.7915119562049365</v>
+        <v>-0.4990696663193198</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.54225052195838</v>
+        <v>-0.5448276718187834</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.46160284646258</v>
+        <v>-0.5544726979297275</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9708504454469296</v>
+        <v>-1.381161894841025</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-0.7066611297234656</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-1.732012196121629</v>
       </c>
     </row>
     <row r="8">
@@ -939,64 +1031,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5643589084804479</v>
+        <v>1.484893524923903</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.1807209931165159</v>
+        <v>1.218052467745777</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5242711268027448</v>
+        <v>0.4831286052855917</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5272320480342931</v>
+        <v>-0.5194731682096183</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.48718704957657</v>
+        <v>-1.066922587516322</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1371199336820828</v>
+        <v>-0.6541496855732682</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.747319651154757</v>
+        <v>0.6345558147641175</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3259646341977893</v>
+        <v>0.2082640722265298</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3578199350912059</v>
+        <v>-0.4774190021538274</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.03811803789124067</v>
+        <v>0.1599416731616867</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2439929303487342</v>
+        <v>-0.1634948051709595</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6321674231072113</v>
+        <v>-0.1016597277463064</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.867378235009973</v>
+        <v>0.2575068669856703</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6461233511988076</v>
+        <v>-0.007173136382548172</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-1.010960415169698</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.9880801842802897</v>
+        <v>-1.656903348924384</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9138799633154754</v>
+        <v>1.146296896827158</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6987862543120524</v>
+        <v>0.5278099345296976</v>
       </c>
       <c r="T8" t="n">
-        <v>2.45605356457371</v>
+        <v>0.5497981673824337</v>
       </c>
       <c r="U8" t="n">
-        <v>2.46511472747645</v>
+        <v>2.431712021141904</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.5825971726585487</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.2606452632001062</v>
       </c>
     </row>
     <row r="9">
@@ -1006,64 +1110,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8241758574356827</v>
+        <v>1.484893524923903</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.1807209931165159</v>
+        <v>-0.8289787724109319</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>0.735797089869202</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1480634232923849</v>
+        <v>0.7518977628518172</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6484400313190632</v>
+        <v>-0.3314029074647478</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1934446839228922</v>
+        <v>1.125927933487783</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.762359840768208</v>
+        <v>0.7810376606409953</v>
       </c>
       <c r="J9" t="n">
-        <v>1.165372769412456</v>
+        <v>0.5886158122727817</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8141671830339022</v>
+        <v>-1.03238066496781</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7151897100036683</v>
+        <v>-2.01541890784534</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2776177730749124</v>
+        <v>-0.3102278255792644</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1841637060203911</v>
+        <v>0.1357195734829637</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8019667086241844</v>
+        <v>-0.3725913566155821</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.4311716934867446</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.3174458538428429</v>
+        <v>-0.1228633146442363</v>
       </c>
       <c r="R9" t="n">
-        <v>-1.044644832795887</v>
+        <v>-0.09916821787889364</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1141386738993654</v>
+        <v>-1.725458027785127</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7080537887786632</v>
+        <v>-0.1726682056374236</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2924610556933888</v>
+        <v>-0.5218666520509103</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-0.1564938390772055</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0.1598758239220028</v>
       </c>
     </row>
     <row r="10">
@@ -1073,64 +1189,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.187919585973011</v>
+        <v>1.504520286883804</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.1807209931165159</v>
+        <v>-0.9187608443476297</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.271084424618113</v>
+        <v>1.089532968286256</v>
       </c>
       <c r="E10" t="n">
-        <v>0.04832431727871479</v>
+        <v>-1.250674736732162</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01673828879171205</v>
+        <v>0.8772884208854174</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8950742773004536</v>
+        <v>-0.5401496462099763</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1702941005278848</v>
+        <v>-0.5441086491252703</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.190972523065403</v>
+        <v>-0.5115167810110188</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.606342498882326</v>
+        <v>-0.3780389762944633</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.048286377945056</v>
+        <v>-0.04677604672382018</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7449211304537035</v>
+        <v>-2.136121596101584</v>
       </c>
       <c r="M10" t="n">
-        <v>1.173285411355883</v>
+        <v>0.4517784732773371</v>
       </c>
       <c r="N10" t="n">
-        <v>1.097065528964239</v>
+        <v>-1.579678497365032</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3023583131341103</v>
+        <v>0.4285253002245145</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.818421078653255</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.548429084025844</v>
+        <v>0.9800782666011918</v>
       </c>
       <c r="R10" t="n">
-        <v>1.047689458874012</v>
+        <v>0.5168296132462704</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3074597805018113</v>
+        <v>1.074317339681145</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3348489098639843</v>
+        <v>-0.3732776015806902</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9066821291503365</v>
+        <v>-0.1276817198201864</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.1403156947267206</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-0.333041481757925</v>
       </c>
     </row>
     <row r="11">
@@ -1140,64 +1268,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.361130885276501</v>
+        <v>1.524147048843706</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.1807209931165159</v>
+        <v>-1.349714789643779</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.511524318064218</v>
+        <v>1.25797862467533</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5272320480342931</v>
+        <v>-3.444279442299792</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2187769572542859</v>
+        <v>-0.7428218385612722</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.006893415419860975</v>
+        <v>0.26443729827406</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.07770961614309954</v>
+        <v>1.16993140680632</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.249711118335882</v>
+        <v>0.7551495888482509</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2852869491624603</v>
+        <v>1.058830564255515</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1616256420975665</v>
+        <v>-0.007206318164878419</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.3609223702029415</v>
+        <v>-0.3014407346066679</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3074094685321985</v>
+        <v>1.449556096116227</v>
       </c>
       <c r="N11" t="n">
-        <v>0.930433180592499</v>
+        <v>-0.2303568639359634</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7034499319398777</v>
+        <v>-0.2312901289459963</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0.1811017303954732</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.8927559516728555</v>
+        <v>1.015315930975856</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.4061442851936103</v>
+        <v>-0.7810624069980113</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3051728576954169</v>
+        <v>-0.1937177952884699</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.052499377981391</v>
+        <v>-0.04395551396631577</v>
       </c>
       <c r="U11" t="n">
-        <v>0.01131347791632062</v>
+        <v>-1.090713862888377</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-0.1040024846656663</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-0.382099362020403</v>
       </c>
     </row>
     <row r="12">
@@ -1207,64 +1347,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.561514536992236</v>
+        <v>1.484893524923903</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.1807209931165159</v>
+        <v>-0.3980248271147825</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.5242711268027448</v>
+        <v>-0.6117681612433864</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5272320480342931</v>
+        <v>-0.5194731682096183</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1158495873868519</v>
+        <v>0.0008654324120704823</v>
       </c>
       <c r="G12" t="n">
-        <v>2.102536131546547</v>
+        <v>0.461277366241344</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5471452226988911</v>
+        <v>1.067256635729733</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8295309176602371</v>
+        <v>0.8198697683301115</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.171144583309851</v>
+        <v>2.099905349039205</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1650390483285127</v>
+        <v>0.06204070681327004</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.04478019035086396</v>
+        <v>1.400467169806381</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8217017574040804</v>
+        <v>1.598060433557527</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3403183239294612</v>
+        <v>-0.1418187966939284</v>
       </c>
       <c r="O12" t="n">
-        <v>0.06728415721141058</v>
+        <v>0.06410144643268943</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>0.6790329233482842</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.001745584595744684</v>
+        <v>0.226030485913737</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8432670309052079</v>
+        <v>0.04789623578091549</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2109093889477544</v>
+        <v>0.7511246275027874</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7004332166012445</v>
+        <v>0.1835575788869437</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1738625532809198</v>
+        <v>-0.4331086338015939</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.9037497175520329</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.07153300335089166</v>
       </c>
     </row>
     <row r="13">
@@ -1274,64 +1426,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.007238379221068516</v>
+        <v>1.484893524923903</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.1807209931165159</v>
+        <v>1.164183224583759</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.520022190556569</v>
+        <v>-0.07274206079835104</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.9094911442324418</v>
+        <v>-1.494408592906343</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3292529309504454</v>
+        <v>0.1018600000751169</v>
       </c>
       <c r="G13" t="n">
-        <v>1.026517019822289</v>
+        <v>-1.146123188781076</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.540931544501907</v>
+        <v>-0.8081294890364931</v>
       </c>
       <c r="I13" t="n">
-        <v>1.796595336562549</v>
+        <v>-0.6409571399747399</v>
       </c>
       <c r="J13" t="n">
-        <v>1.455504713127439</v>
+        <v>0.2394054436280701</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5059642079683527</v>
+        <v>-2.139878240151988</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.01948954508357574</v>
+        <v>0.7124618467457867</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5657749433719278</v>
+        <v>0.3353221843416062</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.79243877023971</v>
+        <v>-0.4605845486411909</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.01510156397430543</v>
+        <v>0.2763354222422418</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>0.152310093596645</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.626512556677519</v>
+        <v>-1.339236147531482</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4096692493325728</v>
+        <v>-1.23679083054463</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4961309120294122</v>
+        <v>0.242487201151595</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4118220462759126</v>
+        <v>-0.5955294305686065</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7319918647572632</v>
+        <v>-0.4484545147242835</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-0.08626560062709546</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-0.3986558113639818</v>
       </c>
     </row>
     <row r="14">
@@ -1341,64 +1505,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1832940500127703</v>
+        <v>1.484893524923903</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.1807209931165159</v>
+        <v>-0.04787474656166122</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.7732088927412009</v>
+        <v>0.1125481612296299</v>
       </c>
       <c r="E14" t="n">
-        <v>1.48504750954545</v>
+        <v>-0.7632070243837995</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2938961639694947</v>
+        <v>0.1202226487411253</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.7546456815706843</v>
+        <v>-0.8598564232688086</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.309461408942322</v>
+        <v>0.3155306332047231</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5143957671535022</v>
+        <v>1.25673097983267</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.4787082449724491</v>
+        <v>0.3527032740348687</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.261948563113211</v>
+        <v>-1.617398634610787</v>
       </c>
       <c r="L14" t="n">
-        <v>1.13646859289878</v>
+        <v>-0.0427921169147146</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3525942298574934</v>
+        <v>0.05027510502798565</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.004635792756770377</v>
+        <v>-0.619924359800993</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2551482724449938</v>
+        <v>0.8838422680276248</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>0.3229170892325588</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.6010913172977284</v>
+        <v>0.09978148371800573</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2768920381336487</v>
+        <v>-0.3263765950480657</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6922642892715927</v>
+        <v>0.1689514597247139</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5506118167234306</v>
+        <v>0.3690560587742675</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5250370898062255</v>
+        <v>-0.3041299486184266</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.4108494546597375</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.1837883739979817</v>
       </c>
     </row>
     <row r="15">
@@ -1408,64 +1584,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.8213314859474707</v>
+        <v>1.524147048843706</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.1807209931165159</v>
+        <v>1.487398683555871</v>
       </c>
       <c r="D15" t="n">
-        <v>2.214044298520272</v>
+        <v>-0.8644366458269966</v>
       </c>
       <c r="E15" t="n">
-        <v>1.48504750954545</v>
+        <v>2.161599249706374</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7933244206947293</v>
+        <v>-0.2745742975780566</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4425981153561957</v>
+        <v>-0.602723001149383</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1206933571936881</v>
+        <v>-0.5278692720672388</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.144666068166971</v>
+        <v>-0.6848744046231454</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.083149794378664</v>
+        <v>0.8921619792205392</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.04520859713353993</v>
+        <v>-0.6025715444137858</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1937590527240852</v>
+        <v>0.3141429755001799</v>
       </c>
       <c r="M15" t="n">
-        <v>2.480064541975865</v>
+        <v>0.1330282819203003</v>
       </c>
       <c r="N15" t="n">
-        <v>1.060940060448007</v>
+        <v>0.1189423726789663</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7054521872681059</v>
+        <v>0.4032695015205009</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.085971939448174</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.3230543998713907</v>
+        <v>1.121030690542928</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4938642393407378</v>
+        <v>0.3705603036325728</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3955063085480252</v>
+        <v>0.3818390542067909</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.02352957816750952</v>
+        <v>-0.4831271287422924</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.507333021794896</v>
+        <v>-0.1393425035984754</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.139354975349613</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-0.2977656439440736</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/usa/data_preparation/df_selected_nan.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y15"/>
+  <dimension ref="A1:Y10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,71 +553,71 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8K42rT3c</t>
+          <t>OWICL5dp</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1.484893524923903</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.30482375367543</v>
+        <v>-0.8289787724109319</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.02220836388162897</v>
+        <v>0.735797089869202</v>
       </c>
       <c r="E2" t="n">
-        <v>1.43039768118383</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8253483575158508</v>
+        <v>0.7518977628518172</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.643670027246644</v>
+        <v>-0.3314029074647478</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.3555223349029683</v>
+        <v>1.125927933487783</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6945824315454244</v>
+        <v>0.7810376606409953</v>
       </c>
       <c r="J2" t="n">
-        <v>1.174773927758107</v>
+        <v>0.5886158122727817</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.602275721109812</v>
+        <v>-1.03238066496781</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5096813304752958</v>
+        <v>-2.01541890784534</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4646428307760516</v>
+        <v>-0.3102278255792644</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8803654672242148</v>
+        <v>0.1357195734829637</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1318058064680049</v>
+        <v>-0.3725913566155821</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4267867277166374</v>
+        <v>-0.4311716934867446</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1650245281777734</v>
+        <v>-0.1228633146442363</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1421652408513906</v>
+        <v>-0.09916821787889364</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3772153751680706</v>
+        <v>-1.725458027785127</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7814038786445447</v>
+        <v>-0.1726682056374236</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2542164947997497</v>
+        <v>-0.5218666520509103</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4295164629720869</v>
+        <v>-0.1564938390772055</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
@@ -626,77 +626,77 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.2558942269821199</v>
+        <v>-0.1598758239220028</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ma0gz0nH</t>
+          <t>IktpQolT</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.504520286883804</v>
+        <v>1.484893524923903</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.6314582141501968</v>
+        <v>1.218052467745777</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.07274206079835104</v>
+        <v>0.4831286052855917</v>
       </c>
       <c r="E3" t="n">
-        <v>0.455462256487106</v>
+        <v>-0.5194731682096183</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6986460817203919</v>
+        <v>-1.066922587516322</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4790107056978561</v>
+        <v>-0.6541496855732682</v>
       </c>
       <c r="H3" t="n">
-        <v>1.562295710563276</v>
+        <v>0.6345558147641175</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7066094542368555</v>
+        <v>0.2082640722265298</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.07805852786712188</v>
+        <v>-0.4774190021538274</v>
       </c>
       <c r="K3" t="n">
-        <v>0.08193927720928973</v>
+        <v>0.1599416731616867</v>
       </c>
       <c r="L3" t="n">
         <v>-0.1634948051709595</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1271176141648149</v>
+        <v>-0.1016597277463064</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01044881503960961</v>
+        <v>0.2575068669856703</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2469340055803715</v>
+        <v>-0.007173136382548172</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.06709034043067431</v>
+        <v>-1.010960415169698</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1124320274006492</v>
+        <v>-1.656903348924384</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4628070268623617</v>
+        <v>1.146296896827158</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1239515343624319</v>
+        <v>0.5278099345296976</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.05267552797811428</v>
+        <v>0.5497981673824337</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5862765141982367</v>
+        <v>2.431712021141904</v>
       </c>
       <c r="V3" t="n">
-        <v>0.001229027206602704</v>
+        <v>0.5825971726585487</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -705,77 +705,77 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.02378575712559158</v>
+        <v>0.2606452632001062</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>UT5bq9li</t>
+          <t>4nxtRRYM</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.484893524923903</v>
+        <v>1.504520286883804</v>
       </c>
       <c r="C4" t="n">
-        <v>1.244987089326787</v>
+        <v>-0.6763492501185456</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.8307475145491819</v>
+        <v>-0.005363798242721613</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2757393120354372</v>
+        <v>-0.7632070243837995</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8933955576225415</v>
+        <v>-0.6326459465652218</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.8137497406818768</v>
+        <v>-0.9130564416383449</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.467689054192751</v>
+        <v>0.2605262915565519</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.859545662218913</v>
+        <v>-0.6039741802708198</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7689721554990351</v>
+        <v>1.886537353704573</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1695786525963986</v>
+        <v>-1.557702923422728</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.2048785840016718</v>
+        <v>-0.9773757888416365</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8850289693890135</v>
+        <v>0.8178860508650206</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8418984868537167</v>
+        <v>-0.7076808804217378</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2364883488219674</v>
+        <v>0.05102754309170245</v>
       </c>
       <c r="P4" t="n">
-        <v>1.03093950304962</v>
+        <v>0.4712852381781211</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9655289006763714</v>
+        <v>0.8789097844390735</v>
       </c>
       <c r="R4" t="n">
-        <v>0.24420900486391</v>
+        <v>-0.4990696663193198</v>
       </c>
       <c r="S4" t="n">
-        <v>1.164842762821797</v>
+        <v>-0.5448276718187834</v>
       </c>
       <c r="T4" t="n">
-        <v>1.707802816006683</v>
+        <v>-0.5544726979297275</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2423081192723966</v>
+        <v>-1.381161894841025</v>
       </c>
       <c r="V4" t="n">
-        <v>1.104709810019914</v>
+        <v>-0.7066611297234656</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -784,77 +784,77 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01165303335159579</v>
+        <v>-1.732012196121629</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Sx1kytXA</t>
+          <t>z7pPU9Zc</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.484893524923903</v>
+        <v>1.504520286883804</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6075343785762326</v>
+        <v>-0.9187608443476297</v>
       </c>
       <c r="D5" t="n">
-        <v>1.072688402647349</v>
+        <v>1.645403634370199</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.03200545586125614</v>
+        <v>-1.250674736732162</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.191024246147718</v>
+        <v>0.8772884208854174</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.5798300052032</v>
+        <v>-0.5401496462099763</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6525457798030938</v>
+        <v>-0.5441086491252703</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1121008162086799</v>
+        <v>-0.5115167810110188</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4573743660858196</v>
+        <v>-0.3780389762944633</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.466169499601038</v>
+        <v>-0.04677604672382018</v>
       </c>
       <c r="L5" t="n">
-        <v>1.09871044916577</v>
+        <v>-2.136121596101584</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2915105615694395</v>
+        <v>0.4517784732773371</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6619135102781571</v>
+        <v>-1.579678497365032</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4185399277592944</v>
+        <v>0.4285253002245145</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1923036253187315</v>
+        <v>0.818421078653255</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.5953641212135954</v>
+        <v>0.9800782666011918</v>
       </c>
       <c r="R5" t="n">
-        <v>-1.429109170801369</v>
+        <v>0.5168296132462704</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1506422359235565</v>
+        <v>1.074317339681145</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1530878105382049</v>
+        <v>-0.3732776015806902</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6053799158050117</v>
+        <v>-0.1276817198201864</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2919870107058845</v>
+        <v>0.1403156947267206</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -863,77 +863,77 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.7641180574321723</v>
+        <v>-0.333041481757925</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2NHGKPBj</t>
+          <t>APxxS7JG</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.504520286883804</v>
+        <v>1.484893524923903</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.1825478544667079</v>
+        <v>-0.3980248271147825</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4831286052855917</v>
+        <v>1.645403634370199</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.494408592906343</v>
+        <v>-0.5194731682096183</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1331819028497911</v>
+        <v>0.0008654324120704823</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1438505899697769</v>
+        <v>0.461277366241344</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007506319974963347</v>
+        <v>1.067256635729733</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1121008162086799</v>
+        <v>0.8198697683301115</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2962574966810276</v>
+        <v>2.099905349039205</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5564068610950201</v>
+        <v>0.06204070681327004</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.1421131861084248</v>
+        <v>1.400467169806381</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1662047828380386</v>
+        <v>1.598060433557527</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4991017181280399</v>
+        <v>-0.1418187966939284</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2799411343178443</v>
+        <v>0.06410144643268943</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7938263964356514</v>
+        <v>0.6790329233482842</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.08088349147412106</v>
+        <v>0.226030485913737</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.3210273573789438</v>
+        <v>0.04789623578091549</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.538829472400337</v>
+        <v>0.7511246275027874</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3695027037400853</v>
+        <v>0.1835575788869437</v>
       </c>
       <c r="U6" t="n">
-        <v>0.266521634274559</v>
+        <v>-0.4331086338015939</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.1791511756188</v>
+        <v>0.9037497175520329</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -942,77 +942,77 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.1618181227520909</v>
+        <v>0.07153300335089166</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4nxtRRYM</t>
+          <t>EcqTTTl4</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.504520286883804</v>
+        <v>1.524147048843706</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.6763492501185456</v>
+        <v>-1.349714789643779</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.005363798242721613</v>
+        <v>1.645403634370199</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7632070243837995</v>
+        <v>-3.444279442299792</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6326459465652218</v>
+        <v>-0.7428218385612722</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9130564416383449</v>
+        <v>0.26443729827406</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2605262915565519</v>
+        <v>1.16993140680632</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6039741802708198</v>
+        <v>0.7551495888482509</v>
       </c>
       <c r="J7" t="n">
-        <v>1.886537353704573</v>
+        <v>1.058830564255515</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.557702923422728</v>
+        <v>-0.007206318164878419</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.9773757888416365</v>
+        <v>-0.3014407346066679</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8178860508650206</v>
+        <v>1.449556096116227</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7076808804217378</v>
+        <v>-0.2303568639359634</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05102754309170245</v>
+        <v>-0.2312901289459963</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4712852381781211</v>
+        <v>-0.1811017303954732</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8789097844390735</v>
+        <v>1.015315930975856</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.4990696663193198</v>
+        <v>-0.7810624069980113</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5448276718187834</v>
+        <v>-0.1937177952884699</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5544726979297275</v>
+        <v>-0.04395551396631577</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.381161894841025</v>
+        <v>-1.090713862888377</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.7066611297234656</v>
+        <v>-0.1040024846656663</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -1021,77 +1021,77 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>-1.732012196121629</v>
+        <v>-0.382099362020403</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>IktpQolT</t>
+          <t>WYwYSm4A</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1.484893524923903</v>
       </c>
       <c r="C8" t="n">
-        <v>1.218052467745777</v>
+        <v>-0.04787474656166122</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4831286052855917</v>
+        <v>1.645403634370199</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5194731682096183</v>
+        <v>-0.7632070243837995</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.066922587516322</v>
+        <v>0.1202226487411253</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6541496855732682</v>
+        <v>-0.8598564232688086</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6345558147641175</v>
+        <v>0.3155306332047231</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2082640722265298</v>
+        <v>1.25673097983267</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4774190021538274</v>
+        <v>0.3527032740348687</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1599416731616867</v>
+        <v>-1.617398634610787</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1634948051709595</v>
+        <v>-0.0427921169147146</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1016597277463064</v>
+        <v>0.05027510502798565</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2575068669856703</v>
+        <v>-0.619924359800993</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.007173136382548172</v>
+        <v>0.8838422680276248</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.010960415169698</v>
+        <v>0.3229170892325588</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.656903348924384</v>
+        <v>0.09978148371800573</v>
       </c>
       <c r="R8" t="n">
-        <v>1.146296896827158</v>
+        <v>-0.3263765950480657</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5278099345296976</v>
+        <v>0.1689514597247139</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5497981673824337</v>
+        <v>0.3690560587742675</v>
       </c>
       <c r="U8" t="n">
-        <v>2.431712021141904</v>
+        <v>-0.3041299486184266</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5825971726585487</v>
+        <v>0.4108494546597375</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1100,77 +1100,77 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.2606452632001062</v>
+        <v>0.1837883739979817</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>OWICL5dp</t>
+          <t>ln2oxMH4</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.484893524923903</v>
+        <v>1.524147048843706</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.8289787724109319</v>
+        <v>1.487398683555871</v>
       </c>
       <c r="D9" t="n">
-        <v>0.735797089869202</v>
+        <v>1.645403634370199</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>2.161599249706374</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7518977628518172</v>
+        <v>-0.2745742975780566</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3314029074647478</v>
+        <v>-0.602723001149383</v>
       </c>
       <c r="H9" t="n">
-        <v>1.125927933487783</v>
+        <v>-0.5278692720672388</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7810376606409953</v>
+        <v>-0.6848744046231454</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5886158122727817</v>
+        <v>0.8921619792205392</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.03238066496781</v>
+        <v>-0.6025715444137858</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.01541890784534</v>
+        <v>0.3141429755001799</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3102278255792644</v>
+        <v>0.1330282819203003</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1357195734829637</v>
+        <v>0.1189423726789663</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3725913566155821</v>
+        <v>0.4032695015205009</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4311716934867446</v>
+        <v>2.085971939448174</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1228633146442363</v>
+        <v>1.121030690542928</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.09916821787889364</v>
+        <v>0.3705603036325728</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.725458027785127</v>
+        <v>0.3818390542067909</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1726682056374236</v>
+        <v>-0.4831271287422924</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5218666520509103</v>
+        <v>-0.1393425035984754</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1564938390772055</v>
+        <v>1.139354975349613</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
@@ -1179,77 +1179,77 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.1598758239220028</v>
+        <v>-0.2977656439440736</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>z7pPU9Zc</t>
+          <t>tpoLVkKi</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.504520286883804</v>
+        <v>1.484893524923903</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.9187608443476297</v>
+        <v>1.164183224583759</v>
       </c>
       <c r="D10" t="n">
-        <v>1.089532968286256</v>
+        <v>1.645403634370199</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.250674736732162</v>
+        <v>-1.494408592906343</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8772884208854174</v>
+        <v>0.1018600000751169</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5401496462099763</v>
+        <v>-1.146123188781076</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5441086491252703</v>
+        <v>-0.8081294890364931</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5115167810110188</v>
+        <v>-0.6409571399747399</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3780389762944633</v>
+        <v>0.2394054436280701</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.04677604672382018</v>
+        <v>-2.139878240151988</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.136121596101584</v>
+        <v>0.7124618467457867</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4517784732773371</v>
+        <v>0.3353221843416062</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.579678497365032</v>
+        <v>-0.4605845486411909</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4285253002245145</v>
+        <v>0.2763354222422418</v>
       </c>
       <c r="P10" t="n">
-        <v>0.818421078653255</v>
+        <v>0.152310093596645</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.9800782666011918</v>
+        <v>-1.339236147531482</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5168296132462704</v>
+        <v>-1.23679083054463</v>
       </c>
       <c r="S10" t="n">
-        <v>1.074317339681145</v>
+        <v>0.242487201151595</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3732776015806902</v>
+        <v>-0.5955294305686065</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1276817198201864</v>
+        <v>-0.4484545147242835</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1403156947267206</v>
+        <v>-0.08626560062709546</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -1258,402 +1258,7 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.333041481757925</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>EcqTTTl4</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1.524147048843706</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-1.349714789643779</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1.25797862467533</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-3.444279442299792</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-0.7428218385612722</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.26443729827406</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.16993140680632</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.7551495888482509</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.058830564255515</v>
-      </c>
-      <c r="K11" t="n">
-        <v>-0.007206318164878419</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-0.3014407346066679</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.449556096116227</v>
-      </c>
-      <c r="N11" t="n">
-        <v>-0.2303568639359634</v>
-      </c>
-      <c r="O11" t="n">
-        <v>-0.2312901289459963</v>
-      </c>
-      <c r="P11" t="n">
-        <v>-0.1811017303954732</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.015315930975856</v>
-      </c>
-      <c r="R11" t="n">
-        <v>-0.7810624069980113</v>
-      </c>
-      <c r="S11" t="n">
-        <v>-0.1937177952884699</v>
-      </c>
-      <c r="T11" t="n">
-        <v>-0.04395551396631577</v>
-      </c>
-      <c r="U11" t="n">
-        <v>-1.090713862888377</v>
-      </c>
-      <c r="V11" t="n">
-        <v>-0.1040024846656663</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>-0.382099362020403</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>APxxS7JG</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1.484893524923903</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-0.3980248271147825</v>
-      </c>
-      <c r="D12" t="n">
-        <v>-0.6117681612433864</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-0.5194731682096183</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.0008654324120704823</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.461277366241344</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.067256635729733</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.8198697683301115</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2.099905349039205</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.06204070681327004</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.400467169806381</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.598060433557527</v>
-      </c>
-      <c r="N12" t="n">
-        <v>-0.1418187966939284</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.06410144643268943</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0.6790329233482842</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.226030485913737</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.04789623578091549</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.7511246275027874</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0.1835575788869437</v>
-      </c>
-      <c r="U12" t="n">
-        <v>-0.4331086338015939</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0.9037497175520329</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0.07153300335089166</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>tpoLVkKi</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1.484893524923903</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1.164183224583759</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.07274206079835104</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-1.494408592906343</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.1018600000751169</v>
-      </c>
-      <c r="G13" t="n">
-        <v>-1.146123188781076</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-0.8081294890364931</v>
-      </c>
-      <c r="I13" t="n">
-        <v>-0.6409571399747399</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.2394054436280701</v>
-      </c>
-      <c r="K13" t="n">
-        <v>-2.139878240151988</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.7124618467457867</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.3353221843416062</v>
-      </c>
-      <c r="N13" t="n">
-        <v>-0.4605845486411909</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.2763354222422418</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0.152310093596645</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>-1.339236147531482</v>
-      </c>
-      <c r="R13" t="n">
-        <v>-1.23679083054463</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.242487201151595</v>
-      </c>
-      <c r="T13" t="n">
-        <v>-0.5955294305686065</v>
-      </c>
-      <c r="U13" t="n">
-        <v>-0.4484545147242835</v>
-      </c>
-      <c r="V13" t="n">
-        <v>-0.08626560062709546</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
         <v>-0.3986558113639818</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>WYwYSm4A</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1.484893524923903</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-0.04787474656166122</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.1125481612296299</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.7632070243837995</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.1202226487411253</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-0.8598564232688086</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.3155306332047231</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1.25673097983267</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.3527032740348687</v>
-      </c>
-      <c r="K14" t="n">
-        <v>-1.617398634610787</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-0.0427921169147146</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.05027510502798565</v>
-      </c>
-      <c r="N14" t="n">
-        <v>-0.619924359800993</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.8838422680276248</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0.3229170892325588</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.09978148371800573</v>
-      </c>
-      <c r="R14" t="n">
-        <v>-0.3263765950480657</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.1689514597247139</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.3690560587742675</v>
-      </c>
-      <c r="U14" t="n">
-        <v>-0.3041299486184266</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.4108494546597375</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.1837883739979817</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>ln2oxMH4</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1.524147048843706</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1.487398683555871</v>
-      </c>
-      <c r="D15" t="n">
-        <v>-0.8644366458269966</v>
-      </c>
-      <c r="E15" t="n">
-        <v>2.161599249706374</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-0.2745742975780566</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-0.602723001149383</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-0.5278692720672388</v>
-      </c>
-      <c r="I15" t="n">
-        <v>-0.6848744046231454</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.8921619792205392</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-0.6025715444137858</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.3141429755001799</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.1330282819203003</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.1189423726789663</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.4032695015205009</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.085971939448174</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.121030690542928</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.3705603036325728</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.3818390542067909</v>
-      </c>
-      <c r="T15" t="n">
-        <v>-0.4831271287422924</v>
-      </c>
-      <c r="U15" t="n">
-        <v>-0.1393425035984754</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.139354975349613</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>-0.2977656439440736</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/usa/data_preparation/df_selected_nan.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y10"/>
+  <dimension ref="A1:Y4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,71 +553,71 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OWICL5dp</t>
+          <t>UT5bq9li</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1.484893524923903</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.8289787724109319</v>
+        <v>1.244987089326787</v>
       </c>
       <c r="D2" t="n">
-        <v>0.735797089869202</v>
+        <v>-0.8307475145491819</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-0.2757393120354372</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7518977628518172</v>
+        <v>-0.8933955576225415</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.3314029074647478</v>
+        <v>-0.8137497406818768</v>
       </c>
       <c r="H2" t="n">
-        <v>1.125927933487783</v>
+        <v>-2.467689054192751</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7810376606409953</v>
+        <v>-1.859545662218913</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5886158122727817</v>
+        <v>0.7689721554990351</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.03238066496781</v>
+        <v>-0.1695786525963986</v>
       </c>
       <c r="L2" t="n">
-        <v>-2.01541890784534</v>
+        <v>-0.2048785840016718</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3102278255792644</v>
+        <v>0.8850289693890135</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1357195734829637</v>
+        <v>-0.8418984868537167</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3725913566155821</v>
+        <v>0.2364883488219674</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4311716934867446</v>
+        <v>1.03093950304962</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1228633146442363</v>
+        <v>0.9655289006763714</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.09916821787889364</v>
+        <v>0.24420900486391</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.725458027785127</v>
+        <v>1.164842762821797</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1726682056374236</v>
+        <v>1.707802816006683</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5218666520509103</v>
+        <v>-0.2423081192723966</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1564938390772055</v>
+        <v>1.104709810019914</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
@@ -626,77 +626,77 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.1598758239220028</v>
+        <v>0.01165303335159579</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>IktpQolT</t>
+          <t>8K42rT3c</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1.484893524923903</v>
       </c>
       <c r="C3" t="n">
-        <v>1.218052467745777</v>
+        <v>-1.30482375367543</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4831286052855917</v>
+        <v>-0.02220836388162897</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5194731682096183</v>
+        <v>1.43039768118383</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.066922587516322</v>
+        <v>0.8253483575158508</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.6541496855732682</v>
+        <v>-1.643670027246644</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6345558147641175</v>
+        <v>-0.3555223349029683</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2082640722265298</v>
+        <v>-0.6945824315454244</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.4774190021538274</v>
+        <v>1.174773927758107</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1599416731616867</v>
+        <v>-1.602275721109812</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.1634948051709595</v>
+        <v>0.5096813304752958</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1016597277463064</v>
+        <v>0.4646428307760516</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2575068669856703</v>
+        <v>-0.8803654672242148</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.007173136382548172</v>
+        <v>0.1318058064680049</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.010960415169698</v>
+        <v>0.4267867277166374</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.656903348924384</v>
+        <v>0.1650245281777734</v>
       </c>
       <c r="R3" t="n">
-        <v>1.146296896827158</v>
+        <v>0.1421652408513906</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5278099345296976</v>
+        <v>-0.3772153751680706</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5497981673824337</v>
+        <v>0.7814038786445447</v>
       </c>
       <c r="U3" t="n">
-        <v>2.431712021141904</v>
+        <v>-0.2542164947997497</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5825971726585487</v>
+        <v>0.4295164629720869</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -705,77 +705,77 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2606452632001062</v>
+        <v>0.2558942269821199</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>4nxtRRYM</t>
+          <t>Ma0gz0nH</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1.504520286883804</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.6763492501185456</v>
+        <v>-0.6314582141501968</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.005363798242721613</v>
+        <v>-0.07274206079835104</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7632070243837995</v>
+        <v>0.455462256487106</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6326459465652218</v>
+        <v>0.6986460817203919</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.9130564416383449</v>
+        <v>0.4790107056978561</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2605262915565519</v>
+        <v>1.562295710563276</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6039741802708198</v>
+        <v>0.7066094542368555</v>
       </c>
       <c r="J4" t="n">
-        <v>1.886537353704573</v>
+        <v>-0.07805852786712188</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.557702923422728</v>
+        <v>0.08193927720928973</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.9773757888416365</v>
+        <v>-0.1634948051709595</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8178860508650206</v>
+        <v>-0.1271176141648149</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7076808804217378</v>
+        <v>0.01044881503960961</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05102754309170245</v>
+        <v>0.2469340055803715</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4712852381781211</v>
+        <v>-0.06709034043067431</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.8789097844390735</v>
+        <v>-0.1124320274006492</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.4990696663193198</v>
+        <v>0.4628070268623617</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5448276718187834</v>
+        <v>-0.1239515343624319</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5544726979297275</v>
+        <v>-0.05267552797811428</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.381161894841025</v>
+        <v>0.5862765141982367</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.7066611297234656</v>
+        <v>0.001229027206602704</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -784,481 +784,7 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1.732012196121629</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>z7pPU9Zc</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1.504520286883804</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-0.9187608443476297</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1.645403634370199</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-1.250674736732162</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.8772884208854174</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-0.5401496462099763</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-0.5441086491252703</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-0.5115167810110188</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-0.3780389762944633</v>
-      </c>
-      <c r="K5" t="n">
-        <v>-0.04677604672382018</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-2.136121596101584</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.4517784732773371</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-1.579678497365032</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.4285253002245145</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.818421078653255</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.9800782666011918</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.5168296132462704</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.074317339681145</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-0.3732776015806902</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-0.1276817198201864</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.1403156947267206</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-0.333041481757925</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>APxxS7JG</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1.484893524923903</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-0.3980248271147825</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1.645403634370199</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-0.5194731682096183</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.0008654324120704823</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.461277366241344</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.067256635729733</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.8198697683301115</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2.099905349039205</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.06204070681327004</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.400467169806381</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.598060433557527</v>
-      </c>
-      <c r="N6" t="n">
-        <v>-0.1418187966939284</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.06410144643268943</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.6790329233482842</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.226030485913737</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.04789623578091549</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.7511246275027874</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.1835575788869437</v>
-      </c>
-      <c r="U6" t="n">
-        <v>-0.4331086338015939</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.9037497175520329</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.07153300335089166</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>EcqTTTl4</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1.524147048843706</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-1.349714789643779</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1.645403634370199</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-3.444279442299792</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-0.7428218385612722</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.26443729827406</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.16993140680632</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.7551495888482509</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.058830564255515</v>
-      </c>
-      <c r="K7" t="n">
-        <v>-0.007206318164878419</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-0.3014407346066679</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.449556096116227</v>
-      </c>
-      <c r="N7" t="n">
-        <v>-0.2303568639359634</v>
-      </c>
-      <c r="O7" t="n">
-        <v>-0.2312901289459963</v>
-      </c>
-      <c r="P7" t="n">
-        <v>-0.1811017303954732</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.015315930975856</v>
-      </c>
-      <c r="R7" t="n">
-        <v>-0.7810624069980113</v>
-      </c>
-      <c r="S7" t="n">
-        <v>-0.1937177952884699</v>
-      </c>
-      <c r="T7" t="n">
-        <v>-0.04395551396631577</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-1.090713862888377</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-0.1040024846656663</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>-0.382099362020403</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>WYwYSm4A</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1.484893524923903</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-0.04787474656166122</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1.645403634370199</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-0.7632070243837995</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.1202226487411253</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-0.8598564232688086</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.3155306332047231</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.25673097983267</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.3527032740348687</v>
-      </c>
-      <c r="K8" t="n">
-        <v>-1.617398634610787</v>
-      </c>
-      <c r="L8" t="n">
-        <v>-0.0427921169147146</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.05027510502798565</v>
-      </c>
-      <c r="N8" t="n">
-        <v>-0.619924359800993</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.8838422680276248</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.3229170892325588</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.09978148371800573</v>
-      </c>
-      <c r="R8" t="n">
-        <v>-0.3263765950480657</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.1689514597247139</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.3690560587742675</v>
-      </c>
-      <c r="U8" t="n">
-        <v>-0.3041299486184266</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0.4108494546597375</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.1837883739979817</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>ln2oxMH4</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1.524147048843706</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.487398683555871</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.645403634370199</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.161599249706374</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-0.2745742975780566</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-0.602723001149383</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-0.5278692720672388</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-0.6848744046231454</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.8921619792205392</v>
-      </c>
-      <c r="K9" t="n">
-        <v>-0.6025715444137858</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.3141429755001799</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.1330282819203003</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.1189423726789663</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.4032695015205009</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.085971939448174</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.121030690542928</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.3705603036325728</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.3818390542067909</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-0.4831271287422924</v>
-      </c>
-      <c r="U9" t="n">
-        <v>-0.1393425035984754</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.139354975349613</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>-0.2977656439440736</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>tpoLVkKi</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1.484893524923903</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1.164183224583759</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1.645403634370199</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-1.494408592906343</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.1018600000751169</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-1.146123188781076</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-0.8081294890364931</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-0.6409571399747399</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.2394054436280701</v>
-      </c>
-      <c r="K10" t="n">
-        <v>-2.139878240151988</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.7124618467457867</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.3353221843416062</v>
-      </c>
-      <c r="N10" t="n">
-        <v>-0.4605845486411909</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.2763354222422418</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.152310093596645</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-1.339236147531482</v>
-      </c>
-      <c r="R10" t="n">
-        <v>-1.23679083054463</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.242487201151595</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-0.5955294305686065</v>
-      </c>
-      <c r="U10" t="n">
-        <v>-0.4484545147242835</v>
-      </c>
-      <c r="V10" t="n">
-        <v>-0.08626560062709546</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>-0.3986558113639818</v>
+        <v>-0.02378575712559158</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/usa/data_preparation/df_selected_nan.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_selected_nan.xlsx
@@ -563,7 +563,7 @@
         <v>1.244987089326787</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.8307475145491819</v>
+        <v>1.662248200009106</v>
       </c>
       <c r="E2" t="n">
         <v>-0.2757393120354372</v>
@@ -642,7 +642,7 @@
         <v>-1.30482375367543</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.02220836388162897</v>
+        <v>1.662248200009106</v>
       </c>
       <c r="E3" t="n">
         <v>1.43039768118383</v>
@@ -721,7 +721,7 @@
         <v>-0.6314582141501968</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.07274206079835104</v>
+        <v>1.662248200009106</v>
       </c>
       <c r="E4" t="n">
         <v>0.455462256487106</v>

--- a/p6_deployment/data/usa/data_preparation/df_selected_nan.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y4"/>
+  <dimension ref="A1:Y42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,71 +553,71 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>UT5bq9li</t>
+          <t>QgE37zwQ</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1.484893524923903</v>
       </c>
       <c r="C2" t="n">
-        <v>1.244987089326787</v>
+        <v>-0.04787474656166122</v>
       </c>
       <c r="D2" t="n">
-        <v>1.662248200009106</v>
+        <v>1.645403634370199</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2757393120354372</v>
+        <v>-1.250674736732162</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8933955576225415</v>
+        <v>0.01201418338786115</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.8137497406818768</v>
+        <v>0.1940106072896258</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.467689054192751</v>
+        <v>0.5591212890751966</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.859545662218913</v>
+        <v>0.7389695439777859</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7689721554990351</v>
+        <v>0.8041692479908935</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1695786525963986</v>
+        <v>0.07909662429557228</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.2048785840016718</v>
+        <v>1.424607707457631</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8850289693890135</v>
+        <v>0.3070205978444341</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8418984868537167</v>
+        <v>-0.6788753049508075</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2364883488219674</v>
+        <v>-0.05042895422796725</v>
       </c>
       <c r="P2" t="n">
-        <v>1.03093950304962</v>
+        <v>0.2097293680121177</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9655289006763714</v>
+        <v>0.1594070511659614</v>
       </c>
       <c r="R2" t="n">
-        <v>0.24420900486391</v>
+        <v>-0.04553484004413343</v>
       </c>
       <c r="S2" t="n">
-        <v>1.164842762821797</v>
+        <v>-0.188454666572953</v>
       </c>
       <c r="T2" t="n">
-        <v>1.707802816006683</v>
+        <v>-0.6427453531400609</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2423081192723966</v>
+        <v>-0.2247647576147545</v>
       </c>
       <c r="V2" t="n">
-        <v>1.104709810019914</v>
+        <v>0.2243997622442526</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
@@ -626,77 +626,77 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01165303335159579</v>
+        <v>-0.8417760123575475</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8K42rT3c</t>
+          <t>v1fv1YFg</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1.484893524923903</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.30482375367543</v>
+        <v>-1.179128852964053</v>
       </c>
       <c r="D3" t="n">
-        <v>1.662248200009106</v>
+        <v>1.679092765648014</v>
       </c>
       <c r="E3" t="n">
-        <v>1.43039768118383</v>
+        <v>-0.5194731682096183</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8253483575158508</v>
+        <v>-0.5014841703794464</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.643670027246644</v>
+        <v>-0.4671896210174687</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3555223349029683</v>
+        <v>1.077733653186527</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6945824315454244</v>
+        <v>0.3830085568275531</v>
       </c>
       <c r="J3" t="n">
-        <v>1.174773927758107</v>
+        <v>0.3590295488291566</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.602275721109812</v>
+        <v>-1.102878457227994</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5096813304752958</v>
+        <v>0.2055105560695598</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4646428307760516</v>
+        <v>0.8100395450924134</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8803654672242148</v>
+        <v>0.0151291628060618</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1318058064680049</v>
+        <v>0.1083595893187165</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4267867277166374</v>
+        <v>0.6757198205277618</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1650245281777734</v>
+        <v>0.6740666668764698</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1421652408513906</v>
+        <v>0.2736385219810167</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3772153751680706</v>
+        <v>-0.09566989232157945</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7814038786445447</v>
+        <v>-0.6551492233386623</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2542164947997497</v>
+        <v>-0.3873550483860498</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4295164629720869</v>
+        <v>0.455639336909191</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -705,86 +705,3088 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2558942269821199</v>
+        <v>-0.3082167774512894</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Ma0gz0nH</t>
+          <t>dx5Z1E0m</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1.504520286883804</v>
       </c>
       <c r="C4" t="n">
+        <v>1.424551233200182</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.679092765648014</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.2117284003129249</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.617434323901744</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.2168106151622842</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.1480773892584359</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-0.8304948084573316</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.3745576778696824</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.332706559244809</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.02445652368519323</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.370564427264471</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.8058846362997141</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.2885878753051554</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.395260641433717</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.2041184048774129</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.2772391213058484</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.520675756154807</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.2641516477838567</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-0.1906901986236039</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.850381170712959</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.07320536217622386</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>rZ0V2fos</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.484893524923903</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-1.268910924900751</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.679092765648014</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.7632070243837995</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.330737299519294</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-1.356389928051148</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.6902630426475541</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0.1832930136387264</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-1.219663570290956</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0.125574385492058</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.6883213090945379</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.2299247290451204</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.11317825960672</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-0.4526187736534731</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.1896588265317713</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.1361268064572548</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-1.405197783776784</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0.2682357266382522</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.9776498485022469</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0.7395355543214437</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-0.8033126516712056</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-0.02378575712559158</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>n3Fa8GNJ</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.484893524923903</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-1.30482375367543</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.662248200009106</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.03200545586125614</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.023664963108742</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.4307096084212159</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.360613124519981</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2797504522905847</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.377674813887642</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-1.544967838369276</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-0.177665614285718</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.1098573923904526</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-1.001095811962857</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0.3435901663625291</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.6145666489563596</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.5524098355440039</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-0.1193482605061787</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0.8138475381883673</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.01438673918085848</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.02258513731170469</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-0.1317075353121376</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.09162579869722887</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>AoWGqXpJ</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.484893524923903</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.182139638971098</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.662248200009106</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-1.250674736732162</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.3709782030746008</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.534144403360327</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.4438740970504566</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.7163174811591347</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.002457696787455544</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.4639918288128664</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-0.484908820756159</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-0.7748492987492093</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.1035104761638596</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.353288163135192</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-1.66943485418357</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-1.509531217527631</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-0.937297308459351</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-1.736663896125332</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-1.344294573119496</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.06833816603476442</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-2.05065982313327</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.3689184085281531</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>WfXCpDVC</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.484893524923903</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.164183224583759</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.645403634370199</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-1.00694088055798</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4003842026739403</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.6222296745515463</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.4309568605918891</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-0.3299640697372283</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.5867754414235338</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-1.266615265058098</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.753434575442286</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.04666405730904857</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-0.3425869587552782</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.1397550920454809</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.05014730881731155</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.6290645126754415</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-0.795421749610205</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0.9034490317676269</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.5571617347701712</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0.5389735864748663</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-0.3402200857701937</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.05251279435785438</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>xYX8ogG6</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.484893524923903</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.8289787724109319</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.679092765648014</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-1.250674736732162</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.377299730065244</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.443544026784832</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.9939175135321708</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.5739330862990414</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0.2270135434780907</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-0.7538006794235352</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-1.537436262350611</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.1107601543201866</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.1716349902174137</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-0.5445521362306232</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0.2028905762928245</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.009721577320042538</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-0.6102987458896323</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-2.047000338609024</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-1.080051724277151</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0.2339923616963637</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-0.9811578271125874</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0.1670384590165507</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>QcU4nZ00</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.484893524923903</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.218052467745777</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.679092765648014</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3589370813992356</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.1813439362492601</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.098687688100117</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.06772126456397556</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-1.13167083906131</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.239467543674889</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.6187163723087961</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-0.4181229222146814</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.7007107909756112</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.006023109697703621</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-1.511339875391514</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-1.52889740787933</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.020924885233699</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.09032890851342165</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.4217725071183159</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.62046278160942</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.3052250490835297</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.794415941791945</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>rRCPxg8F</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.524147048843706</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.487398683555871</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.645403634370199</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.6991961126612871</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.770893602039101</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.7977897351710163</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.9731425139810074</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0.4907138661775638</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.5194868822479222</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.5349164050673192</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-1.786083800158476</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0.4119390029960017</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.1939103480764645</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.09203378029088639</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.276783756965614</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.4733281974731596</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.433916972199022</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.4861810048872638</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-1.101455395033381</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.4601304060763952</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.9610161576444708</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-0.6330753680019733</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>xlCTyDNL</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.504520286883804</v>
+      </c>
+      <c r="C12" t="n">
         <v>-0.6314582141501968</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D12" t="n">
         <v>1.662248200009106</v>
       </c>
-      <c r="E4" t="n">
-        <v>0.455462256487106</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.6986460817203919</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.4790107056978561</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.562295710563276</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.7066094542368555</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-0.07805852786712188</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.08193927720928973</v>
-      </c>
-      <c r="L4" t="n">
-        <v>-0.1634948051709595</v>
-      </c>
-      <c r="M4" t="n">
-        <v>-0.1271176141648149</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="E12" t="n">
+        <v>-1.00694088055798</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.28191935704446</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.686490777339048</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.12959488959766</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.6551274932853759</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-0.2745181160242918</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.6470586764562472</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.7168510354096503</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0.1610840317710696</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-0.2969787876881816</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.2178602840646803</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0.3187208626222855</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.8155905980441446</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.04071514225304699</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0.9375125696373243</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.05364335943845314</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0.5807182171709351</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-1.283149379979582</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.705373840256308</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>4rtdleWm</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.524147048843706</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.4878068990514803</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.645403634370199</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-1.00694088055798</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.4369783382297715</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.3548773295022712</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.608887121994971</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.9493101272938326</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-0.3719427478563306</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.3956264122951818</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0.4945650358166593</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-0.4272859558014853</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-0.006517210562120079</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.457953154848467</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.7518109906209504</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0.4206467758550574</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.308076699189834</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.8929409144317942</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.5429563500903469</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.066894655576281</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.9141820429348005</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.9633902342280749</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>z9yhkyHs</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.484893524923903</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-1.448475068774147</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.611714503092384</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-1.250674736732162</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.09267867574211304</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.4346773570565757</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3338654137541139</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.415295419563228</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.7593102085404858</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0.3478698433447344</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-0.1952223689411715</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-0.339718048617254</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-0.5307208614356632</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-1.214561449406334</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-1.614792390473132</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-2.370581754627004</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-1.892432614981796</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-1.632528828396543</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-3.707946856014272</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-0.001526147137739669</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-1.600091338291399</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-1.505712026467972</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>rZv0mFof</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.524147048843706</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.415573026006512</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.645403634370199</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.2757393120354372</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.285486486735202</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.5765440727086727</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.2605262915565516</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.467071563148717</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.210201066606121</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.3525598345951563</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.8573050726532805</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.6403428713505992</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.4971811641856564</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-0.1376343812396914</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-0.3937556891845762</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-0.5291239526729256</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.4608986721882596</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0.08127030164793569</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-0.3201514657945303</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.829758973463664</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.2374452554548077</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.229194256369561</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>YakQgH8Q</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.484893524923903</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.182139638971098</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.662248200009106</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.2757393120354372</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.2900771489017037</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.534144403360327</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.7739001469394852</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-0.3127333726024475</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-0.8308852283874237</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.89668889732628</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-0.3617920787347896</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.8207824120562524</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-0.4164096196133426</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.01120137006474184</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0.4184300126680936</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-0.7892586252358016</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-0.5749087711336168</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0.3492886001293863</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-1.48434328300594</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0.42553870942538</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-0.6387811867192289</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.07694261852492093</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>jy0LfcgK</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.504520286883804</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.9187608443476297</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.645403634370199</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-1.250674736732162</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-0.009234024354233988</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.462629619442937</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.2565145199362598</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-0.7237065123122618</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-0.2962574966810276</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.410663660151534</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-0.9242666060088899</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.090256848081955</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-1.373022684089857</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-0.0605582340315805</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.4224590050511285</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.8304264649356002</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-0.5758526693233976</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.1795549670370419</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-0.3644556653271971</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-1.068224266750553</v>
+      </c>
+      <c r="V17" t="n">
+        <v>-0.6336076385418715</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-0.3368759148642129</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>xYeHewvE</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.504520286883804</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.2124932620547623</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.662248200009106</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-1.00694088055798</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-1.418483842885538</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.1303713228986509</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.1905207658225153</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-0.309791546262363</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.05223136293755799</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0.09859502511096117</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.463013108266435</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-0.00957801091340171</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-0.7157683654588208</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.006039935524201435</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0.3961306472657654</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.07320652210644149</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-1.160636310027402</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-0.2249542858487072</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.2208158205737127</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0.7793884544883561</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-1.041829681779109</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.1738928447902093</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>OU7ZWg1D</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.524147048843706</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-1.349714789643779</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.645403634370199</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-1.738142449080524</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-1.058659395616618</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.2236506175240814</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.1725193449194777</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.2082640722265298</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.2979522412697556</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-0.1265977405409961</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-0.6852752832615254</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.7300548381179499</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-0.2303568639359634</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.0919313594787881</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.4278520529374902</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.8100495537746637</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.04539726160100895</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0.1594890439629588</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-0.5095514136265288</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-0.2404659631314445</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-0.7925436637262978</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-0.4537939127553229</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>UN8LwZh9</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1.504520286883804</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.6314582141501968</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.662248200009106</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-0.5194731682096183</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.112877589274722</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-0.4661762873342394</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.4512080092702128</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.3538844760607159</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.045947968310783</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-0.3956264122951818</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-0.3883466701511629</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.2425633960614011</v>
+      </c>
+      <c r="N20" t="n">
         <v>0.01044881503960961</v>
       </c>
-      <c r="O4" t="n">
-        <v>0.2469340055803715</v>
-      </c>
-      <c r="P4" t="n">
-        <v>-0.06709034043067431</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-0.1124320274006492</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.4628070268623617</v>
-      </c>
-      <c r="S4" t="n">
-        <v>-0.1239515343624319</v>
-      </c>
-      <c r="T4" t="n">
+      <c r="O20" t="n">
+        <v>0.1815522400500459</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-0.7770715781266936</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.215431958374224</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-0.359244336601963</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-1.010009749644232</v>
+      </c>
+      <c r="T20" t="n">
         <v>-0.05267552797811428</v>
       </c>
-      <c r="U4" t="n">
-        <v>0.5862765141982367</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.001229027206602704</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
+      <c r="U20" t="n">
+        <v>-0.1679782739183137</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-1.467578306889108</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.01725548919909233</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>IHxZYFW0</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1.484893524923903</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.2005042688540474</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.645403634370199</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-2.225610161428886</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-0.3158902570765756</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.461277366241344</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.9205783913346091</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.596511922112438</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-0.7986787385255927</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.3406206923575447</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.9538672232582767</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-1.249702073789477</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-1.703352886631182</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-0.101148273420096</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-0.725125163702852</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-0.3392582131021022</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.2252230187392011</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-0.368436286667432</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.1865419687091602</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.4500087214738644</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-0.434573647045305</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.205914760553312</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>pv9VXZo7</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1.484893524923903</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1.244987089326787</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.662248200009106</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-0.2757393120354372</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.1055325298083186</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-1.289003238116402</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-2.174332565402503</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-0.4098136418252382</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.7271037186786554</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-1.010094266124268</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-0.6200958316031532</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-0.237818795798489</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-0.3790293612115181</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.04452003892403334</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-0.3723961437800339</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.1053735038010003</v>
+      </c>
+      <c r="R22" t="n">
+        <v>-0.1821848485638067</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-0.2332794431933891</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.8722987925460183</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-0.6658912685407906</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-0.7092863470816225</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
         <v>-0.02378575712559158</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>vRwVZeHf</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1.484893524923903</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.8289787724109319</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.679092765648014</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-1.250674736732162</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.377299730065244</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.321344329882182</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.818982638254742</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.337631204184996</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-0.8067303609910502</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.03418270825884227</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-2.522370198521568</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-1.446504174471565</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.1015548211802321</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-0.5275546744935018</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-0.1066173565361856</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.242118990106678</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.09622998466333683</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-0.8846814614845268</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.5672796680036195</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.04823133996732459</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.5017190522499707</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0.232822932171066</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>88KCueOd</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1.484893524923903</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.6075343785762326</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.679092765648014</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.674131537358011</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.7298625844526064</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-1.59401667676841</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-1.675626534459083</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.6039741802708198</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.248848854440319</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-1.019645579914358</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.6554023941155628</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.0334987791670883</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.63894943755389</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.00714039144048087</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.4332554750170066</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.0738682082851239</v>
+      </c>
+      <c r="R24" t="n">
+        <v>-0.9129559413735839</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.1956464936890787</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.1589944153946817</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.8426755294319588</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-0.03728581517702084</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>-0.7529453545074912</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>p4vRzx2l</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1.484893524923903</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-1.134237816995704</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.645403634370199</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-0.03200545586125614</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.4865574896279944</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.846090832447657</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.657636569420106</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.269601788723787</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.3324897977755876</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.1552516819112647</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.6158996961407914</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.1051178922593469</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.8733013826751641</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.5794083581967184</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-1.019813551192749</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.329726652310071</v>
+      </c>
+      <c r="R25" t="n">
+        <v>-0.3482646661361856</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-1.617080889037469</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.3883017462649535</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.7158080621159777</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-0.9542211019316077</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0.02800248222628318</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>QJcftbvR</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1.484893524923903</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-1.448475068774147</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1.611714503092384</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.5194731682096183</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.0155555513448772</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.7184107883607697</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.2235119149473567</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.9881422349829487</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-0.3324897977755876</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.2029225852170887</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.345525674446803</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-1.284232717601816</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.3358731011132183</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-1.186486067753002</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-2.208568766456667</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-1.425790715177721</v>
+      </c>
+      <c r="R26" t="n">
+        <v>-0.816086544813269</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-3.013746851743691</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-3.607534573454181</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.6972737332469973</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-2.670263268448284</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>-0.9881049953485819</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>naJGvFw3</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1.484893524923903</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1.047466531066052</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.645403634370199</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-0.5194731682096183</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0.2158138218468292</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.7024507828499085</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.096592284608758</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.272911024703135</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.0443261336078358</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-0.09078031382816071</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-0.3786904550906641</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.2026161806706569</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-0.3866171499774749</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-0.948987634157054</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-1.547382223595897</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-0.2417729237847752</v>
+      </c>
+      <c r="R27" t="n">
+        <v>-0.6409150425098081</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.5145859185701835</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.04050481323437718</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.8762921109555407</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-1.870249908441139</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>-0.4534603769547511</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>W0zNyInr</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1.484893524923903</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-1.179128852964053</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1.679092765648014</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-0.5194731682096183</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.4428806181581317</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-1.105589841451905</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-0.05378423214728504</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-0.01224682500809506</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.4004378929372249</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-1.635023082675833</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-1.87402433017374</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.03276152359113901</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.1337098821710552</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.1499232651107134</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.640307276435588</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.152996898851936</v>
+      </c>
+      <c r="R28" t="n">
+        <v>-0.539333320194466</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.1378614057401768</v>
+      </c>
+      <c r="T28" t="n">
+        <v>-0.6551492233386623</v>
+      </c>
+      <c r="U28" t="n">
+        <v>-1.280108808779482</v>
+      </c>
+      <c r="V28" t="n">
+        <v>-0.2464771591391242</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>-0.3082167774512894</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>v3erq0f8</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1.504520286883804</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1.424551233200182</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1.679092765648014</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-2.225610161428886</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.552509244689785</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.0002105403720289837</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.2055219499083804</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.2373881529933669</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.2037482584238998</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-0.4632815516416485</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.043532077391487</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.3292285413158988</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.6425637223505661</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.1108082977350454</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.6895127818739603</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>-0.2977976760609556</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.8837287522298415</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.857934010196457</v>
+      </c>
+      <c r="T29" t="n">
+        <v>-0.05267552797811428</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.7862764486580607</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.404356148960273</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>-0.06482700345027549</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>IgfnrK9E</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1.504520286883804</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.1825478544667079</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.679092765648014</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-1.494408592906343</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-0.5598630845799519</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.5443016373331964</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.528626386281668</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.656525179450163</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.06277166871052109</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-0.2867993218384049</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.6545245563827895</v>
+      </c>
+      <c r="M30" t="n">
+        <v>-0.9827854632313545</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-0.4991017181280399</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-0.1677893077105784</v>
+      </c>
+      <c r="P30" t="n">
+        <v>-0.7319311804189481</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>-0.119939626784076</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.3380350234076058</v>
+      </c>
+      <c r="S30" t="n">
+        <v>-1.020473433126742</v>
+      </c>
+      <c r="T30" t="n">
+        <v>-0.3695027037400853</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0.5573658862166951</v>
+      </c>
+      <c r="V30" t="n">
+        <v>-0.7405708786329752</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>-0.1618181227520909</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>xbHaKGH7</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1.484893524923903</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.6793600361255908</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1.679092765648014</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-0.2757393120354372</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-0.9925538604189869</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-0.5583896525081027</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-0.4875327548585798</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-0.5780861084780754</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.8559296781259798</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-0.1409247112261304</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.5965872660197924</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.172558644009404</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-1.242446340583009</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.6986804680610891</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.439434849334514</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.02915444538082</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.906038749211058</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1.493176652241154</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.695819402811682</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.229542216869521</v>
+      </c>
+      <c r="V31" t="n">
+        <v>2.387049937082213</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0.01351823285039526</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>nTbjsvPK</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1.484893524923903</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.04787474656166122</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.645403634370199</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.186663825009649</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.8839419000773864</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-0.9501352423201431</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-0.5745396225565963</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-0.5171903032383249</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.7472327748422993</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-0.840992596977003</v>
+      </c>
+      <c r="L32" t="n">
+        <v>2.399885428568087</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.1076004875661165</v>
+      </c>
+      <c r="N32" t="n">
+        <v>-0.7758189858546489</v>
+      </c>
+      <c r="O32" t="n">
+        <v>-0.02524402559309496</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.319524551239897</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>-0.04538403859687264</v>
+      </c>
+      <c r="R32" t="n">
+        <v>-0.8058106320625915</v>
+      </c>
+      <c r="S32" t="n">
+        <v>-0.3803556178789224</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0.4798639658817566</v>
+      </c>
+      <c r="U32" t="n">
+        <v>-0.776658130473648</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0.004185359733816401</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>-0.3656160696864847</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>YyTMIXGq</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1.484893524923903</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-1.268910924900751</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1.679092765648014</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-0.7632070243837995</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-0.141445094749495</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-0.7977897351710163</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-0.6195431748141911</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.3830085568275531</v>
+      </c>
+      <c r="J33" t="n">
+        <v>-1.499169893020418</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.2888844093278937</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.6865969849765919</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.06381653397400083</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.8597443634593122</v>
+      </c>
+      <c r="O33" t="n">
+        <v>-0.2128770508828436</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.2131569468276257</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>-0.3157813495638727</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.007937409596771836</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.3649863189629398</v>
+      </c>
+      <c r="T33" t="n">
+        <v>-0.9776498485022469</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0.4231364256646152</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0.5621532348679269</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>-0.02378575712559158</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>W0EiMxme</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1.504520286883804</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-0.6763492501185456</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1.679092765648014</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-1.494408592906343</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.5489070285075773</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.3817997630407942</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.744643437118123</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.6292394214926315</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.754490745271066</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-0.9692841072029773</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-0.2531596593041694</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.07220469690444888</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-0.7076808804217378</v>
+      </c>
+      <c r="O34" t="n">
+        <v>-0.2498864759797323</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.2985491705219345</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.07786957042576699</v>
+      </c>
+      <c r="R34" t="n">
+        <v>-0.9041842410188635</v>
+      </c>
+      <c r="S34" t="n">
+        <v>-0.539340396050025</v>
+      </c>
+      <c r="T34" t="n">
+        <v>-0.2153434257254617</v>
+      </c>
+      <c r="U34" t="n">
+        <v>-1.33557417744343</v>
+      </c>
+      <c r="V34" t="n">
+        <v>-0.2215492289470073</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>-1.528897298304507</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>QNDeLd21</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1.484893524923903</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-1.448475068774147</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1.611714503092384</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-0.5194731682096183</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-0.1166555190503838</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.5268907222304389</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.3045297648750889</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.402351383666856</v>
+      </c>
+      <c r="J35" t="n">
+        <v>-0.1295889116460519</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.1742686438468205</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-0.4680104444002852</v>
+      </c>
+      <c r="M35" t="n">
+        <v>-0.1567582975244261</v>
+      </c>
+      <c r="N35" t="n">
+        <v>-0.3269113665222589</v>
+      </c>
+      <c r="O35" t="n">
+        <v>-1.423290049142954</v>
+      </c>
+      <c r="P35" t="n">
+        <v>-2.629911905672202</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>-2.436465237758355</v>
+      </c>
+      <c r="R35" t="n">
+        <v>-0.6493547535311409</v>
+      </c>
+      <c r="S35" t="n">
+        <v>-2.296074791917345</v>
+      </c>
+      <c r="T35" t="n">
+        <v>-3.105473160653724</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.239942007743739</v>
+      </c>
+      <c r="V35" t="n">
+        <v>-1.999946312732058</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>-1.221281006142275</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>hAFmNIXl</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1.484893524923903</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.3980248271147825</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1.645403634370199</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-1.00694088055798</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.3222117840672188</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.4346773570565757</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.7005610247419233</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.3021083324752274</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.339027026053445</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.09785813352610538</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.2055105560695598</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.1538670364650023</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-0.1418187966939284</v>
+      </c>
+      <c r="O36" t="n">
+        <v>-0.3151543477010588</v>
+      </c>
+      <c r="P36" t="n">
+        <v>-0.2908803006434924</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>-0.5549643670576263</v>
+      </c>
+      <c r="R36" t="n">
+        <v>-0.5285078549865823</v>
+      </c>
+      <c r="S36" t="n">
+        <v>-0.1026313825328291</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0.3037880751102096</v>
+      </c>
+      <c r="U36" t="n">
+        <v>-0.3277765457108285</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.1601026779640606</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>-0.1113846326152508</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>zZKrObIr</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1.484893524923903</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-1.134237816995704</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1.645403634370199</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-0.5194731682096183</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-0.5224700545691703</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.8602775040128666</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.7005610247419233</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.337631204184996</v>
+      </c>
+      <c r="J37" t="n">
+        <v>-0.9476337541365616</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.320722121961525</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.183202330945141</v>
+      </c>
+      <c r="M37" t="n">
+        <v>-0.4241262890474154</v>
+      </c>
+      <c r="N37" t="n">
+        <v>-0.6432516656216264</v>
+      </c>
+      <c r="O37" t="n">
+        <v>-0.1211278340308643</v>
+      </c>
+      <c r="P37" t="n">
+        <v>-0.6809340791242073</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.6635491277106225</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.3397235995753787</v>
+      </c>
+      <c r="S37" t="n">
+        <v>-0.9085500315217656</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0.2208158205737127</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.0835361378473521</v>
+      </c>
+      <c r="V37" t="n">
+        <v>-0.8850650939060134</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0.1738928447902093</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>b9cFuRmG</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1.524147048843706</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.4878068990514803</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1.645403634370199</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-1.250674736732162</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-0.4122941625731199</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-0.3455895790299575</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-0.766221419209315</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-0.8628548981982617</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.2440063707511888</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-0.4433829812456288</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.4227753949308</v>
+      </c>
+      <c r="M38" t="n">
+        <v>-0.5939583770786898</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.03483306962432298</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.8586375039375891</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.39959323209896</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.4229298346212199</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.005009012654816</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.9114342704070476</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0.1246754640699059</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0.06888301270282395</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.3852475606524023</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0.2597357275804335</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>4nbBt7Y9</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1.504520286883804</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.9217716303546748</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1.645403634370199</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-2.713077873777248</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-1.624228974529678</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.5765440727086727</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1.140595757927295</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.725952281076158</v>
+      </c>
+      <c r="J39" t="n">
+        <v>-0.1424715075907843</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1.021151799901416</v>
+      </c>
+      <c r="L39" t="n">
+        <v>-0.4462839605141609</v>
+      </c>
+      <c r="M39" t="n">
+        <v>-1.195197822281766</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-1.190602259376259</v>
+      </c>
+      <c r="O39" t="n">
+        <v>-0.1193448102059112</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.0142808348305838</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.3451602232323717</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.5960196660797337</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.04466498506218686</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0.4600965282954177</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0.4514217271041558</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0.4265960970232193</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0.3760756340620252</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>fiHVGBod</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1.484893524923903</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.2005042688540474</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.645403634370199</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-0.5194731682096183</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-0.2194863515800309</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.9489442012954269</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.9389131718839995</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.240550934962205</v>
+      </c>
+      <c r="J40" t="n">
+        <v>-1.044253223722055</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.7266529580403259</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1.726364428098242</v>
+      </c>
+      <c r="M40" t="n">
+        <v>-0.7440425478970253</v>
+      </c>
+      <c r="N40" t="n">
+        <v>-1.2371675514037</v>
+      </c>
+      <c r="O40" t="n">
+        <v>-0.2092689920908433</v>
+      </c>
+      <c r="P40" t="n">
+        <v>-0.7749708040139619</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.3539692777813807</v>
+      </c>
+      <c r="R40" t="n">
+        <v>-0.01927001333448523</v>
+      </c>
+      <c r="S40" t="n">
+        <v>-1.060216206430866</v>
+      </c>
+      <c r="T40" t="n">
+        <v>-0.2972089690362189</v>
+      </c>
+      <c r="U40" t="n">
+        <v>-0.5629831528268824</v>
+      </c>
+      <c r="V40" t="n">
+        <v>-1.236535475376074</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0.1170841027032557</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>G0IRHiWk</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1.524147048843706</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1.487398683555871</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1.645403634370199</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-1.250674736732162</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-0.158555744642821</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.1444954386772868</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.1271824330155303</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.4197813860786102</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.321459849765174</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.6072615356642077</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.09687813663893971</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.5327261263101835</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.09900921218513895</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.500243644578477</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1.397681948332383</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.5763694305988533</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.9337066536154189</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1.415527451433978</v>
+      </c>
+      <c r="T41" t="n">
+        <v>-0.07407919873434328</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0.8633207932132263</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0.8858932024177194</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>-0.4898226661110142</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>jqf7smJ3</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1.484893524923903</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1.047466531066052</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.645403634370199</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-0.7632070243837995</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-0.07809395685176591</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.321183984534898</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-0.2088440905078444</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.4315486914389485</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.7335450166510216</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-0.0008387756381521587</v>
+      </c>
+      <c r="L42" t="n">
+        <v>-0.5114634121725331</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.5192975426053851</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.8143253398097933</v>
+      </c>
+      <c r="O42" t="n">
+        <v>-1.006956933956219</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.02150374892221166</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.7066089875879809</v>
+      </c>
+      <c r="R42" t="n">
+        <v>-0.80710791671261</v>
+      </c>
+      <c r="S42" t="n">
+        <v>-0.776106438075824</v>
+      </c>
+      <c r="T42" t="n">
+        <v>-1.089284680289643</v>
+      </c>
+      <c r="U42" t="n">
+        <v>-1.556288379988075</v>
+      </c>
+      <c r="V42" t="n">
+        <v>-1.363350066571558</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>-1.062749987831133</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/usa/data_preparation/df_selected_nan.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_selected_nan.xlsx
@@ -553,71 +553,71 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8K42rT3c</t>
+          <t>xbHaKGH7</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1.484893524923903</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.30482375367543</v>
+        <v>0.6793600361255908</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.02220836388162897</v>
+        <v>1.645403634370199</v>
       </c>
       <c r="E2" t="n">
-        <v>1.43039768118383</v>
+        <v>-0.2757393120354372</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8253483575158508</v>
+        <v>-0.9925538604189869</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.643670027246644</v>
+        <v>-0.5583896525081027</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.3555223349029683</v>
+        <v>-0.4875327548585798</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6945824315454244</v>
+        <v>-0.5780861084780754</v>
       </c>
       <c r="J2" t="n">
-        <v>1.174773927758107</v>
+        <v>0.8559296781259798</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.602275721109812</v>
+        <v>-0.1409247112261304</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5096813304752958</v>
+        <v>0.5965872660197924</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4646428307760516</v>
+        <v>1.172558644009404</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8803654672242148</v>
+        <v>-1.242446340583009</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1318058064680049</v>
+        <v>0.7109494874126697</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4267867277166374</v>
+        <v>1.439509046443201</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1650245281777734</v>
+        <v>1.044328826167431</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1421652408513906</v>
+        <v>1.876221899552257</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3772153751680706</v>
+        <v>1.486618123582667</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7814038786445447</v>
+        <v>1.710038184677961</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2542164947997497</v>
+        <v>1.12875498730522</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4295164629720869</v>
+        <v>2.373776526204845</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
@@ -626,77 +626,77 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.2558942269821199</v>
+        <v>0.009965471900301453</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ma0gz0nH</t>
+          <t>nTbjsvPK</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.504520286883804</v>
+        <v>1.484893524923903</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.6314582141501968</v>
+        <v>-0.04787474656166122</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.07274206079835104</v>
+        <v>1.645403634370199</v>
       </c>
       <c r="E3" t="n">
-        <v>0.455462256487106</v>
+        <v>1.186663825009649</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6986460817203919</v>
+        <v>0.8839419000773864</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4790107056978561</v>
+        <v>-0.9501352423201431</v>
       </c>
       <c r="H3" t="n">
-        <v>1.562295710563276</v>
+        <v>-0.5745396225565963</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7066094542368555</v>
+        <v>-0.5171903032383249</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.07805852786712188</v>
+        <v>0.7472327748422993</v>
       </c>
       <c r="K3" t="n">
-        <v>0.08193927720928973</v>
+        <v>-0.840992596977003</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.1634948051709595</v>
+        <v>2.399885428568087</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1271176141648149</v>
+        <v>0.1076004875661165</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01044881503960961</v>
+        <v>-0.6850383583073784</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2469340055803715</v>
+        <v>0.002653945724342031</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.06709034043067431</v>
+        <v>0.3055243781897151</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1124320274006492</v>
+        <v>0.01327023011665525</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4628070268623617</v>
+        <v>-0.79441896765352</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1239515343624319</v>
+        <v>-0.3814091001708955</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.05267552797811428</v>
+        <v>0.450082525060199</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5862765141982367</v>
+        <v>-0.7882092018884832</v>
       </c>
       <c r="V3" t="n">
-        <v>0.001229027206602704</v>
+        <v>0.003897208054267512</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -705,77 +705,77 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.02378575712559158</v>
+        <v>-0.2902188218863766</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>UT5bq9li</t>
+          <t>YyTMIXGq</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1.484893524923903</v>
       </c>
       <c r="C4" t="n">
-        <v>1.244987089326787</v>
+        <v>-1.268910924900751</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.8307475145491819</v>
+        <v>1.645403634370199</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2757393120354372</v>
+        <v>-0.7632070243837995</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8933955576225415</v>
+        <v>-0.141445094749495</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.8137497406818768</v>
+        <v>-0.7977897351710163</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.467689054192751</v>
+        <v>-0.6195431748141911</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.859545662218913</v>
+        <v>0.3830085568275531</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7689721554990351</v>
+        <v>-1.499169893020418</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1695786525963986</v>
+        <v>0.2888844093278937</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.2048785840016718</v>
+        <v>0.6865969849765919</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8850289693890135</v>
+        <v>0.06381653397400083</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8418984868537167</v>
+        <v>0.8597443634593122</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2364883488219674</v>
+        <v>-0.1982540662162228</v>
       </c>
       <c r="P4" t="n">
-        <v>1.03093950304962</v>
+        <v>0.1981963303326454</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9655289006763714</v>
+        <v>-0.2817941069480826</v>
       </c>
       <c r="R4" t="n">
-        <v>0.24420900486391</v>
+        <v>0.08756376832895926</v>
       </c>
       <c r="S4" t="n">
-        <v>1.164842762821797</v>
+        <v>0.3281418629242858</v>
       </c>
       <c r="T4" t="n">
-        <v>1.707802816006683</v>
+        <v>-0.9859812700892766</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2423081192723966</v>
+        <v>0.4495257822428165</v>
       </c>
       <c r="V4" t="n">
-        <v>1.104709810019914</v>
+        <v>0.5256247871986603</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -784,77 +784,77 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01165303335159579</v>
+        <v>-0.02378575712559158</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Sx1kytXA</t>
+          <t>v3erq0f8</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.484893524923903</v>
+        <v>1.504520286883804</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6075343785762326</v>
+        <v>1.424551233200182</v>
       </c>
       <c r="D5" t="n">
-        <v>1.072688402647349</v>
+        <v>1.645403634370199</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.03200545586125614</v>
+        <v>-2.225610161428886</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.191024246147718</v>
+        <v>1.552509244689785</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.5798300052032</v>
+        <v>0.0002105403720289837</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6525457798030938</v>
+        <v>0.2055219499083804</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1121008162086799</v>
+        <v>0.2373881529933669</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4573743660858196</v>
+        <v>0.2037482584238998</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.466169499601038</v>
+        <v>-0.4632815516416485</v>
       </c>
       <c r="L5" t="n">
-        <v>1.09871044916577</v>
+        <v>1.043532077391487</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2915105615694395</v>
+        <v>0.3292285413158988</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6619135102781571</v>
+        <v>0.6425637223505661</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4185399277592944</v>
+        <v>0.1434661943215198</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1923036253187315</v>
+        <v>0.6405116951960408</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.5953641212135954</v>
+        <v>-0.298822831641812</v>
       </c>
       <c r="R5" t="n">
-        <v>-1.429109170801369</v>
+        <v>0.8694016844920973</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1506422359235565</v>
+        <v>0.8140043086865982</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1530878105382049</v>
+        <v>-0.05267552797811428</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6053799158050117</v>
+        <v>0.7469435599526005</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2919870107058845</v>
+        <v>1.3020401691152</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -863,13 +863,13 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.7641180574321723</v>
+        <v>-0.06050687225820343</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2NHGKPBj</t>
+          <t>IgfnrK9E</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -879,61 +879,61 @@
         <v>-0.1825478544667079</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4831286052855917</v>
+        <v>1.645403634370199</v>
       </c>
       <c r="E6" t="n">
         <v>-1.494408592906343</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1331819028497911</v>
+        <v>-0.5598630845799519</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1438505899697769</v>
+        <v>0.5443016373331964</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007506319974963347</v>
+        <v>1.528626386281668</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1121008162086799</v>
+        <v>1.656525179450163</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2962574966810276</v>
+        <v>0.06277166871052109</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5564068610950201</v>
+        <v>-0.2867993218384049</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.1421131861084248</v>
+        <v>0.6545245563827895</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1662047828380386</v>
+        <v>-0.9827854632313545</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4991017181280399</v>
+        <v>-0.5375513759067363</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2799411343178443</v>
+        <v>-0.1671344654468115</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7938263964356514</v>
+        <v>-0.7325948859123463</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.08088349147412106</v>
+        <v>-0.1616286114438752</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.3210273573789438</v>
+        <v>0.37106228516151</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.538829472400337</v>
+        <v>-0.9827049295190485</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3695027037400853</v>
+        <v>-0.3785133848856099</v>
       </c>
       <c r="U6" t="n">
-        <v>0.266521634274559</v>
+        <v>0.6271518026939927</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.1791511756188</v>
+        <v>-0.7605590939661112</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -942,77 +942,77 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.1618181227520909</v>
+        <v>-0.1688705282211591</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4nxtRRYM</t>
+          <t>zZKrObIr</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.504520286883804</v>
+        <v>1.484893524923903</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.6763492501185456</v>
+        <v>-1.134237816995704</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.005363798242721613</v>
+        <v>1.645403634370199</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7632070243837995</v>
+        <v>-0.5194731682096183</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6326459465652218</v>
+        <v>-0.5224700545691703</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9130564416383449</v>
+        <v>0.8602775040128666</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2605262915565519</v>
+        <v>0.7005610247419233</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6039741802708198</v>
+        <v>1.337631204184996</v>
       </c>
       <c r="J7" t="n">
-        <v>1.886537353704573</v>
+        <v>-0.9476337541365616</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.557702923422728</v>
+        <v>0.320722121961525</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.9773757888416365</v>
+        <v>1.183202330945141</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8178860508650206</v>
+        <v>-0.4241262890474154</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7076808804217378</v>
+        <v>-0.6432516656216264</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05102754309170245</v>
+        <v>-0.1654411312974193</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4712852381781211</v>
+        <v>-0.7116647012744797</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8789097844390735</v>
+        <v>0.6196270808710123</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.4990696663193198</v>
+        <v>0.3000034760381733</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5448276718187834</v>
+        <v>-0.9284198783553465</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5544726979297275</v>
+        <v>0.2162859431649873</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.381161894841025</v>
+        <v>0.1088774958580459</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.7066611297234656</v>
+        <v>-0.9056697062113068</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -1021,77 +1021,77 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>-1.732012196121629</v>
+        <v>0.1550663112744179</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>IktpQolT</t>
+          <t>hAFmNIXl</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1.484893524923903</v>
       </c>
       <c r="C8" t="n">
-        <v>1.218052467745777</v>
+        <v>-0.3980248271147825</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4831286052855917</v>
+        <v>1.645403634370199</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5194731682096183</v>
+        <v>-1.00694088055798</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.066922587516322</v>
+        <v>0.3222117840672188</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6541496855732682</v>
+        <v>0.4346773570565757</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6345558147641175</v>
+        <v>0.7005610247419233</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2082640722265298</v>
+        <v>0.3021083324752274</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4774190021538274</v>
+        <v>1.339027026053445</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1599416731616867</v>
+        <v>0.09785813352610538</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1634948051709595</v>
+        <v>0.2055105560695598</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1016597277463064</v>
+        <v>0.1538670364650023</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2575068669856703</v>
+        <v>-0.2023105051829045</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.007173136382548172</v>
+        <v>-0.3452099860330272</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.010960415169698</v>
+        <v>-0.2976080827893575</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.656903348924384</v>
+        <v>-0.6370806773693891</v>
       </c>
       <c r="R8" t="n">
-        <v>1.146296896827158</v>
+        <v>-0.5981833606652645</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5278099345296976</v>
+        <v>-0.1171984223945263</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5497981673824337</v>
+        <v>0.313327241953418</v>
       </c>
       <c r="U8" t="n">
-        <v>2.431712021141904</v>
+        <v>-0.2880582923001621</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5825971726585487</v>
+        <v>0.1093599523900017</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1100,77 +1100,77 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.2606452632001062</v>
+        <v>-0.1391709977458838</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>OWICL5dp</t>
+          <t>QNDeLd21</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1.484893524923903</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.8289787724109319</v>
+        <v>-1.448475068774147</v>
       </c>
       <c r="D9" t="n">
-        <v>0.735797089869202</v>
+        <v>1.611714503092384</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>-0.5194731682096183</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7518977628518172</v>
+        <v>-0.1166555190503838</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3314029074647478</v>
+        <v>0.5268907222304389</v>
       </c>
       <c r="H9" t="n">
-        <v>1.125927933487783</v>
+        <v>0.3045297648750889</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7810376606409953</v>
+        <v>1.402351383666856</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5886158122727817</v>
+        <v>-0.1295889116460519</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.03238066496781</v>
+        <v>0.1742686438468205</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.01541890784534</v>
+        <v>-0.4680104444002852</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3102278255792644</v>
+        <v>-0.1567582975244261</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1357195734829637</v>
+        <v>-0.3269113665222589</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3725913566155821</v>
+        <v>-1.414922634667242</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4311716934867446</v>
+        <v>-2.614153307729299</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1228633146442363</v>
+        <v>-2.473699290346661</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.09916821787889364</v>
+        <v>-0.704410797852548</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.725458027785127</v>
+        <v>-2.27967086761495</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1726682056374236</v>
+        <v>-3.089618589723184</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5218666520509103</v>
+        <v>1.210279365815468</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1564938390772055</v>
+        <v>-1.983424628771395</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
@@ -1179,77 +1179,77 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.1598758239220028</v>
+        <v>-1.223478498058372</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>z7pPU9Zc</t>
+          <t>W0EiMxme</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1.504520286883804</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.9187608443476297</v>
+        <v>-0.6763492501185456</v>
       </c>
       <c r="D10" t="n">
-        <v>1.089532968286256</v>
+        <v>1.645403634370199</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.250674736732162</v>
+        <v>-1.494408592906343</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8772884208854174</v>
+        <v>0.5489070285075773</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5401496462099763</v>
+        <v>0.3817997630407942</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5441086491252703</v>
+        <v>1.744643437118123</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5115167810110188</v>
+        <v>0.6292394214926315</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3780389762944633</v>
+        <v>1.754490745271066</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.04677604672382018</v>
+        <v>-0.9692841072029773</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.136121596101584</v>
+        <v>-0.2531596593041694</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4517784732773371</v>
+        <v>0.07220469690444888</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.579678497365032</v>
+        <v>-0.8598815024448834</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4285253002245145</v>
+        <v>-0.2154996548495263</v>
       </c>
       <c r="P10" t="n">
-        <v>0.818421078653255</v>
+        <v>0.3081727029162967</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.9800782666011918</v>
+        <v>0.1156637882182539</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5168296132462704</v>
+        <v>-0.8372146471300851</v>
       </c>
       <c r="S10" t="n">
-        <v>1.074317339681145</v>
+        <v>-0.4792562471504822</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3732776015806902</v>
+        <v>-0.2730576672242057</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1276817198201864</v>
+        <v>-1.270882121472861</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1403156947267206</v>
+        <v>-0.2352715681629826</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -1258,77 +1258,77 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.333041481757925</v>
+        <v>-1.388225346162075</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>EcqTTTl4</t>
+          <t>fiHVGBod</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.524147048843706</v>
+        <v>1.484893524923903</v>
       </c>
       <c r="C11" t="n">
-        <v>-1.349714789643779</v>
+        <v>-0.2005042688540474</v>
       </c>
       <c r="D11" t="n">
-        <v>1.25797862467533</v>
+        <v>1.645403634370199</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.444279442299792</v>
+        <v>-0.5194731682096183</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7428218385612722</v>
+        <v>-0.2194863515800309</v>
       </c>
       <c r="G11" t="n">
-        <v>0.26443729827406</v>
+        <v>0.9489442012954269</v>
       </c>
       <c r="H11" t="n">
-        <v>1.16993140680632</v>
+        <v>0.9389131718839995</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7551495888482509</v>
+        <v>1.240550934962205</v>
       </c>
       <c r="J11" t="n">
-        <v>1.058830564255515</v>
+        <v>-1.044253223722055</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.007206318164878419</v>
+        <v>0.7266529580403259</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.3014407346066679</v>
+        <v>1.726364428098242</v>
       </c>
       <c r="M11" t="n">
-        <v>1.449556096116227</v>
+        <v>-0.7440425478970253</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2303568639359634</v>
+        <v>-1.2371675514037</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2312901289459963</v>
+        <v>-0.1718196890769035</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1811017303954732</v>
+        <v>-0.7500630611845774</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.015315930975856</v>
+        <v>0.3593049244054501</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.7810624069980113</v>
+        <v>0.02336923763345983</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1937177952884699</v>
+        <v>-1.044336704472095</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.04395551396631577</v>
+        <v>-0.2714686068195774</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.090713862888377</v>
+        <v>-0.5401602614391359</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.1040024846656663</v>
+        <v>-1.205857766076372</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -1337,77 +1337,77 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.382099362020403</v>
+        <v>0.1031459052571811</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>APxxS7JG</t>
+          <t>4nbBt7Y9</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.484893524923903</v>
+        <v>1.504520286883804</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.3980248271147825</v>
+        <v>0.9217716303546748</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.6117681612433864</v>
+        <v>1.645403634370199</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5194731682096183</v>
+        <v>-2.713077873777248</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0008654324120704823</v>
+        <v>-1.624228974529678</v>
       </c>
       <c r="G12" t="n">
-        <v>0.461277366241344</v>
+        <v>0.5765440727086727</v>
       </c>
       <c r="H12" t="n">
-        <v>1.067256635729733</v>
+        <v>1.140595757927295</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8198697683301115</v>
+        <v>1.725952281076158</v>
       </c>
       <c r="J12" t="n">
-        <v>2.099905349039205</v>
+        <v>-0.1424715075907843</v>
       </c>
       <c r="K12" t="n">
-        <v>0.06204070681327004</v>
+        <v>1.021151799901416</v>
       </c>
       <c r="L12" t="n">
-        <v>1.400467169806381</v>
+        <v>-0.4462839605141609</v>
       </c>
       <c r="M12" t="n">
-        <v>1.598060433557527</v>
+        <v>-1.195197822281766</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1418187966939284</v>
+        <v>-1.190602259376259</v>
       </c>
       <c r="O12" t="n">
-        <v>0.06410144643268943</v>
+        <v>-0.1340092206803797</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6790329233482842</v>
+        <v>0.02041224823106476</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.226030485913737</v>
+        <v>0.3119875048232637</v>
       </c>
       <c r="R12" t="n">
-        <v>0.04789623578091549</v>
+        <v>0.6086856011235645</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7511246275027874</v>
+        <v>0.009140883095114157</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1835575788869437</v>
+        <v>0.4907321188176731</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4331086338015939</v>
+        <v>0.5008277455242902</v>
       </c>
       <c r="V12" t="n">
-        <v>0.9037497175520329</v>
+        <v>0.3829894835961346</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -1416,77 +1416,77 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.07153300335089166</v>
+        <v>0.4165877762777097</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>tpoLVkKi</t>
+          <t>b9cFuRmG</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.484893524923903</v>
+        <v>1.524147048843706</v>
       </c>
       <c r="C13" t="n">
-        <v>1.164183224583759</v>
+        <v>-0.4878068990514803</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.07274206079835104</v>
+        <v>1.645403634370199</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.494408592906343</v>
+        <v>-1.250674736732162</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1018600000751169</v>
+        <v>-0.4122941625731199</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.146123188781076</v>
+        <v>-0.3455895790299575</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.8081294890364931</v>
+        <v>-0.766221419209315</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6409571399747399</v>
+        <v>-0.8628548981982617</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2394054436280701</v>
+        <v>0.2440063707511888</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.139878240151988</v>
+        <v>-0.4433829812456288</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7124618467457867</v>
+        <v>0.4227753949308</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3353221843416062</v>
+        <v>-0.5939583770786898</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4605845486411909</v>
+        <v>0.03483306962432298</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2763354222422418</v>
+        <v>0.8255619043350976</v>
       </c>
       <c r="P13" t="n">
-        <v>0.152310093596645</v>
+        <v>1.367166277797772</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.339236147531482</v>
+        <v>0.4082999123438334</v>
       </c>
       <c r="R13" t="n">
-        <v>-1.23679083054463</v>
+        <v>0.9261631738576426</v>
       </c>
       <c r="S13" t="n">
-        <v>0.242487201151595</v>
+        <v>0.8698757775832962</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5955294305686065</v>
+        <v>0.09041197467001667</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4484545147242835</v>
+        <v>0.007952479933744145</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.08626560062709546</v>
+        <v>0.3611594827282895</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -1495,77 +1495,77 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.3986558113639818</v>
+        <v>0.2481490653127253</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>WYwYSm4A</t>
+          <t>G0IRHiWk</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.484893524923903</v>
+        <v>1.524147048843706</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.04787474656166122</v>
+        <v>1.487398683555871</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1125481612296299</v>
+        <v>1.645403634370199</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.7632070243837995</v>
+        <v>-1.250674736732162</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1202226487411253</v>
+        <v>-0.158555744642821</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.8598564232688086</v>
+        <v>0.1444954386772868</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3155306332047231</v>
+        <v>0.1271824330155303</v>
       </c>
       <c r="I14" t="n">
-        <v>1.25673097983267</v>
+        <v>0.4197813860786102</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3527032740348687</v>
+        <v>1.321459849765174</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.617398634610787</v>
+        <v>0.6072615356642077</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.0427921169147146</v>
+        <v>0.09687813663893971</v>
       </c>
       <c r="M14" t="n">
-        <v>0.05027510502798565</v>
+        <v>0.5327261263101835</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.619924359800993</v>
+        <v>-0.2133265908926857</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8838422680276248</v>
+        <v>0.4539181050073154</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3229170892325588</v>
+        <v>1.369709487670598</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.09978148371800573</v>
+        <v>0.5714793130003447</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.3263765950480657</v>
+        <v>0.9341789839705305</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1689514597247139</v>
+        <v>1.268634118170913</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3690560587742675</v>
+        <v>-0.1475651349973979</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3041299486184266</v>
+        <v>0.8886738447345787</v>
       </c>
       <c r="V14" t="n">
-        <v>0.4108494546597375</v>
+        <v>0.815705008902823</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -1574,77 +1574,77 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.1837883739979817</v>
+        <v>-0.5105861588208792</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>ln2oxMH4</t>
+          <t>jqf7smJ3</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.524147048843706</v>
+        <v>1.484893524923903</v>
       </c>
       <c r="C15" t="n">
-        <v>1.487398683555871</v>
+        <v>1.047466531066052</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.8644366458269966</v>
+        <v>1.645403634370199</v>
       </c>
       <c r="E15" t="n">
-        <v>2.161599249706374</v>
+        <v>-0.7632070243837995</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2745742975780566</v>
+        <v>-0.07809395685176591</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.602723001149383</v>
+        <v>0.321183984534898</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5278692720672388</v>
+        <v>-0.2088440905078444</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6848744046231454</v>
+        <v>0.4315486914389485</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8921619792205392</v>
+        <v>0.7335450166510216</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6025715444137858</v>
+        <v>-0.0008387756381521587</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3141429755001799</v>
+        <v>-0.5114634121725331</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1330282819203003</v>
+        <v>0.5192975426053851</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1189423726789663</v>
+        <v>0.8143253398097933</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4032695015205009</v>
+        <v>-0.9503520603267207</v>
       </c>
       <c r="P15" t="n">
-        <v>2.085971939448174</v>
+        <v>0.04803160629028178</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.121030690542928</v>
+        <v>0.7788358793783446</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3705603036325728</v>
+        <v>-0.7610141269846636</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3818390542067909</v>
+        <v>-0.7394407087899373</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4831271287422924</v>
+        <v>-1.110968137591706</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1393425035984754</v>
+        <v>-1.561305392824594</v>
       </c>
       <c r="V15" t="n">
-        <v>1.139354975349613</v>
+        <v>-1.320605674410901</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
@@ -1653,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.2977656439440736</v>
+        <v>-1.029707649693997</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/usa/data_preparation/df_selected_nan.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y15"/>
+  <dimension ref="A1:AT43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,1224 +436,6187 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_team_away</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>h2h_27_segun_loc</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>h2h_27</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>h2h_3_segun_loc</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>h2h_3</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls_against</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal_against</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals_against</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>mean_last_match_mean_rat_player_start_home_against</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_away_against</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_sub</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_start</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_rat_player_miss</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>xbHaKGH7</t>
+          <t>d0ReJPqB</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.484893524923903</v>
+        <v>1.460586108766236</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6793600361255908</v>
+        <v>-1.004046052674687</v>
       </c>
       <c r="D2" t="n">
-        <v>1.645403634370199</v>
+        <v>-1.327993888990671</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2757393120354372</v>
+        <v>1.631613246155598</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.9925538604189869</v>
+        <v>1.652750648314044</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.5583896525081027</v>
+        <v>-0.04450296339670891</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4875327548585798</v>
+        <v>0.784026476557584</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5780861084780754</v>
+        <v>0.2478973019411075</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8559296781259798</v>
+        <v>0.5474611689635186</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1409247112261304</v>
+        <v>0.4311347910301251</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5965872660197924</v>
+        <v>0.6620599223989427</v>
       </c>
       <c r="M2" t="n">
-        <v>1.172558644009404</v>
+        <v>-0.08107976347716568</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.242446340583009</v>
+        <v>-0.3026956741199273</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7109494874126697</v>
+        <v>-1.860660838509485</v>
       </c>
       <c r="P2" t="n">
-        <v>1.439509046443201</v>
+        <v>2.170284700195697</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.044328826167431</v>
+        <v>-2.825178296261222</v>
       </c>
       <c r="R2" t="n">
-        <v>1.876221899552257</v>
+        <v>-0.5697786174235997</v>
       </c>
       <c r="S2" t="n">
-        <v>1.486618123582667</v>
+        <v>0.873754043457952</v>
       </c>
       <c r="T2" t="n">
-        <v>1.710038184677961</v>
+        <v>1.083333860651111</v>
       </c>
       <c r="U2" t="n">
-        <v>1.12875498730522</v>
+        <v>-1.083419346580778</v>
       </c>
       <c r="V2" t="n">
-        <v>2.373776526204845</v>
+        <v>-0.004322005167574608</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>-0.8324076392731445</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.0961055104882071</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.009965471900301453</v>
+        <v>1.001162242357758</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-1.211064597011594</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-0.1945477242212655</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-0.8009838608410148</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-0.8599821949319129</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-1.000324309090743</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-0.5730748259955963</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-0.1275655428208402</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-0.02148913804784683</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.2080125368299405</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.5335593486794388</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>-0.3864257334437438</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.03611563016432098</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.1830333690373639</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>-1.040624041737406</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>nTbjsvPK</t>
+          <t>dx5Z1E0m</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.484893524923903</v>
+        <v>1.480282970429273</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.04787474656166122</v>
+        <v>-0.1499982146601106</v>
       </c>
       <c r="D3" t="n">
-        <v>1.645403634370199</v>
+        <v>1.39012298617859</v>
       </c>
       <c r="E3" t="n">
-        <v>1.186663825009649</v>
+        <v>1.647624247492205</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8839419000773864</v>
+        <v>1.635920238513152</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.9501352423201431</v>
+        <v>0.2012829449586997</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5745396225565963</v>
+        <v>1.034998220786815</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5171903032383249</v>
+        <v>-1.161628394132923</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7472327748422993</v>
+        <v>-0.4368959392708438</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.840992596977003</v>
+        <v>-1.687156168093831</v>
       </c>
       <c r="L3" t="n">
-        <v>2.399885428568087</v>
+        <v>0.7032234395214597</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1076004875661165</v>
+        <v>-0.3085110509710888</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6850383583073784</v>
+        <v>0.9080782087739503</v>
       </c>
       <c r="O3" t="n">
-        <v>0.002653945724342031</v>
+        <v>-0.5418569012729133</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3055243781897151</v>
+        <v>0.160984396436005</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01327023011665525</v>
+        <v>0.7295464728903693</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.79441896765352</v>
+        <v>1.110582357130726</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3814091001708955</v>
+        <v>-1.095869437097496</v>
       </c>
       <c r="T3" t="n">
-        <v>0.450082525060199</v>
+        <v>1.03576752641634</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7882092018884832</v>
+        <v>-1.035848618374161</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003897208054267512</v>
+        <v>-0.004322005167574608</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>-1.447653484812556</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.4993788646841465</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.2902188218863766</v>
+        <v>-1.271560024372007</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-1.358425001598663</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-0.2307393233635287</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.749822381786915</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-0.8483897326216852</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.559759365692898</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.1283178747621304</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.1736218242484482</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-0.4752023310959915</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-0.2107313834349427</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.1049107507706471</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.3505114367681189</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.3008252576678129</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.1888589128848833</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.31752597196057</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>YyTMIXGq</t>
+          <t>v1fv1YFg</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.484893524923903</v>
+        <v>1.460586108766236</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.268910924900751</v>
+        <v>0.2770257043471778</v>
       </c>
       <c r="D4" t="n">
-        <v>1.645403634370199</v>
+        <v>-1.202817453949981</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7632070243837995</v>
+        <v>1.631613246155598</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.141445094749495</v>
+        <v>1.652750648314044</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.7977897351710163</v>
+        <v>-0.5360747801075261</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6195431748141911</v>
+        <v>0.2820829880991219</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3830085568275531</v>
+        <v>-0.4568655460959077</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.499169893020418</v>
+        <v>0.05528261484633741</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2888844093278937</v>
+        <v>1.042180260008189</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6865969849765919</v>
+        <v>-0.7786631768891558</v>
       </c>
       <c r="M4" t="n">
-        <v>0.06381653397400083</v>
+        <v>1.01558166214053</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8597443634593122</v>
+        <v>1.05052219499676</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1982540662162228</v>
+        <v>0.04427818194334077</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1981963303326454</v>
+        <v>0.6221352858234753</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2817941069480826</v>
+        <v>-0.5068795337710538</v>
       </c>
       <c r="R4" t="n">
-        <v>0.08756376832895926</v>
+        <v>0.299373610794155</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3281418629242858</v>
+        <v>-0.1824208664051147</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9859812700892766</v>
+        <v>0.02101906274123</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4495257822428165</v>
+        <v>-0.02100641663299029</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5256247871986603</v>
+        <v>-0.1036557705086023</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.793641701443858</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.0948632398565</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.02378575712559158</v>
+        <v>0.698132606793789</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-0.4145680788099127</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-1.791761572696688</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.06334797939387229</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-2.058235487575891</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.4183553450414161</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.128150988365096</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-0.8803713568616914</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-1.155037823192254</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-0.4485261918105287</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-0.5869873562481713</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.474880490683448</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.6647488599661739</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-0.3266942555418161</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-0.3546753309857057</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>v3erq0f8</t>
+          <t>rZ0V2fos</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.504520286883804</v>
+        <v>1.460586108766236</v>
       </c>
       <c r="C5" t="n">
-        <v>1.424551233200182</v>
+        <v>0.6493029670714805</v>
       </c>
       <c r="D5" t="n">
-        <v>1.645403634370199</v>
+        <v>-1.29222919326476</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.225610161428886</v>
+        <v>1.631613246155598</v>
       </c>
       <c r="F5" t="n">
-        <v>1.552509244689785</v>
+        <v>1.635920238513152</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002105403720289837</v>
+        <v>-0.7818606884629347</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2055219499083804</v>
+        <v>0.03111124386989085</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2373881529933669</v>
+        <v>-0.4568655460959077</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2037482584238998</v>
+        <v>0.05528261484633741</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.4632815516416485</v>
+        <v>-1.931574355685057</v>
       </c>
       <c r="L5" t="n">
-        <v>1.043532077391487</v>
+        <v>0.8267139908890105</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3292285413158988</v>
+        <v>0.2814918542667702</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6425637223505661</v>
+        <v>0.9793002018853546</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1434661943215198</v>
+        <v>-0.6151237866749454</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6405116951960408</v>
+        <v>-0.5307419376452001</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.298822831641812</v>
+        <v>-0.01230913110648486</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8694016844920973</v>
+        <v>0.8788084296059911</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8140043086865982</v>
+        <v>-0.6391451517513056</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.05267552797811428</v>
+        <v>0.06858539697600113</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7469435599526005</v>
+        <v>-0.06857714483960801</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3020401691152</v>
+        <v>-0.1036557705086023</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.9074376204364879</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.690347615028854</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.06050687225820343</v>
+        <v>-0.05944148211613278</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-1.122040852293744</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.3378241871018784</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-1.066326641778479</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-0.8731650882152471</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-0.3771431649885848</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-0.2430632816844394</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-1.020846639568854</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-0.692175831613535</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-0.7531118310458891</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-0.6835938794242924</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>-0.5018619446858009</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-1.432473781938106</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-0.01846612535071925</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-0.4262779968146467</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>IgfnrK9E</t>
+          <t>QgE37zwQ</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.504520286883804</v>
+        <v>1.460586108766236</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.1825478544667079</v>
+        <v>1.218668192414532</v>
       </c>
       <c r="D6" t="n">
-        <v>1.645403634370199</v>
+        <v>-0.07622953858377449</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.494408592906343</v>
+        <v>1.631613246155598</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5598630845799519</v>
+        <v>1.635920238513152</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5443016373331964</v>
+        <v>-1.273432505173752</v>
       </c>
       <c r="H6" t="n">
-        <v>1.528626386281668</v>
+        <v>-0.4708322445885712</v>
       </c>
       <c r="I6" t="n">
-        <v>1.656525179450163</v>
+        <v>0.2478973019411075</v>
       </c>
       <c r="J6" t="n">
-        <v>0.06277166871052109</v>
+        <v>0.5474611689635186</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2867993218384049</v>
+        <v>-2.557895961387572</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6545245563827895</v>
+        <v>1.058258774703169</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9827854632313545</v>
+        <v>1.088378509027819</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5375513759067363</v>
+        <v>-0.4006259146481085</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1671344654468115</v>
+        <v>1.033381134870769</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7325948859123463</v>
+        <v>0.5068475634766076</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1616286114438752</v>
+        <v>1.216389213013304</v>
       </c>
       <c r="R6" t="n">
-        <v>0.37106228516151</v>
+        <v>-0.5118351355424161</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9827049295190485</v>
+        <v>0.6625190614853385</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3785133848856099</v>
+        <v>-0.3793309170680911</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6271518026939927</v>
+        <v>0.3793805457727062</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.7605590939661112</v>
+        <v>1.535351357618356</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.1511354103099895</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.2760722239945141</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.1688705282211591</v>
+        <v>1.777675683490427</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.1666970874328806</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-0.8811923167367639</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.3595116579823827</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-0.4372511574752032</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.09231223714306878</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.3250968768753764</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-0.3674883161069744</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-0.1627362546316778</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0.2683906373416538</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.5790819078949639</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.1072010860537351</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.04831413907149665</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-0.8874510850775537</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-0.06119441495266443</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>zZKrObIr</t>
+          <t>AoWGqXpJ</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.484893524923903</v>
+        <v>1.460586108766236</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.134237816995704</v>
+        <v>-1.409171309168781</v>
       </c>
       <c r="D7" t="n">
-        <v>1.645403634370199</v>
+        <v>1.148711290028688</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5194731682096183</v>
+        <v>1.631613246155598</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5224700545691703</v>
+        <v>1.652750648314044</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8602775040128666</v>
+        <v>-1.273432505173752</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7005610247419233</v>
+        <v>-0.4708322445885712</v>
       </c>
       <c r="I7" t="n">
-        <v>1.337631204184996</v>
+        <v>0.2478973019411075</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9476337541365616</v>
+        <v>0.5474611689635186</v>
       </c>
       <c r="K7" t="n">
-        <v>0.320722121961525</v>
+        <v>1.335482085117661</v>
       </c>
       <c r="L7" t="n">
-        <v>1.183202330945141</v>
+        <v>1.151905776156896</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4241262890474154</v>
+        <v>0.9558750632704894</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6432516656216264</v>
+        <v>-0.1816182858305399</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1654411312974193</v>
+        <v>1.304468610858287</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.7116647012744797</v>
+        <v>-0.280402883406288</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.6196270808710123</v>
+        <v>-0.08031256147286338</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3000034760381733</v>
+        <v>-1.380987363760171</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9284198783553465</v>
+        <v>0.9879351147944997</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2162859431649873</v>
+        <v>0.3349568686907176</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1088774958580459</v>
+        <v>-0.3349732227966655</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9056697062113068</v>
+        <v>0.5337358904296587</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.238419840835121</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.7660254325571049</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.1550663112744179</v>
+        <v>1.228434469030734</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-1.247939187879795</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-0.5749211276782871</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-1.733300232373681</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.02639204416114845</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-1.570879699456106</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-1.345887001396255</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-0.96843867212528</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.08631424816890608</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-0.1111634112111653</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>-0.390852821810891</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>-0.4052028134441173</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-0.9159958966370092</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.4809948427548838</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>-1.552726430133701</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hAFmNIXl</t>
+          <t>n3Fa8GNJ</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.484893524923903</v>
+        <v>1.460586108766236</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.3980248271147825</v>
+        <v>-1.004046052674687</v>
       </c>
       <c r="D8" t="n">
-        <v>1.645403634370199</v>
+        <v>-1.327993888990671</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.00694088055798</v>
+        <v>1.631613246155598</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3222117840672188</v>
+        <v>1.652750648314044</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4346773570565757</v>
+        <v>-0.04450296339670891</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7005610247419233</v>
+        <v>0.784026476557584</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3021083324752274</v>
+        <v>0.2478973019411075</v>
       </c>
       <c r="J8" t="n">
-        <v>1.339027026053445</v>
+        <v>0.5474611689635186</v>
       </c>
       <c r="K8" t="n">
-        <v>0.09785813352610538</v>
+        <v>0.5696384306651532</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2055105560695598</v>
+        <v>0.7814341220542419</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1538670364650023</v>
+        <v>-0.4403552756052475</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2023105051829045</v>
+        <v>-0.07478529616343284</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3452099860330272</v>
+        <v>-1.545613231280748</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2976080827893575</v>
+        <v>2.107699936635969</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.6370806773693891</v>
+        <v>-2.686080370511811</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.5981833606652645</v>
+        <v>-0.8884677677701099</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1171984223945263</v>
+        <v>1.187751989633458</v>
       </c>
       <c r="T8" t="n">
-        <v>0.313327241953418</v>
+        <v>1.091261583023573</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2880582923001621</v>
+        <v>-1.091347801281881</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1093599523900017</v>
+        <v>-0.004322005167574608</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.667341680713789</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.2152023855226777</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.1391709977458838</v>
+        <v>1.031465205914154</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-1.143487179300688</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.01136265490080136</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-0.8009838608410148</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-0.8599821949319129</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-1.000324309090743</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-0.5730748259955963</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-0.1275655428208402</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-0.02148913804784683</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.2080125368299405</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.5335593486794388</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-0.3864257334437438</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0.03611563016432098</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.1830333690373639</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>-1.040624041737406</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>QNDeLd21</t>
+          <t>WfXCpDVC</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.484893524923903</v>
+        <v>1.460586108766236</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.448475068774147</v>
+        <v>-1.244931340319824</v>
       </c>
       <c r="D9" t="n">
-        <v>1.611714503092384</v>
+        <v>1.130828942165733</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5194731682096183</v>
+        <v>1.631613246155598</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1166555190503838</v>
+        <v>1.635920238513152</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5268907222304389</v>
+        <v>-1.027646596818343</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3045297648750889</v>
+        <v>-0.2198605003593402</v>
       </c>
       <c r="I9" t="n">
-        <v>1.402351383666856</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1295889116460519</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1742686438468205</v>
+        <v>-0.4645361864416174</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.4680104444002852</v>
+        <v>0.1189153328343017</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1567582975244261</v>
+        <v>-1.902507726798063</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3269113665222589</v>
+        <v>-0.8955956427486329</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.414922634667242</v>
+        <v>-1.167955740163003</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.614153307729299</v>
+        <v>0.3663205995027821</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.473699290346661</v>
+        <v>-1.036776393768807</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.704410797852548</v>
+        <v>0.4216987392099869</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.27967086761495</v>
+        <v>-0.5566810446749101</v>
       </c>
       <c r="T9" t="n">
-        <v>-3.089618589723184</v>
+        <v>-0.2866177482836515</v>
       </c>
       <c r="U9" t="n">
-        <v>1.210279365815468</v>
+        <v>0.2866588125474704</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.983424628771395</v>
+        <v>2.63630059014808</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.4072377460141998</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.4529774848005866</v>
       </c>
       <c r="Y9" t="n">
-        <v>-1.223478498058372</v>
+        <v>-0.5375986343372002</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-1.215362124825985</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-0.3106787971235744</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-0.1606091646326548</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-0.7966461193347986</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.2241606477570799</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-0.7612663155670438</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.6164402291059662</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-1.069720580679903</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-0.6555690955584205</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.09147995826109896</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-0.03334449445084129</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-0.9952822202419309</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>-0.1117660894362876</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>-0.7635571443815176</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>W0EiMxme</t>
+          <t>xYX8ogG6</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.504520286883804</v>
+        <v>1.460586108766236</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.6763492501185456</v>
+        <v>0.03614041670204072</v>
       </c>
       <c r="D10" t="n">
-        <v>1.645403634370199</v>
+        <v>-0.8541116706223458</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.494408592906343</v>
+        <v>1.647624247492205</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5489070285075773</v>
+        <v>1.635920238513152</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3817997630407942</v>
+        <v>-1.273432505173752</v>
       </c>
       <c r="H10" t="n">
-        <v>1.744643437118123</v>
+        <v>-0.4708322445885712</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6292394214926315</v>
+        <v>-1.161628394132923</v>
       </c>
       <c r="J10" t="n">
-        <v>1.754490745271066</v>
+        <v>-0.4368959392708438</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9692841072029773</v>
+        <v>-0.09029067583115649</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.2531596593041694</v>
+        <v>0.5221039641823845</v>
       </c>
       <c r="M10" t="n">
-        <v>0.07220469690444888</v>
+        <v>0.3441178609679947</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8598815024448834</v>
+        <v>1.912308311644755</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2154996548495263</v>
+        <v>0.4985328714359376</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3081727029162967</v>
+        <v>0.9515287782430969</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1156637882182539</v>
+        <v>-0.04321978127302032</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.8372146471300851</v>
+        <v>0.5504620322792838</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4792562471504822</v>
+        <v>-0.5915697053610774</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2730576672242057</v>
+        <v>0.5632752730176176</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.270882121472861</v>
+        <v>-0.5490414997264437</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2352715681629826</v>
+        <v>-1.552273181731924</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.3080480744096685</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.526589411856456</v>
       </c>
       <c r="Y10" t="n">
-        <v>-1.388225346162075</v>
+        <v>0.6223751979027967</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-1.008930899368009</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.2376855146909636</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-0.555227052663119</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-0.1592026537270805</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.1214751895831562</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-0.0744842627587585</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-0.9320124885449378</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-0.3852187546592311</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-0.3898690810435704</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>-0.7221463858387392</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-0.4897675244446649</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-0.6213627534417276</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-0.2455277334384279</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>-1.387143578370024</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>fiHVGBod</t>
+          <t>QcU4nZ00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.484893524923903</v>
+        <v>1.460586108766236</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.2005042688540474</v>
+        <v>-0.6974647774899675</v>
       </c>
       <c r="D11" t="n">
-        <v>1.645403634370199</v>
+        <v>1.1844759857546</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5194731682096183</v>
+        <v>1.647624247492205</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2194863515800309</v>
+        <v>1.652750648314044</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9489442012954269</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9389131718839995</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1.240550934962205</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.044253223722055</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7266529580403259</v>
+        <v>0.4158586543056738</v>
       </c>
       <c r="L11" t="n">
-        <v>1.726364428098242</v>
+        <v>0.2761519493753446</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7440425478970253</v>
+        <v>1.269005096776615</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.2371675514037</v>
+        <v>-0.6944166362326525</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1718196890769035</v>
+        <v>-1.01809165638612</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.7500630611845774</v>
+        <v>-0.9136618725830107</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3593049244054501</v>
+        <v>0.3238441894545897</v>
       </c>
       <c r="R11" t="n">
-        <v>0.02336923763345983</v>
+        <v>-0.5697786174235997</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.044336704472095</v>
+        <v>0.4341569188122432</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2714686068195774</v>
+        <v>0.1914650937491585</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5401602614391359</v>
+        <v>-0.1914681927067024</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.205857766076372</v>
+        <v>-0.004322005167574608</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.7852387546085282</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.11959428031569</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.1031459052571811</v>
+        <v>0.3382849145615762</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-0.8396229907240981</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-0.2474452002821114</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.4311570661095778</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-1.107557154732087</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-1.250276717658128</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-1.664784370612197</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.5406899463025984</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.1395510633083816</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>2.526993073998827</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>2.115268707565245</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-0.209796997560998</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.7321805425092104</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1.564072303902617</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.2589054006589695</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>4nbBt7Y9</t>
+          <t>rZv0mFof</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.504520286883804</v>
+        <v>1.499979832092311</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9217716303546748</v>
+        <v>-0.1609475459167078</v>
       </c>
       <c r="D12" t="n">
-        <v>1.645403634370199</v>
+        <v>1.381181812247112</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.713077873777248</v>
+        <v>1.647624247492205</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.624228974529678</v>
+        <v>1.635920238513152</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5765440727086727</v>
+        <v>-0.2902888717521175</v>
       </c>
       <c r="H12" t="n">
-        <v>1.140595757927295</v>
+        <v>0.5330547323283529</v>
       </c>
       <c r="I12" t="n">
-        <v>1.725952281076158</v>
+        <v>2.362185846052153</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1424715075907843</v>
+        <v>2.023996831315062</v>
       </c>
       <c r="K12" t="n">
-        <v>1.021151799901416</v>
+        <v>-0.465065230137702</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.4462839605141609</v>
+        <v>0.3739153025413228</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.195197822281766</v>
+        <v>-0.1371135589466825</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.190602259376259</v>
+        <v>0.05341429143709552</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1340092206803797</v>
+        <v>0.4106126089534994</v>
       </c>
       <c r="P12" t="n">
-        <v>0.02041224823106476</v>
+        <v>0.7868320320332856</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.3119875048232637</v>
+        <v>0.51317192172462</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6086856011235645</v>
+        <v>-1.299866489126514</v>
       </c>
       <c r="S12" t="n">
-        <v>0.009140883095114157</v>
+        <v>1.084989025430565</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4907321188176731</v>
+        <v>1.321165531824964</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5008277455242902</v>
+        <v>-1.321272987613865</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3829894835961346</v>
+        <v>1.436017592277328</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.2450228902324615</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.8404609794536492</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.4165877762777097</v>
+        <v>0.8496474245757734</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-1.423488455771094</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-1.86540425534513</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.4921939885318537</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.733527726086664</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-0.5451815273976329</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-0.3301693353327712</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.2604639417489439</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.1576628388841668</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.520306900838686</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.162310186232142</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-0.07883959407177589</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0.5223907606918949</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-0.005869445695628527</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0.01099181958132139</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>b9cFuRmG</t>
+          <t>4rtdleWm</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.524147048843706</v>
+        <v>1.499979832092311</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.4878068990514803</v>
+        <v>0.9887322360259917</v>
       </c>
       <c r="D13" t="n">
-        <v>1.645403634370199</v>
+        <v>-0.5143470612261882</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.250674736732162</v>
+        <v>1.647624247492205</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4122941625731199</v>
+        <v>1.635920238513152</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.3455895790299575</v>
+        <v>-1.027646596818343</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.766221419209315</v>
+        <v>-0.2198605003593402</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.8628548981982617</v>
+        <v>-1.161628394132923</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2440063707511888</v>
+        <v>-0.4368959392708438</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.4433829812456288</v>
+        <v>-1.727892532692369</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4227753949308</v>
+        <v>-0.2847009714189503</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.5939583770786898</v>
+        <v>-0.4040981138308536</v>
       </c>
       <c r="N13" t="n">
-        <v>0.03483306962432298</v>
+        <v>-0.3739176672313322</v>
       </c>
       <c r="O13" t="n">
-        <v>0.8255619043350976</v>
+        <v>0.85021392136569</v>
       </c>
       <c r="P13" t="n">
-        <v>1.367166277797772</v>
+        <v>-0.3989845406773519</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.4082999123438334</v>
+        <v>0.6059038722242265</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9261631738576426</v>
+        <v>0.8788084296059913</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8698757775832962</v>
+        <v>-0.9816883657609489</v>
       </c>
       <c r="T13" t="n">
-        <v>0.09041197467001667</v>
+        <v>0.03687450748615405</v>
       </c>
       <c r="U13" t="n">
-        <v>0.007952479933744145</v>
+        <v>-0.03686332603519654</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3611594827282895</v>
+        <v>-0.004322005167574608</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>-0.7273656656444633</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>0.3505077708910581</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.2481490653127253</v>
+        <v>-1.120045206590023</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0.09427302433484439</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-0.6179075711602766</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.262236456183452</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-1.873746605137085</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.7951880940295881</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>-0.556761477947848</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.6582777654024599</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-0.9069896229673668</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.8682791146083182</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.1026127008398445</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.496982660114069</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.9292352848408216</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.8251596211823874</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.9467905950470558</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>G0IRHiWk</t>
+          <t>z9yhkyHs</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.524147048843706</v>
+        <v>1.460586108766236</v>
       </c>
       <c r="C14" t="n">
-        <v>1.487398683555871</v>
+        <v>-1.14638735901045</v>
       </c>
       <c r="D14" t="n">
-        <v>1.645403634370199</v>
+        <v>-1.471052671894316</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.250674736732162</v>
+        <v>1.631613246155598</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.158555744642821</v>
+        <v>1.652750648314044</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1444954386772868</v>
+        <v>-1.273432505173752</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1271824330155303</v>
+        <v>-0.4708322445885712</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4197813860786102</v>
+        <v>-0.4568655460959077</v>
       </c>
       <c r="J14" t="n">
-        <v>1.321459849765174</v>
+        <v>0.05528261484633741</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6072615356642077</v>
+        <v>1.082916624606727</v>
       </c>
       <c r="L14" t="n">
-        <v>0.09687813663893971</v>
+        <v>-0.2281011353754897</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5327261263101835</v>
+        <v>-1.426550075868751</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2133265908926857</v>
+        <v>0.3739132604384161</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4539181050073154</v>
+        <v>-0.4411149338451197</v>
       </c>
       <c r="P14" t="n">
-        <v>1.369709487670598</v>
+        <v>1.729720904084453</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.5714793130003447</v>
+        <v>-1.573296964516531</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9341789839705305</v>
+        <v>0.1950753434080244</v>
       </c>
       <c r="S14" t="n">
-        <v>1.268634118170913</v>
+        <v>0.05735938340163577</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1475651349973979</v>
+        <v>-0.0146556879348481</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8886738447345787</v>
+        <v>0.01467162952197275</v>
       </c>
       <c r="V14" t="n">
-        <v>0.815705008902823</v>
+        <v>-0.004322005167574608</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.545942312574978</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.8901654858910036</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.5105861588208792</v>
+        <v>0.4519210278980643</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0.7060350629155234</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-0.4082110808618439</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-1.946781022488244</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-0.9468848535043248</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-1.566988755822074</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-2.365193837067639</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-3.848838322010332</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-0.9886139766262367</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.1696901059243996</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>-1.10972122668279</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-0.9437648521716656</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-1.814491935167119</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-0.8432242430432729</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-1.875428833599006</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
+          <t>rRCPxg8F</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.499979832092311</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.8463909296902289</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.452711203698935</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.631613246155598</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.635920238513152</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.6928547616695169</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.536941709245277</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.657422998015138</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.531818277197881</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-1.3903626545902</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.638223328447205</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-0.4288189059497582</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.643539377217305</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-0.3848564325542738</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.1421619111548833</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-0.807154421103114</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.664264517328703</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-1.463786222515262</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.223767799820435</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-1.223866258428887</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-1.643329133294532</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.5472937108524405</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.22246703453629</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-1.682814529780251</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-0.9674788098821838</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-1.514188188518056</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.335809620124008</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-0.7554451575369974</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.704583158212262</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.5987878652601087</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-1.068011493723172</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.7599266287033261</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0.4482221791187261</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>-0.4650210552226735</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.308772759377643</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0.6916573160145023</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-0.903700057288095</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0.5493906997202336</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>xlCTyDNL</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.480282970429273</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.6055056420450919</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.6574058441298335</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.631613246155598</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.652750648314044</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-1.027646596818343</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.2198605003593402</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-0.4568655460959077</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.05528261484633741</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.4005825175812224</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-0.5471183930749971</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.1661281577118812</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.01780329488139336</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.189073266350087</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0.3001664929514652</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.6174953660366777</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-0.03669858411671018</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0.2737657234743527</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.2291217750183526</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0.2291283525369417</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.542013704208078</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.172994108315651</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.648249958477235</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.7360113112392852</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-0.5985825603465225</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-0.765861357879433</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-1.377017850872467</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.8549349113567295</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-0.229461342713063</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0.8128947823922354</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.03698042334999763</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0.9383624157135386</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>-0.6832253184721121</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>-0.9619180582473404</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.2631306977383049</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>-0.01116667775163748</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0.5711569599106765</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>-0.957086233807812</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>YakQgH8Q</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.460586108766236</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.1499982146601106</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.148711290028688</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.647624247492205</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.652750648314044</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.2902888717521175</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.5330547323283529</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-1.161628394132923</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-0.4368959392708438</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-0.5791270510136075</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.3286354337065542</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.18989856199612</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-0.3952842651647535</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.7183335276420326</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-0.4450996296160988</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.6615430425239908</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-0.8710847232057546</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.5825923115497552</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.03370341853716883</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-0.03369194415475488</v>
+      </c>
+      <c r="V17" t="n">
+        <v>-0.5506577145432272</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.8932819274837422</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.7660254325571049</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.7738900156847812</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-1.86920965510587</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-0.8582653552477159</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-0.6931680423952837</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-0.4558035019259735</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-0.3027459607913325</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-0.6879265086233887</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-1.520506069855454</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>-0.3084535884720424</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>-0.7547493765200889</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>-0.5576233849101205</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>-0.1403213729530031</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>-0.7167424270834101</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0.1248031394608712</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>-0.5478775840688708</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>jy0LfcgK</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.480282970429273</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.6493029670714805</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.9435234099371241</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.631613246155598</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.635920238513152</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-1.273432505173752</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.4708322445885712</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.2478973019411075</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.5474611689635186</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-1.346452027815153</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.2504247511737713</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-0.0316381792393556</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.290087080916938</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-0.7683181834246479</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0.3510727599617702</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.2293559520137028</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.7899617573881762</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-0.9265008479482844</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.7126556077284171</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.712736027523624</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-1.09699342391888</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-0.04309223743477715</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.7159186374740935</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-0.7068229762755205</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-0.9023155249932623</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-0.8495731747479269</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-0.196152529405747</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.09699142034048863</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.5952590154944738</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.5352383561882601</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-0.3004510706299659</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>-0.08478786845037138</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>-1.310551623521167</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>-1.339741669359194</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>-0.1707938517685748</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>-1.056800770597196</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>-0.3996772435652914</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0.2324752034964024</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>xYeHewvE</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.480282970429273</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-1.354424652885796</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.1830645054290826</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.631613246155598</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.652750648314044</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-1.027646596818343</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.2198605003593402</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-1.161628394132923</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-0.4368959392708438</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-0.6280106885318525</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-0.2360531784559762</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.30422633964317</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.1116868312555174</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.555334163449338</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-0.8212071082334128</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.07837484379374</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-0.2085975803642219</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.1620253654601376</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-0.1562736375883702</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.1563026612280381</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.088349413583731</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-0.1061174216119842</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.1069005265023681</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.5328437146679876</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-0.1380644515091167</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-0.2956718897547522</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-0.9059171697734343</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.501420533391454</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-0.3958193293218054</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>-0.1187499089293596</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.2887710343521574</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0.2234868478328871</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>-0.6192036942416024</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>-0.461732364253035</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>-0.1764725149742649</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>-1.294569040959758</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0.1612454984757698</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>-0.167214711362634</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>OU7ZWg1D</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1.499979832092311</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.03614041670204072</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-1.37269975864806</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.647624247492205</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.635920238513152</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-1.765004321884569</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.9727757330470331</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-1.161628394132923</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-0.4368959392708438</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-1.11351408842897</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-0.4209147917152797</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.128458379244979</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.1408231011647286</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.3246905342547536</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.06216634871011836</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.7559610284872268</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.6470345020812568</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-0.5249640804147578</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.1883660750035599</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-0.175395052721739</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-0.5506577145432272</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-0.4752649289356316</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.4181764498879169</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-0.1462181504821781</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-1.007377270632856</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-1.018170319470904</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-0.7379947766602336</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>-0.613114679408775</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.6142643005095342</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0.6326729466248602</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>-0.8185196080443878</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>-0.3891648453768931</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>-0.3580801191441388</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>-1.121800640815714</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0.21252147750637</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>-0.1436865185470765</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>-0.5819828668803343</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>-0.02166924227457051</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>IHxZYFW0</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1.460586108766236</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.02519108544544358</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.2282294954188976</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.647624247492205</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.635920238513152</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-2.256576138595387</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-1.474719221505495</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-1.161628394132923</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-0.4368959392708438</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.245862083000877</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-0.07888338580636492</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.1703660077894074</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-0.6588056396769506</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-0.1022555888607225</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-1.321286319452292</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-0.01230913110648486</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.3225510035466284</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-0.1938389735387692</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-0.6131987270557137</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.6132699594552413</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-1.643329133294532</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.05894853694736965</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.05276558330488136</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.09207333566585131</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-0.980125060769274</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-1.387713541013862</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-0.7438293369378837</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>-0.689831667249987</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>-0.4269049776627365</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>-0.5075040208023115</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>-0.06170438936974391</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>-0.07214186896715692</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0.7274289917953722</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>-0.3218976144166324</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>-0.1132475973564871</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0.21729161223968</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0.4216870322604273</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>-0.4350952413786774</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>pv9VXZo7</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1.460586108766236</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-1.29967799660281</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.211299507549033</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.631613246155598</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.652750648314044</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-0.2902888717521175</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.5330547323283529</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.9526601499781225</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.0396397230807</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.292786653183295</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-0.6634053289461076</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-0.6958505480570127</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.5662126418392089</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-0.2268092940441773</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.6550746350654374</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-0.8778073357694808</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.06759968326942034</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-0.41078300907821</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.3349568686907176</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-0.3349732227966655</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-0.5506577145432272</v>
+      </c>
+      <c r="W22" t="n">
+        <v>3.126174166904829</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-0.8851223075915756</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>-1.695801514161563</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.2228377494866959</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.2897031193118635</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>-0.4103040720120749</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0.7856818076514827</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>-0.3857641535195657</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>-0.1691768197647332</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0.9280162535030884</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0.460090044604693</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>-0.665686483716183</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>-0.4900895068317522</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>-0.08759759354818009</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>-0.4745039304362446</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>-0.01846612535071925</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>-0.2280494933795678</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>UN8LwZh9</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1.480282970429273</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.361009498750294</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-0.6574058441298335</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.647624247492205</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.652750648314044</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.5360747801075261</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.2820829880991219</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-0.4568655460959077</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.05528261484633741</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.449543905993566</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-0.4905185570315357</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-0.2840256949676022</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.5519682432169278</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.117545067345372</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.1939237456779671</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-0.3214156327718404</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.1950753434080243</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-0.3194381520089718</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.3912225006267832</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.3912732278243599</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.542013704208078</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.655986284947881</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0.9459921460634119</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0.5466177890118045</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-0.3210473914272665</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-0.5260346585574085</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>-1.386460395977134</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.764387148731166</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>-0.80615275614435</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0.2561295834403474</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>-0.0464151930328829</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0.7513308265395638</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>-0.1542811790057136</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0.1300412377320707</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0.1462166792754468</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>-0.3042865547296901</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>-0.01846612535071925</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>-1.004657440363478</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>vRwVZeHf</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1.460586108766236</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1.087276217335366</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-0.8541116706223458</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.631613246155598</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.635920238513152</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-1.273432505173752</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.4708322445885712</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.9526601499781225</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.0396397230807</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.04969428615290948</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.2855072941759169</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.362614496266867</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.7016962969170397</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.3831375269277376</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-0.5374795318083294</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.8956912175354977</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.634158172774327</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.3473490805579056</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.1687057476724579</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.1557620847711452</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-2.189664842670185</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-0.1646408069193912</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-0.05381258611517062</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0.374441859714095</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-0.274093278542586</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.2394644933671027</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.5204799259971108</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0.6598727675582747</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>-0.1509115833484221</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0.5038915425676047</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>-0.4416256727033798</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0.5172334178743991</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>-0.07663441512751035</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0.2092830120909182</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>-0.5185125662185737</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0.1803198485012025</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0.412176755535375</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>-0.6512238780011977</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>88KCueOd</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1.460586108766236</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.174870867388143</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.5764761584141072</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.631613246155598</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.635920238513152</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.675998395091151</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.540828686162201</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.362185846052153</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.023996831315062</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.05362794769247212</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.5509184261681463</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-1.716889893402402</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.5875792397726297</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.6737372949965706</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.7967138368058747</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-0.6336131994538496</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.180114535388146</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.7190719016868888</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.3603255802825953</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.3603442778401946</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-0.5506577145432272</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-0.7333680641375323</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.4100562084082938</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>-1.498832251044984</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-0.4206261005262469</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-0.242445394378151</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.01293430879646798</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.371397920020206</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.08919409541292897</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>-0.01367938698978061</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>-0.1298108094157634</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0.1218221609542514</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>-0.6474371936361619</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>-0.2862072938407841</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0.0424290989560156</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>-0.7678972717786806</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>-0.608089210612115</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0.08696201264597442</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>p4vRzx2l</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1.460586108766236</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.4894274836146219</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-1.158111584292592</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.631613246155598</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.635920238513152</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-0.04450296339670891</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.784026476557584</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.2478973019411075</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.5474611689635186</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-0.2939724988238439</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.2874719165840366</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.010590416493666</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.6303168424323888</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.02962480486293475</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-0.3166361675724468</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-0.03085552120640614</v>
+      </c>
+      <c r="R26" t="n">
+        <v>-1.925656093443297</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1.564549525044066</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.5513624925505122</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.5514280127866392</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.542013704208078</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-1.830306388745606</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-1.316848479591532</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0.8193444610193766</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-0.703126878873597</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-0.3185748665090395</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>-1.196917040576059</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.005424472072442</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>-1.193909077937194</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.419936418696227</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0.4164304778921062</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0.3485222299211759</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>-0.5471242368125492</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0.5458741438687726</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>-0.368649470313676</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0.02240873577196063</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0.06858383181078846</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>-1.650931824188136</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>QJcftbvR</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1.460586108766236</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.3799341710486505</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-1.471052671894316</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.647624247492205</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.652750648314044</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-0.5360747801075261</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.2820829880991219</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.2478973019411075</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.5474611689635186</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.5492702483658845</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-0.4287732813477603</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-0.968203046372717</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-1.014915605233973</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.04427818194334047</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.3685022966603665</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-1.100364016968537</v>
+      </c>
+      <c r="R27" t="n">
+        <v>-0.05987597686918378</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.02256736653394775</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.9715317782909872</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.9716361119450926</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.542013704208078</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.775634505964657</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-1.182864495177752</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>-1.074590761255428</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-0.3741637085207091</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.04492814380164605</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>-3.035996086506549</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0.1713408064092825</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>-2.464610127435719</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>-1.240444080081316</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>-3.807140513818892</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>-1.010902340414044</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0.8582231198550112</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>-0.688669125267002</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>-0.6185658133315399</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>-0.5296776503153264</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>-0.2717530115400658</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>-3.254004656901208</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>naJGvFw3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1.460586108766236</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1.437654817546474</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1.014593681056521</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.631613246155598</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.635920238513152</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-0.5360747801075261</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.2820829880991219</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-2.571154090206953</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-1.421253047505206</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.8629402557746243</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-0.3299808402537197</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.08184202839218681</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.9508114046407932</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-0.358689687767834</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.12145717734565</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-0.3492352179217224</v>
+      </c>
+      <c r="R28" t="n">
+        <v>-0.3959481717800488</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.502665561614172</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.4205762703133042</v>
+      </c>
+      <c r="U28" t="n">
+        <v>-0.4206005335685759</v>
+      </c>
+      <c r="V28" t="n">
+        <v>-0.004322005167574608</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.7852387546085282</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.7226855053737792</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.031465205914155</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-1.868168269152327</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.5480887724588086</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>-2.056503396604502</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.122573712641218</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>-1.80541556558673</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>-0.06540117373106288</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>-0.1923575217029255</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>-0.42565843654293</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>-0.858992213248046</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>-0.2664325256318418</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>-0.8691828992083381</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>-0.5069281474353803</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>-0.06390789710795783</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>-0.6103821375969777</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>W0zNyInr</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1.460586108766236</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8463909296902289</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-1.202817453949981</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.631613246155598</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.652750648314044</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-0.5360747801075261</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.2820829880991219</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-1.161628394132923</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-0.4368959392708438</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-1.137797194079266</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.8026039308601085</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.412762388850932</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.555180889043284</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.7434536026370152</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.4517917940293277</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>-0.9771629970190595</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.4152605745565222</v>
+      </c>
+      <c r="S29" t="n">
+        <v>-0.1110576968197722</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.566245406310784</v>
+      </c>
+      <c r="U29" t="n">
+        <v>-1.566375501516532</v>
+      </c>
+      <c r="V29" t="n">
+        <v>-1.643329133294532</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.339560666498272</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.564870550260393</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0.6808166276187049</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-1.172021157780643</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-2.09641066161431</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>-0.4551264347283738</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>-1.320279957820623</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.5335029228951881</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.569913003744088</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>-0.8803713568616914</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>-0.6661979389367781</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>-1.271800720290645</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>-1.18497387918198</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0.6311881905940238</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>-0.0764693730626511</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>-0.3266942555418161</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>-0.1639099712914155</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>xbHaKGH7</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1.460586108766236</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1.10917487984856</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.6480055498659298</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.631613246155598</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.635920238513152</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-0.2902888717521175</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.5330547323283529</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-1.161628394132923</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-0.4368959392708438</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.439652394537092</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-0.3737638539203966</v>
+      </c>
+      <c r="M30" t="n">
+        <v>-1.797409044875405</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.006796259582358252</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-0.7003797987791278</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.3074147762480001</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>-0.07356841961834573</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.27282410639804</v>
+      </c>
+      <c r="S30" t="n">
+        <v>-1.244304829835009</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0.5541944273909787</v>
+      </c>
+      <c r="U30" t="n">
+        <v>-0.5542310337126195</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.542013704208078</v>
+      </c>
+      <c r="W30" t="n">
+        <v>-0.2491745856967592</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0.2720121032547024</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>-1.385884841425686</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-0.3201267225471706</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-1.410912162121363</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2.352110166866468</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0.1820425089273958</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.493020867568195</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.133473349204358</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.647712701071019</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>-0.1948992445086559</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1.555917774538494</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.492502774350965</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0.8736083988702414</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>2.318563865794844</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0.04558964807329279</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.486479766783199</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>IgfnrK9E</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1.480282970429273</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1.218668192414532</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-0.2103471475559419</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.631613246155598</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.635920238513152</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-1.519218413529161</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-0.7218039888178022</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-2.571154090206953</v>
+      </c>
+      <c r="J31" t="n">
+        <v>-1.421253047505206</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-0.1169544781138355</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.3267643647464397</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.8926840098922613</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-0.7449195040752853</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.026054446330566</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.5014574881461049</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.2653247085711253</v>
+      </c>
+      <c r="R31" t="n">
+        <v>-1.195568221740383</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1.564549525044066</v>
+      </c>
+      <c r="T31" t="n">
+        <v>-0.7171239603383494</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0.7172047929006086</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.542013704208078</v>
+      </c>
+      <c r="W31" t="n">
+        <v>-1.393631898374949</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0.08930666996318497</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>2.295925230676533</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0.5882665724762903</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-1.541802195328287</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>-0.6996629979570972</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0.5287675654889397</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>-0.7003307858618673</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0.001727254722978689</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>-0.2664522103142141</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0.6317019673452986</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0.642333741545523</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>-0.01250400617116833</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>-0.02501976250130358</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0.3838850692836088</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>-0.2257911635863218</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>-0.7065005104392005</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>YyTMIXGq</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1.460586108766236</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.6646167837201761</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-1.29222919326476</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.631613246155598</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.635920238513152</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-0.7818606884629347</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.03111124386989085</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-0.4568655460959077</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.05528261484633741</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-1.951942537984326</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.3451008405555603</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-0.1065068639423249</v>
+      </c>
+      <c r="N32" t="n">
+        <v>-0.9152048148780071</v>
+      </c>
+      <c r="O32" t="n">
+        <v>-0.4978967700316939</v>
+      </c>
+      <c r="P32" t="n">
+        <v>-1.150001703394089</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>-0.1112232116393988</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.3083870413090057</v>
+      </c>
+      <c r="S32" t="n">
+        <v>-0.08219525934303376</v>
+      </c>
+      <c r="T32" t="n">
+        <v>-0.1121666731161288</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0.1121916223455389</v>
+      </c>
+      <c r="V32" t="n">
+        <v>-0.5506577145432272</v>
+      </c>
+      <c r="W32" t="n">
+        <v>-2.20795729393443</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.03787847392557243</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>-0.2564107452327123</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-0.5514447786701204</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.2430823918654167</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.2292534968829236</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>-2.062923497323306</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.05952513223973029</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>-0.1819638993059476</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>-1.020846639568854</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>-1.471657160037806</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0.4130691294131728</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0.01633352151383427</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>-0.2653030348121282</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0.1728089538352051</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>-0.01846612535071925</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0.1994556543025889</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>nTbjsvPK</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1.460586108766236</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-1.244931340319824</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-0.07622953858377449</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.631613246155598</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.635920238513152</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.184426578380334</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2.038885197703739</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-1.161628394132923</v>
+      </c>
+      <c r="J33" t="n">
+        <v>-0.4368959392708438</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-0.7094834177289274</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.9399136629759325</v>
+      </c>
+      <c r="M33" t="n">
+        <v>-0.3268750679737034</v>
+      </c>
+      <c r="N33" t="n">
+        <v>-0.551972650009843</v>
+      </c>
+      <c r="O33" t="n">
+        <v>-0.2121559169637704</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.1033405352625707</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.4358952963082814</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.271536473467347</v>
+      </c>
+      <c r="S33" t="n">
+        <v>-1.394008901142927</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0.3738027083157799</v>
+      </c>
+      <c r="U33" t="n">
+        <v>-0.3738226508320691</v>
+      </c>
+      <c r="V33" t="n">
+        <v>2.181020832335036</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2.171792806507106</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.3877255443393303</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>-0.7791368665805581</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-0.9719602896518472</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-1.038992310371922</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.2996158207837178</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>-1.108013212720559</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.1451400991938296</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0.1081847669927557</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.7857539218734326</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>-0.9353563083303457</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>-0.9724937273251237</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0.7097267931376784</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>-0.005990195690846376</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>-0.8878562957359272</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>-0.3230465601893191</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>-0.3244042732817394</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>v3erq0f8</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1.480282970429273</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.2770257043471778</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1.39012298617859</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1.631613246155598</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.635920238513152</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-2.256576138595387</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-1.474719221505495</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-1.866391242169938</v>
+      </c>
+      <c r="J34" t="n">
+        <v>-0.9290744933880251</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-0.2002788602472077</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.4109624679515888</v>
+      </c>
+      <c r="M34" t="n">
+        <v>-0.3590120977282796</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.1175140852373594</v>
+      </c>
+      <c r="O34" t="n">
+        <v>-1.01809165638612</v>
+      </c>
+      <c r="P34" t="n">
+        <v>-0.2935786231030734</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>-0.1823177070224304</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.7049779839624404</v>
+      </c>
+      <c r="S34" t="n">
+        <v>-0.5706365089493768</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0.8486732784262425</v>
+      </c>
+      <c r="U34" t="n">
+        <v>-0.8487370874281334</v>
+      </c>
+      <c r="V34" t="n">
+        <v>-0.004322005167574608</v>
+      </c>
+      <c r="W34" t="n">
+        <v>-2.428045238680236</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0.05276558330488136</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>-1.013984834142634</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-0.3572411867758353</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-0.3755167573217803</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.476582230059461</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>-1.145535206496539</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.897405884240954</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>-0.1256085932273676</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>-0.0464151930328829</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>-0.1927959920942039</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0.7345468242813374</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0.1866380432762249</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0.4697242362194179</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.092986795969704</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>-0.01846612535071925</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0.9320615209307933</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>W0EiMxme</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1.480282970429273</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-1.004046052674687</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-0.7021117137872227</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.631613246155598</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.635920238513152</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-1.519218413529161</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-0.7218039888178022</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-3.275916938243968</v>
+      </c>
+      <c r="J35" t="n">
+        <v>-1.913431601622388</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.3007784243148046</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-0.1694431234759029</v>
+      </c>
+      <c r="M35" t="n">
+        <v>-0.352302168438863</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.164477383975007</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.05893155902374677</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.979236474592317</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>-1.485201611541906</v>
+      </c>
+      <c r="R35" t="n">
+        <v>-0.5060407873542977</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.873754043457952</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0.7416490263980072</v>
+      </c>
+      <c r="U35" t="n">
+        <v>-0.7417029489632432</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.088349413583731</v>
+      </c>
+      <c r="W35" t="n">
+        <v>-0.5352889138663059</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0.968322810132375</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0.9632835379122615</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-0.9855976974381878</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-0.3668358507266645</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>-0.6838527205657003</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0.1415146040493191</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.08565345464231756</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0.3042652304977658</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>-0.3794844547712812</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>-0.4392030957457713</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>-1.027256074026591</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>-0.4786370900424211</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>-0.04272013205646652</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>-0.4228697625343149</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>-1.219793436389483</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>-0.6692158520298569</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>QNDeLd21</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1.460586108766236</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-1.22303267780663</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-1.471052671894316</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.631613246155598</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.652750648314044</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-0.5360747801075261</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.2820829880991219</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-1.161628394132923</v>
+      </c>
+      <c r="J36" t="n">
+        <v>-0.4368959392708438</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.2193056951177296</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.7567360117807318</v>
+      </c>
+      <c r="M36" t="n">
+        <v>-1.5247740232212</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-1.143115192834502</v>
+      </c>
+      <c r="O36" t="n">
+        <v>-1.010764967845917</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.2795660537070689</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>-1.016905261518891</v>
+      </c>
+      <c r="R36" t="n">
+        <v>-0.4706308817602411</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.3643795974399085</v>
+      </c>
+      <c r="T36" t="n">
+        <v>-0.6861337728823624</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0.6862117427053883</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.542013704208078</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0.7907409532271742</v>
+      </c>
+      <c r="X36" t="n">
+        <v>-1.182864495177752</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>-1.210954097259214</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-3.06256914911925</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-0.02625119067663739</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>-1.836617996267092</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0.7716875511999169</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>-2.436267151443443</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>-2.559565604847168</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>-3.014882158181523</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>-0.4843732469887087</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1.33705337500038</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0.1430707181451124</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>-1.078314627905164</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>-0.6488866502849788</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>-0.5349961128521761</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>-2.223316038573963</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>hAFmNIXl</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1.460586108766236</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-1.409171309168781</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-0.4249353219114099</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.631613246155598</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.635920238513152</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-1.027646596818343</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-0.2198605003593402</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-1.161628394132923</v>
+      </c>
+      <c r="J37" t="n">
+        <v>-0.4368959392708438</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1.179572907881439</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.468490644208255</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.3681323447406454</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1.801590485989754</v>
+      </c>
+      <c r="O37" t="n">
+        <v>-0.08893433696944424</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.498621424289142</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>-0.4276358669804806</v>
+      </c>
+      <c r="R37" t="n">
+        <v>-0.9869716869681221</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.7767001328218865</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.336444414942801</v>
+      </c>
+      <c r="U37" t="n">
+        <v>-1.336553282128718</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.542013704208078</v>
+      </c>
+      <c r="W37" t="n">
+        <v>-0.271183380171338</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0.7470462298126481</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.09344854046133</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-0.9412329657787942</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-0.2625522325385428</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.4958340313823871</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>-0.6785477228232807</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>-0.1590819361791372</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>-0.5950045611841239</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0.6839914137871819</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>-0.5161472321277576</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>-0.2713881790725162</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0.3297957577575947</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>-0.3689625638325895</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>-0.445875147858969</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>-0.0264206153243113</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0.056628892306486</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>zZKrObIr</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1.460586108766236</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-1.354424652885796</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-1.158111584292592</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.631613246155598</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.635920238513152</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-0.5360747801075261</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.2820829880991219</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-0.9844538787690571</v>
+      </c>
+      <c r="L38" t="n">
+        <v>-0.05830162724510711</v>
+      </c>
+      <c r="M38" t="n">
+        <v>2.06440246910526</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-0.4807506568984392</v>
+      </c>
+      <c r="O38" t="n">
+        <v>2.040800809148707</v>
+      </c>
+      <c r="P38" t="n">
+        <v>-1.453043716420142</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.935061829385257</v>
+      </c>
+      <c r="R38" t="n">
+        <v>-0.9946974845522799</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.6644220793409479</v>
+      </c>
+      <c r="T38" t="n">
+        <v>-0.732114562642641</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0.7321967799717851</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.634685122959383</v>
+      </c>
+      <c r="W38" t="n">
+        <v>-0.2385989312089732</v>
+      </c>
+      <c r="X38" t="n">
+        <v>-0.5799365653157444</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0.09207333566585162</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-0.6051888245454576</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-0.2231687255615612</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>-0.6289358467031163</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.128252792134485</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>-0.7921497403831265</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0.8080225128852526</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0.2887710343521574</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>-0.4065629151929905</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0.09469261806347824</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0.2543338249239699</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0.1400966549392938</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>0.5200393447644183</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0.1612454984757698</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>-0.785332083739479</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>G0IRHiWk</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1.499979832092311</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-0.9164514026219103</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1.452711203698935</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.631613246155598</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.635920238513152</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-1.273432505173752</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-0.4708322445885712</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.2478973019411075</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.5474611689635186</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.4657607009388823</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.04049081384893423</v>
+      </c>
+      <c r="M39" t="n">
+        <v>-0.6800292411009132</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-0.5128005537985706</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.1028916902649663</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.7291881708598523</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.3833471910251706</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.6412401538931383</v>
+      </c>
+      <c r="S39" t="n">
+        <v>-0.6962356874195794</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0.4396028040072135</v>
+      </c>
+      <c r="U39" t="n">
+        <v>-0.4277361427995692</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.088349413583731</v>
+      </c>
+      <c r="W39" t="n">
+        <v>-0.227165791222177</v>
+      </c>
+      <c r="X39" t="n">
+        <v>-0.3268557058674939</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>-1.354893174152099</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0.239870123768381</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-1.818914772091917</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0.9046242719981973</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>-1.167971693011984</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.476444434072038</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0.4601490344813668</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>-0.1824141982111173</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0.3795021513693489</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1.001593427090918</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>-0.1816455166721878</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0.4706598214756889</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>0.919136776082488</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>-0.6766384492003864</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.104715281086343</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>b9cFuRmG</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1.499979832092311</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1.350060167493697</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-0.5143470612261882</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.631613246155598</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.635920238513152</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-1.273432505173752</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-0.4708322445885712</v>
+      </c>
+      <c r="I40" t="n">
+        <v>2.362185846052153</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.023996831315062</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-0.6768943260500981</v>
+      </c>
+      <c r="L40" t="n">
+        <v>-0.774546825176904</v>
+      </c>
+      <c r="M40" t="n">
+        <v>-0.1375844311775199</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1.014911198441057</v>
+      </c>
+      <c r="O40" t="n">
+        <v>-0.02898870345869104</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.7440108780187354</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>-0.3492352179217224</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.469831944794065</v>
+      </c>
+      <c r="S40" t="n">
+        <v>-1.324231579770592</v>
+      </c>
+      <c r="T40" t="n">
+        <v>-0.7495555518620567</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0.7496393803142112</v>
+      </c>
+      <c r="V40" t="n">
+        <v>-0.004322005167574608</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0.2130100982694332</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.124637458615118</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>-1.013984834142634</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-0.9865759081232948</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-0.6245573114596641</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0.5257179380192084</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>-2.025105441785813</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.421005072308726</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0.3030934001743888</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0.04115020416914154</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>-0.6350504020042681</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>-0.00150611250404661</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>-1.544580135468082</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0.7209183637947231</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>0.6589097054274148</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0.3107190399483702</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>0.8592955748166187</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>4nbBt7Y9</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1.480282970429273</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1.087276217335366</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.8894172460158313</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1.631613246155598</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.635920238513152</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-2.748147955306204</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-1.976662709963957</v>
+      </c>
+      <c r="I41" t="n">
+        <v>-1.161628394132923</v>
+      </c>
+      <c r="J41" t="n">
+        <v>-0.4368959392708438</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.130423142854837</v>
+      </c>
+      <c r="L41" t="n">
+        <v>-1.37920948919445</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1.034651987489398</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-0.4387805538149328</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.6657383706212889</v>
+      </c>
+      <c r="P41" t="n">
+        <v>-0.07547307490808047</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1.968732359030947</v>
+      </c>
+      <c r="R41" t="n">
+        <v>-0.2738529778161261</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0.2681865758337614</v>
+      </c>
+      <c r="T41" t="n">
+        <v>-1.021193296295623</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.021302217465573</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0.542013704208078</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0.2758923681968079</v>
+      </c>
+      <c r="X41" t="n">
+        <v>-1.358851395340296</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0.4275704321831026</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-0.2604630634818657</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-1.308939694390376</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0.08929457787130017</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0.247346232083288</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>-0.3790503074886458</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0.3652527117888629</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0.443971622808675</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0.1368089405404221</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0.4767368328446814</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0.492658550641404</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>-0.3566255041205278</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>0.4077993085691881</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0.6392383636230837</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>-0.09589929663508828</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>fiHVGBod</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1.460586108766236</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.6055056420450919</v>
+      </c>
+      <c r="D42" t="n">
+        <v>-0.2282294954188976</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1.631613246155598</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.635920238513152</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-0.5360747801075261</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.2820829880991219</v>
+      </c>
+      <c r="I42" t="n">
+        <v>-1.161628394132923</v>
+      </c>
+      <c r="J42" t="n">
+        <v>-0.4368959392708438</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.5529735542384789</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.1145851446694654</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.324826999742257</v>
+      </c>
+      <c r="N42" t="n">
+        <v>-1.607353093387929</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.721423795055304</v>
+      </c>
+      <c r="P42" t="n">
+        <v>-1.762374150665113</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1.092325103481255</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.1487205579030774</v>
+      </c>
+      <c r="S42" t="n">
+        <v>-0.1938389735387695</v>
+      </c>
+      <c r="T42" t="n">
+        <v>-0.6094510764796416</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0.609521962687448</v>
+      </c>
+      <c r="V42" t="n">
+        <v>-0.5506577145432272</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0.6531859877610452</v>
+      </c>
+      <c r="X42" t="n">
+        <v>-0.02031659001172584</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0.8703085360914985</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-0.3795098653130567</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-1.327720994668488</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>-1.528504835135946</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>-1.683408236581562</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>-0.6719225464380421</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0.251319724310799</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>-0.2993818960609549</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>-0.2250935012030153</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>-0.4965673781628891</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>-0.977443347697832</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>-0.1908626220703185</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>-0.110238939538054</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0.1423251577949885</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>-1.144189074880863</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
           <t>jqf7smJ3</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>1.484893524923903</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1.047466531066052</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1.645403634370199</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-0.7632070243837995</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-0.07809395685176591</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.321183984534898</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-0.2088440905078444</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.4315486914389485</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.7335450166510216</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-0.0008387756381521587</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-0.5114634121725331</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.5192975426053851</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.8143253398097933</v>
-      </c>
-      <c r="O15" t="n">
-        <v>-0.9503520603267207</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0.04803160629028178</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.7788358793783446</v>
-      </c>
-      <c r="R15" t="n">
-        <v>-0.7610141269846636</v>
-      </c>
-      <c r="S15" t="n">
-        <v>-0.7394407087899373</v>
-      </c>
-      <c r="T15" t="n">
-        <v>-1.110968137591706</v>
-      </c>
-      <c r="U15" t="n">
-        <v>-1.561305392824594</v>
-      </c>
-      <c r="V15" t="n">
-        <v>-1.320605674410901</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>-1.029707649693997</v>
+      <c r="B43" t="n">
+        <v>1.460586108766236</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1.174870867388143</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.014593681056521</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1.631613246155598</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.635920238513152</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-0.7818606884629347</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.03111124386989085</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.9526601499781225</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.0396397230807</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.8262775276359405</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.1804467720654925</v>
+      </c>
+      <c r="M43" t="n">
+        <v>-0.6809709855625863</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.3311800645715732</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.5791264453781728</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.5002596936282152</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.06187642929320075</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0.6624860972495725</v>
+      </c>
+      <c r="S43" t="n">
+        <v>-0.2775717591855711</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0.3317857797417324</v>
+      </c>
+      <c r="U43" t="n">
+        <v>-0.3318018409162238</v>
+      </c>
+      <c r="V43" t="n">
+        <v>-0.5506577145432272</v>
+      </c>
+      <c r="W43" t="n">
+        <v>-0.5022757221544352</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0.6780241772358528</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0.001164444996661042</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-0.5955601625078318</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0.9116249387362088</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>-1.552954421061282</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.203149256105941</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>-0.3929077211063465</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0.7533122825685737</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>-1.213953822393215</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>-0.4348234780613991</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0.3678253806561984</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>-1.503364427993472</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>-1.648010090419853</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>0.01061742878777838</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>-0.2340675634119321</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>-1.050860503578206</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>-0.6575625482865234</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>-0.9491418290453336</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>-0.9648399357163697</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>-0.07912684192884509</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>-1.735972839905265</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>-1.846476598417712</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>-1.776843270855056</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/usa/data_preparation/df_selected_nan.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_selected_nan.xlsx
@@ -734,37 +734,37 @@
         <v>1.001162242357758</v>
       </c>
       <c r="Z2" t="n">
-        <v>-1.211064597011594</v>
+        <v>-1.20938300817858</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.1945477242212655</v>
+        <v>-0.2368938504123779</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.8009838608410148</v>
+        <v>-0.8622837337833478</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.8599821949319129</v>
+        <v>-0.8165354462201483</v>
       </c>
       <c r="AD2" t="n">
-        <v>-1.000324309090743</v>
+        <v>-1.045291530616946</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.5730748259955963</v>
+        <v>-0.4804789251199185</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.1275655428208402</v>
+        <v>-0.1343280719698371</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0.02148913804784683</v>
+        <v>-0.1182759806977934</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.2080125368299405</v>
+        <v>0.182999981867229</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.5335593486794388</v>
+        <v>0.4926334166128287</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
@@ -773,16 +773,16 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0.3864257334437438</v>
+        <v>-0.2939285782704334</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.03611563016432098</v>
+        <v>0.1288662817094696</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.1830333690373639</v>
+        <v>0.1958215077307025</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1.040624041737406</v>
+        <v>-1.065778083683654</v>
       </c>
       <c r="AQ2" t="n">
         <v>0</v>
@@ -876,22 +876,22 @@
         <v>-1.271560024372007</v>
       </c>
       <c r="Z3" t="n">
-        <v>-1.358425001598663</v>
+        <v>-1.361338550843856</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.2307393233635287</v>
+        <v>-0.2287715145485819</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.749822381786915</v>
+        <v>1.765874708464859</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.8483897326216852</v>
+        <v>-0.8574842549954222</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.559759365692898</v>
+        <v>1.533518380743111</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.1283178747621304</v>
+        <v>0.09892399137931839</v>
       </c>
       <c r="AF3" t="n">
         <v>0.1736218242484482</v>
@@ -900,13 +900,13 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.4752023310959915</v>
+        <v>-0.4729457421229442</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.2107313834349427</v>
+        <v>-0.2240095460042932</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.1049107507706471</v>
+        <v>0.1504399010775835</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
@@ -915,16 +915,16 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.3505114367681189</v>
+        <v>0.3528487859040036</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.3008252576678129</v>
+        <v>0.2954877105642216</v>
       </c>
       <c r="AO3" t="n">
         <v>0.1888589128848833</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.31752597196057</v>
+        <v>1.324288797541187</v>
       </c>
       <c r="AQ3" t="n">
         <v>0</v>
@@ -1018,37 +1018,37 @@
         <v>0.698132606793789</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.4145680788099127</v>
+        <v>-0.4239373698506559</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1.791761572696688</v>
+        <v>-1.732282867499828</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.06334797939387229</v>
+        <v>0.02117127792634352</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2.058235487575891</v>
+        <v>-2.017310136894035</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4183553450414161</v>
+        <v>0.3918092323596583</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.128150988365096</v>
+        <v>1.162538792630678</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.8803713568616914</v>
+        <v>-0.917899384233989</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-1.155037823192254</v>
+        <v>-1.186796535930874</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.4485261918105287</v>
+        <v>-0.4121904058654816</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.5869873562481713</v>
+        <v>-0.5836559550061984</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
@@ -1057,16 +1057,16 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.474880490683448</v>
+        <v>0.495590536523219</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.6647488599661739</v>
+        <v>0.7152948398048079</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.3266942555418161</v>
+        <v>-0.2785613652317629</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.3546753309857057</v>
+        <v>-0.3572313190568586</v>
       </c>
       <c r="AQ4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
         <v>-0.05944148211613278</v>
       </c>
       <c r="Z5" t="n">
-        <v>-1.122040852293744</v>
+        <v>-1.153196526679196</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.3378241871018784</v>
+        <v>0.352682448073482</v>
       </c>
       <c r="AB5" t="n">
-        <v>-1.066326641778479</v>
+        <v>-1.041744549355989</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.8731650882152471</v>
+        <v>-0.9314025118442629</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.3771431649885848</v>
+        <v>-0.3566690941731119</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.2430632816844394</v>
+        <v>-0.2041133871130789</v>
       </c>
       <c r="AF5" t="n">
         <v>-1.020846639568854</v>
@@ -1184,13 +1184,13 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.692175831613535</v>
+        <v>-0.6737259284920515</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.7531118310458891</v>
+        <v>-0.7029199793110334</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.6835938794242924</v>
+        <v>-0.6787078242694027</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
@@ -1199,16 +1199,16 @@
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.5018619446858009</v>
+        <v>-0.4809230212680943</v>
       </c>
       <c r="AN5" t="n">
-        <v>-1.432473781938106</v>
+        <v>-1.336609640548923</v>
       </c>
       <c r="AO5" t="n">
         <v>-0.01846612535071925</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.4262779968146467</v>
+        <v>-0.4254350864628118</v>
       </c>
       <c r="AQ5" t="n">
         <v>0</v>
@@ -1226,29 +1226,29 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>QgE37zwQ</t>
+          <t>n3Fa8GNJ</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1.460586108766236</v>
       </c>
       <c r="C6" t="n">
-        <v>1.218668192414532</v>
+        <v>-1.004046052674687</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.07622953858377449</v>
+        <v>-1.327993888990671</v>
       </c>
       <c r="E6" t="n">
         <v>1.631613246155598</v>
       </c>
       <c r="F6" t="n">
-        <v>1.635920238513152</v>
+        <v>1.652750648314044</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.273432505173752</v>
+        <v>-0.04450296339670891</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4708322445885712</v>
+        <v>0.784026476557584</v>
       </c>
       <c r="I6" t="n">
         <v>0.2478973019411075</v>
@@ -1257,82 +1257,82 @@
         <v>0.5474611689635186</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.557895961387572</v>
+        <v>0.5696384306651532</v>
       </c>
       <c r="L6" t="n">
-        <v>1.058258774703169</v>
+        <v>0.7814341220542419</v>
       </c>
       <c r="M6" t="n">
-        <v>1.088378509027819</v>
+        <v>-0.4403552756052475</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4006259146481085</v>
+        <v>-0.07478529616343284</v>
       </c>
       <c r="O6" t="n">
-        <v>1.033381134870769</v>
+        <v>-1.545613231280748</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5068475634766076</v>
+        <v>2.107699936635969</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.216389213013304</v>
+        <v>-2.686080370511811</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.5118351355424161</v>
+        <v>-0.8884677677701099</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6625190614853385</v>
+        <v>1.187751989633458</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3793309170680911</v>
+        <v>1.091261583023573</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3793805457727062</v>
+        <v>-1.091347801281881</v>
       </c>
       <c r="V6" t="n">
-        <v>1.535351357618356</v>
+        <v>-0.004322005167574608</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1511354103099895</v>
+        <v>-0.667341680713789</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2760722239945141</v>
+        <v>-0.2152023855226777</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.777675683490427</v>
+        <v>1.031465205914154</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.1666970874328806</v>
+        <v>-1.136801867773648</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.8811923167367639</v>
+        <v>-0.009750293842934124</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.3595116579823827</v>
+        <v>-0.8622837337833478</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.4372511574752032</v>
+        <v>-0.8165354462201483</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.09231223714306878</v>
+        <v>-1.045291530616946</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.3250968768753764</v>
+        <v>-0.4804789251199185</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.3674883161069744</v>
+        <v>-0.1343280719698371</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.1627362546316778</v>
+        <v>-0.1182759806977934</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.2683906373416538</v>
+        <v>0.182999981867229</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.5790819078949639</v>
+        <v>0.4926334166128287</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
@@ -1341,16 +1341,16 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.1072010860537351</v>
+        <v>-0.2939285782704334</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.04831413907149665</v>
+        <v>0.1288662817094696</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.8874510850775537</v>
+        <v>0.1958215077307025</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.06119441495266443</v>
+        <v>-1.065778083683654</v>
       </c>
       <c r="AQ6" t="n">
         <v>0</v>
@@ -1368,23 +1368,23 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>AoWGqXpJ</t>
+          <t>QgE37zwQ</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1.460586108766236</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.409171309168781</v>
+        <v>1.218668192414532</v>
       </c>
       <c r="D7" t="n">
-        <v>1.148711290028688</v>
+        <v>-0.07622953858377449</v>
       </c>
       <c r="E7" t="n">
         <v>1.631613246155598</v>
       </c>
       <c r="F7" t="n">
-        <v>1.652750648314044</v>
+        <v>1.635920238513152</v>
       </c>
       <c r="G7" t="n">
         <v>-1.273432505173752</v>
@@ -1399,82 +1399,82 @@
         <v>0.5474611689635186</v>
       </c>
       <c r="K7" t="n">
-        <v>1.335482085117661</v>
+        <v>-2.557895961387572</v>
       </c>
       <c r="L7" t="n">
-        <v>1.151905776156896</v>
+        <v>1.058258774703169</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9558750632704894</v>
+        <v>1.088378509027819</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1816182858305399</v>
+        <v>-0.4006259146481085</v>
       </c>
       <c r="O7" t="n">
-        <v>1.304468610858287</v>
+        <v>1.033381134870769</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.280402883406288</v>
+        <v>0.5068475634766076</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.08031256147286338</v>
+        <v>1.216389213013304</v>
       </c>
       <c r="R7" t="n">
-        <v>-1.380987363760171</v>
+        <v>-0.5118351355424161</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9879351147944997</v>
+        <v>0.6625190614853385</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3349568686907176</v>
+        <v>-0.3793309170680911</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3349732227966655</v>
+        <v>0.3793805457727062</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5337358904296587</v>
+        <v>1.535351357618356</v>
       </c>
       <c r="W7" t="n">
-        <v>1.238419840835121</v>
+        <v>-0.1511354103099895</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.7660254325571049</v>
+        <v>0.2760722239945141</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.228434469030734</v>
+        <v>1.777675683490427</v>
       </c>
       <c r="Z7" t="n">
-        <v>-1.247939187879795</v>
+        <v>0.1666970874328806</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.5749211276782871</v>
+        <v>-0.9142639434774971</v>
       </c>
       <c r="AB7" t="n">
-        <v>-1.733300232373681</v>
+        <v>0.4055877808542406</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.02639204416114845</v>
+        <v>-0.3861425882888818</v>
       </c>
       <c r="AD7" t="n">
-        <v>-1.570879699456106</v>
+        <v>0.1125834545219093</v>
       </c>
       <c r="AE7" t="n">
-        <v>-1.345887001396255</v>
+        <v>0.2971412964477302</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.96843867212528</v>
+        <v>-0.4031631075596508</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.08631424816890608</v>
+        <v>-0.2208105080891528</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.1111634112111653</v>
+        <v>-0.2909544176089387</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.390852821810891</v>
+        <v>0.6078340941283964</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
@@ -1483,16 +1483,16 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.4052028134441173</v>
+        <v>0.07857499631877594</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.9159958966370092</v>
+        <v>0.01804908022559003</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.4809948427548838</v>
+        <v>-0.8778072398676258</v>
       </c>
       <c r="AP7" t="n">
-        <v>-1.552726430133701</v>
+        <v>-0.03237512088145177</v>
       </c>
       <c r="AQ7" t="n">
         <v>0</v>
@@ -1510,17 +1510,17 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>n3Fa8GNJ</t>
+          <t>AoWGqXpJ</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1.460586108766236</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.004046052674687</v>
+        <v>-1.409171309168781</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.327993888990671</v>
+        <v>1.148711290028688</v>
       </c>
       <c r="E8" t="n">
         <v>1.631613246155598</v>
@@ -1529,10 +1529,10 @@
         <v>1.652750648314044</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.04450296339670891</v>
+        <v>-1.273432505173752</v>
       </c>
       <c r="H8" t="n">
-        <v>0.784026476557584</v>
+        <v>-0.4708322445885712</v>
       </c>
       <c r="I8" t="n">
         <v>0.2478973019411075</v>
@@ -1541,82 +1541,82 @@
         <v>0.5474611689635186</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5696384306651532</v>
+        <v>1.335482085117661</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7814341220542419</v>
+        <v>1.151905776156896</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4403552756052475</v>
+        <v>0.9558750632704894</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.07478529616343284</v>
+        <v>-0.1816182858305399</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.545613231280748</v>
+        <v>1.304468610858287</v>
       </c>
       <c r="P8" t="n">
-        <v>2.107699936635969</v>
+        <v>-0.280402883406288</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.686080370511811</v>
+        <v>-0.08031256147286338</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.8884677677701099</v>
+        <v>-1.380987363760171</v>
       </c>
       <c r="S8" t="n">
-        <v>1.187751989633458</v>
+        <v>0.9879351147944997</v>
       </c>
       <c r="T8" t="n">
-        <v>1.091261583023573</v>
+        <v>0.3349568686907176</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.091347801281881</v>
+        <v>-0.3349732227966655</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.004322005167574608</v>
+        <v>0.5337358904296587</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.667341680713789</v>
+        <v>1.238419840835121</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2152023855226777</v>
+        <v>-0.7660254325571049</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.031465205914154</v>
+        <v>1.228434469030734</v>
       </c>
       <c r="Z8" t="n">
-        <v>-1.143487179300688</v>
+        <v>-1.262048026322013</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01136265490080136</v>
+        <v>-0.56771710259479</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.8009838608410148</v>
+        <v>-1.670583080937723</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.8599821949319129</v>
+        <v>0.08745827326130703</v>
       </c>
       <c r="AD8" t="n">
-        <v>-1.000324309090743</v>
+        <v>-1.543955002366154</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.5730748259955963</v>
+        <v>-1.367848042257278</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.1275655428208402</v>
+        <v>-0.8854677556406447</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0.02148913804784683</v>
+        <v>0.09089881599499437</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.2080125368299405</v>
+        <v>-0.1402021721825744</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.5335593486794388</v>
+        <v>-0.3181720659083785</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
@@ -1625,16 +1625,16 @@
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0.3864257334437438</v>
+        <v>-0.4985071934936154</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.03611563016432098</v>
+        <v>-1.004987340610728</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.1830333690373639</v>
+        <v>0.3691725778146344</v>
       </c>
       <c r="AP8" t="n">
-        <v>-1.040624041737406</v>
+        <v>-1.516775907439312</v>
       </c>
       <c r="AQ8" t="n">
         <v>0</v>
@@ -1728,37 +1728,37 @@
         <v>-0.5375986343372002</v>
       </c>
       <c r="Z9" t="n">
-        <v>-1.215362124825985</v>
+        <v>-1.221921890596646</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.3106787971235744</v>
+        <v>-0.26377155901376</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.1606091646326548</v>
+        <v>-0.1304360472253564</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.7966461193347986</v>
+        <v>-0.8328575598637544</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.2241606477570799</v>
+        <v>0.1821773527407</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.7612663155670438</v>
+        <v>-0.8086072554291793</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.6164402291059662</v>
+        <v>0.6292986796882155</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-1.069720580679903</v>
+        <v>-1.148172195382233</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.6555690955584205</v>
+        <v>-0.6863849265745235</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.09147995826109896</v>
+        <v>0.1333830792628357</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1767,16 +1767,16 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0.03334449445084129</v>
+        <v>-0.0478701974769724</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.9952822202419309</v>
+        <v>-1.009308924364725</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.1117660894362876</v>
+        <v>-0.2485920913734002</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.7635571443815176</v>
+        <v>-0.7402545479633842</v>
       </c>
       <c r="AQ9" t="n">
         <v>0</v>
@@ -1870,37 +1870,37 @@
         <v>0.6223751979027967</v>
       </c>
       <c r="Z10" t="n">
-        <v>-1.008930899368009</v>
+        <v>-1.00059779978854</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.2376855146909636</v>
+        <v>0.2161890047277619</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.555227052663119</v>
+        <v>-0.5298383870947364</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.1592026537270805</v>
+        <v>-0.1724844689112794</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.1214751895831562</v>
+        <v>0.1908317662326336</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.0744842627587585</v>
+        <v>-0.03547559151596152</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.9320124885449378</v>
+        <v>-0.8911432906444811</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0.3852187546592311</v>
+        <v>-0.455385979324596</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.3898690810435704</v>
+        <v>-0.4116710411577368</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0.7221463858387392</v>
+        <v>-0.7638832198814484</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
@@ -1909,16 +1909,16 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0.4897675244446649</v>
+        <v>-0.496976384827822</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.6213627534417276</v>
+        <v>-0.6277384159826926</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.2455277334384279</v>
+        <v>-0.2644495341124025</v>
       </c>
       <c r="AP10" t="n">
-        <v>-1.387143578370024</v>
+        <v>-1.275732478822336</v>
       </c>
       <c r="AQ10" t="n">
         <v>0</v>
@@ -2012,22 +2012,22 @@
         <v>0.3382849145615762</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.8396229907240981</v>
+        <v>-0.8634652163135846</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0.2474452002821114</v>
+        <v>-0.2548521556496309</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.4311570661095778</v>
+        <v>0.4652454311016421</v>
       </c>
       <c r="AC11" t="n">
-        <v>-1.107557154732087</v>
+        <v>-1.036823860368998</v>
       </c>
       <c r="AD11" t="n">
-        <v>-1.250276717658128</v>
+        <v>-1.192730945860953</v>
       </c>
       <c r="AE11" t="n">
-        <v>-1.664784370612197</v>
+        <v>-1.728303191150697</v>
       </c>
       <c r="AF11" t="n">
         <v>0.5406899463025984</v>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.1395510633083816</v>
+        <v>0.118090931730136</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.526993073998827</v>
+        <v>2.578310052526618</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.115268707565245</v>
+        <v>2.102136177635047</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2051,16 +2051,16 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0.209796997560998</v>
+        <v>-0.2248496784080803</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.7321805425092104</v>
+        <v>0.7509046142243415</v>
       </c>
       <c r="AO11" t="n">
         <v>1.564072303902617</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.2589054006589695</v>
+        <v>0.2672115077275367</v>
       </c>
       <c r="AQ11" t="n">
         <v>0</v>
@@ -2154,37 +2154,37 @@
         <v>0.8496474245757734</v>
       </c>
       <c r="Z12" t="n">
-        <v>-1.423488455771094</v>
+        <v>-1.43544383575328</v>
       </c>
       <c r="AA12" t="n">
-        <v>-1.86540425534513</v>
+        <v>-1.865994597989597</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.4921939885318537</v>
+        <v>0.4245393186032027</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.733527726086664</v>
+        <v>1.802955863258244</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0.5451815273976329</v>
+        <v>-0.5893255994953225</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.3301693353327712</v>
+        <v>-0.3102045532244879</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.2604639417489439</v>
+        <v>-0.2757531380858049</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.1576628388841668</v>
+        <v>0.0361632181039989</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.520306900838686</v>
+        <v>0.5453057216269873</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.162310186232142</v>
+        <v>1.13044457933183</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2193,16 +2193,16 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0.07883959407177589</v>
+        <v>-0.05480285302102655</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.5223907606918949</v>
+        <v>0.5813573106366052</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.005869445695628527</v>
+        <v>0.0441288868943316</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.01099181958132139</v>
+        <v>0.01727836167047636</v>
       </c>
       <c r="AQ12" t="n">
         <v>0</v>
@@ -2296,37 +2296,37 @@
         <v>-1.120045206590023</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.09427302433484439</v>
+        <v>-0.1134731764789499</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.6179075711602766</v>
+        <v>-0.6408737262169458</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.262236456183452</v>
+        <v>1.261008925319847</v>
       </c>
       <c r="AC13" t="n">
-        <v>-1.873746605137085</v>
+        <v>-1.93870747923526</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.7951880940295881</v>
+        <v>0.7613494285536473</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.556761477947848</v>
+        <v>-0.5313141702297165</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.6582777654024599</v>
+        <v>0.7746146502565792</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0.9069896229673668</v>
+        <v>-0.8633203258949976</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.8682791146083182</v>
+        <v>0.7893937329820284</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.1026127008398445</v>
+        <v>0.1358156665514917</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2335,16 +2335,16 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.496982660114069</v>
+        <v>1.440159887185154</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.9292352848408216</v>
+        <v>0.8322047622486534</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.8251596211823874</v>
+        <v>0.6500963134684451</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.9467905950470558</v>
+        <v>0.9797234984914005</v>
       </c>
       <c r="AQ13" t="n">
         <v>0</v>
@@ -2438,37 +2438,37 @@
         <v>0.4519210278980643</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.7060350629155234</v>
+        <v>-0.712141777509573</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0.4082110808618439</v>
+        <v>-0.4125515341593781</v>
       </c>
       <c r="AB14" t="n">
-        <v>-1.946781022488244</v>
+        <v>-2.016180231768645</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.9468848535043248</v>
+        <v>-0.9073453348032388</v>
       </c>
       <c r="AD14" t="n">
-        <v>-1.566988755822074</v>
+        <v>-1.525816853854353</v>
       </c>
       <c r="AE14" t="n">
-        <v>-2.365193837067639</v>
+        <v>-2.258814590277809</v>
       </c>
       <c r="AF14" t="n">
-        <v>-3.848838322010332</v>
+        <v>-3.878907074806161</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0.9886139766262367</v>
+        <v>-0.9299917701453909</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.1696901059243996</v>
+        <v>0.2351079763807004</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-1.10972122668279</v>
+        <v>-1.222462425256753</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2477,16 +2477,16 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>-0.9437648521716656</v>
+        <v>-0.8175729089188526</v>
       </c>
       <c r="AN14" t="n">
-        <v>-1.814491935167119</v>
+        <v>-1.703751022006617</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.8432242430432729</v>
+        <v>-0.5565346221124269</v>
       </c>
       <c r="AP14" t="n">
-        <v>-1.875428833599006</v>
+        <v>-1.840725252704162</v>
       </c>
       <c r="AQ14" t="n">
         <v>0</v>
@@ -2580,37 +2580,37 @@
         <v>-1.682814529780251</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0.9674788098821838</v>
+        <v>-0.97619920262059</v>
       </c>
       <c r="AA15" t="n">
-        <v>-1.514188188518056</v>
+        <v>-1.526911673286485</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.335809620124008</v>
+        <v>1.560890668494019</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.7554451575369974</v>
+        <v>-0.860064645272116</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.704583158212262</v>
+        <v>1.770620427604792</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.5987878652601087</v>
+        <v>0.4707992670441062</v>
       </c>
       <c r="AF15" t="n">
-        <v>-1.068011493723172</v>
+        <v>-1.124303534781617</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.7599266287033261</v>
+        <v>0.8841964610880459</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.4482221791187261</v>
+        <v>0.31743310953722</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0.4650210552226735</v>
+        <v>-0.2686798994855533</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.308772759377643</v>
+        <v>-0.07814639595346365</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.6916573160145023</v>
+        <v>0.4488242420569915</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.903700057288095</v>
+        <v>-0.9922234504818329</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.5493906997202336</v>
+        <v>0.67451842901195</v>
       </c>
       <c r="AQ15" t="n">
         <v>0</v>
@@ -2722,37 +2722,37 @@
         <v>0.7360113112392852</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.5985825603465225</v>
+        <v>-0.6347353525356112</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0.765861357879433</v>
+        <v>-0.770565650827676</v>
       </c>
       <c r="AB16" t="n">
-        <v>-1.377017850872467</v>
+        <v>-1.430672490500555</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.8549349113567295</v>
+        <v>0.8759028379406379</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0.229461342713063</v>
+        <v>-0.1866112382194797</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.8128947823922354</v>
+        <v>0.806224833195338</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.03698042334999763</v>
+        <v>0.04531998498828545</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.9383624157135386</v>
+        <v>1.01144528900619</v>
       </c>
       <c r="AI16" t="n">
-        <v>-0.6832253184721121</v>
+        <v>-0.5945089149575398</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-0.9619180582473404</v>
+        <v>-1.069999407923582</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2761,16 +2761,16 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.2631306977383049</v>
+        <v>0.271476161342517</v>
       </c>
       <c r="AN16" t="n">
-        <v>-0.01116667775163748</v>
+        <v>0.05577455050740128</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.5711569599106765</v>
+        <v>0.6048973076511122</v>
       </c>
       <c r="AP16" t="n">
-        <v>-0.957086233807812</v>
+        <v>-0.9636710602191541</v>
       </c>
       <c r="AQ16" t="n">
         <v>0</v>
@@ -2864,37 +2864,37 @@
         <v>0.7738900156847812</v>
       </c>
       <c r="Z17" t="n">
-        <v>-1.86920965510587</v>
+        <v>-1.86198554304105</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.8582653552477159</v>
+        <v>-0.8502608829327386</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0.6931680423952837</v>
+        <v>-0.6583063990181045</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.4558035019259735</v>
+        <v>-0.4543659418417603</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0.3027459607913325</v>
+        <v>-0.2823306553168303</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0.6879265086233887</v>
+        <v>-0.7063965836362489</v>
       </c>
       <c r="AF17" t="n">
-        <v>-1.520506069855454</v>
+        <v>-1.50772646382641</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0.3084535884720424</v>
+        <v>-0.2470205649604938</v>
       </c>
       <c r="AI17" t="n">
-        <v>-0.7547493765200889</v>
+        <v>-0.6856575078122026</v>
       </c>
       <c r="AJ17" t="n">
-        <v>-0.5576233849101205</v>
+        <v>-0.535746497947668</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2903,16 +2903,16 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>-0.1403213729530031</v>
+        <v>-0.1754811840994896</v>
       </c>
       <c r="AN17" t="n">
-        <v>-0.7167424270834101</v>
+        <v>-0.7197724398919136</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.1248031394608712</v>
+        <v>0.118979887331415</v>
       </c>
       <c r="AP17" t="n">
-        <v>-0.5478775840688708</v>
+        <v>-0.5431410585552813</v>
       </c>
       <c r="AQ17" t="n">
         <v>0</v>
@@ -3006,37 +3006,37 @@
         <v>-0.7068229762755205</v>
       </c>
       <c r="Z18" t="n">
-        <v>-0.9023155249932623</v>
+        <v>-0.9127445412277834</v>
       </c>
       <c r="AA18" t="n">
         <v>-0.8495731747479269</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0.196152529405747</v>
+        <v>-0.0918717245517236</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.09699142034048863</v>
+        <v>0.01069797817067283</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.5952590154944738</v>
+        <v>0.6620557791070359</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.5352383561882601</v>
+        <v>0.5311247641862004</v>
       </c>
       <c r="AF18" t="n">
-        <v>-0.3004510706299659</v>
+        <v>-0.2795754371700201</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0.08478786845037138</v>
+        <v>-0.01095628485781148</v>
       </c>
       <c r="AI18" t="n">
-        <v>-1.310551623521167</v>
+        <v>-1.250541352017031</v>
       </c>
       <c r="AJ18" t="n">
-        <v>-1.339741669359194</v>
+        <v>-1.274693450037511</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -3045,16 +3045,16 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>-0.1707938517685748</v>
+        <v>-0.1667087536773727</v>
       </c>
       <c r="AN18" t="n">
-        <v>-1.056800770597196</v>
+        <v>-1.003339252107345</v>
       </c>
       <c r="AO18" t="n">
-        <v>-0.3996772435652914</v>
+        <v>-0.4034204358768325</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.2324752034964024</v>
+        <v>0.2518953952795654</v>
       </c>
       <c r="AQ18" t="n">
         <v>0</v>
@@ -3148,37 +3148,37 @@
         <v>0.5328437146679876</v>
       </c>
       <c r="Z19" t="n">
-        <v>-0.1380644515091167</v>
+        <v>-0.1545214077407561</v>
       </c>
       <c r="AA19" t="n">
-        <v>-0.2956718897547522</v>
+        <v>-0.3003761827029952</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0.9059171697734343</v>
+        <v>-0.9000801434939772</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.501420533391454</v>
+        <v>1.409051167414143</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0.3958193293218054</v>
+        <v>-0.3776466257463418</v>
       </c>
       <c r="AE19" t="n">
-        <v>-0.1187499089293596</v>
+        <v>-0.1818978056054715</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.2887710343521574</v>
+        <v>0.2746579300412086</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.2234868478328871</v>
+        <v>0.3336612363443033</v>
       </c>
       <c r="AI19" t="n">
-        <v>-0.6192036942416024</v>
+        <v>-0.607674469639942</v>
       </c>
       <c r="AJ19" t="n">
-        <v>-0.461732364253035</v>
+        <v>-0.4754162609499355</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
@@ -3187,16 +3187,16 @@
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>-0.1764725149742649</v>
+        <v>-0.2639944587758331</v>
       </c>
       <c r="AN19" t="n">
-        <v>-1.294569040959758</v>
+        <v>-1.359959151002585</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.1612454984757698</v>
+        <v>0.1522005520939723</v>
       </c>
       <c r="AP19" t="n">
-        <v>-0.167214711362634</v>
+        <v>-0.1756190237878933</v>
       </c>
       <c r="AQ19" t="n">
         <v>0</v>
@@ -3293,34 +3293,34 @@
         <v>-1.007377270632856</v>
       </c>
       <c r="AA20" t="n">
-        <v>-1.018170319470904</v>
+        <v>-1.027768511945899</v>
       </c>
       <c r="AB20" t="n">
-        <v>-0.7379947766602336</v>
+        <v>-0.7849772672875153</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.613114679408775</v>
+        <v>-0.6751462992767709</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.6142643005095342</v>
+        <v>0.6094670145012722</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.6326729466248602</v>
+        <v>0.6809932487868841</v>
       </c>
       <c r="AF20" t="n">
-        <v>-0.8185196080443878</v>
+        <v>-0.8887109184999793</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0.3891648453768931</v>
+        <v>-0.3560322495374838</v>
       </c>
       <c r="AI20" t="n">
-        <v>-0.3580801191441388</v>
+        <v>-0.3109491528024096</v>
       </c>
       <c r="AJ20" t="n">
-        <v>-1.121800640815714</v>
+        <v>-1.18071708870613</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
@@ -3329,16 +3329,16 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.21252147750637</v>
+        <v>0.2968544281828291</v>
       </c>
       <c r="AN20" t="n">
-        <v>-0.1436865185470765</v>
+        <v>-0.07974145880402916</v>
       </c>
       <c r="AO20" t="n">
-        <v>-0.5819828668803343</v>
+        <v>-0.4759838540695411</v>
       </c>
       <c r="AP20" t="n">
-        <v>-0.02166924227457051</v>
+        <v>-0.06559068014949328</v>
       </c>
       <c r="AQ20" t="n">
         <v>0</v>
@@ -3432,37 +3432,37 @@
         <v>0.09207333566585131</v>
       </c>
       <c r="Z21" t="n">
-        <v>-0.980125060769274</v>
+        <v>-0.984314072557304</v>
       </c>
       <c r="AA21" t="n">
-        <v>-1.387713541013862</v>
+        <v>-1.39417041368792</v>
       </c>
       <c r="AB21" t="n">
-        <v>-0.7438293369378837</v>
+        <v>-0.6669104810898674</v>
       </c>
       <c r="AC21" t="n">
-        <v>-0.689831667249987</v>
+        <v>-0.7650449311537428</v>
       </c>
       <c r="AD21" t="n">
-        <v>-0.4269049776627365</v>
+        <v>-0.3285295366688282</v>
       </c>
       <c r="AE21" t="n">
-        <v>-0.5075040208023115</v>
+        <v>-0.4998426606963244</v>
       </c>
       <c r="AF21" t="n">
-        <v>-0.06170438936974391</v>
+        <v>0.03512718743037774</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>-0.07214186896715692</v>
+        <v>-0.01487634332063696</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.7274289917953722</v>
+        <v>0.7450141787051346</v>
       </c>
       <c r="AJ21" t="n">
-        <v>-0.3218976144166324</v>
+        <v>-0.3122084464011456</v>
       </c>
       <c r="AK21" t="n">
         <v>0</v>
@@ -3471,16 +3471,16 @@
         <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>-0.1132475973564871</v>
+        <v>-0.08235183478192645</v>
       </c>
       <c r="AN21" t="n">
-        <v>0.21729161223968</v>
+        <v>0.2530826433899188</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.4216870322604273</v>
+        <v>0.3730584777672549</v>
       </c>
       <c r="AP21" t="n">
-        <v>-0.4350952413786774</v>
+        <v>-0.3869900373151888</v>
       </c>
       <c r="AQ21" t="n">
         <v>0</v>
@@ -3498,113 +3498,113 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>pv9VXZo7</t>
+          <t>UN8LwZh9</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.460586108766236</v>
+        <v>1.480282970429273</v>
       </c>
       <c r="C22" t="n">
-        <v>-1.29967799660281</v>
+        <v>1.361009498750294</v>
       </c>
       <c r="D22" t="n">
-        <v>1.211299507549033</v>
+        <v>-0.6574058441298335</v>
       </c>
       <c r="E22" t="n">
-        <v>1.631613246155598</v>
+        <v>1.647624247492205</v>
       </c>
       <c r="F22" t="n">
         <v>1.652750648314044</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2902888717521175</v>
+        <v>-0.5360747801075261</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5330547323283529</v>
+        <v>0.2820829880991219</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9526601499781225</v>
+        <v>-0.4568655460959077</v>
       </c>
       <c r="J22" t="n">
-        <v>1.0396397230807</v>
+        <v>0.05528261484633741</v>
       </c>
       <c r="K22" t="n">
-        <v>2.292786653183295</v>
+        <v>1.449543905993566</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6634053289461076</v>
+        <v>-0.4905185570315357</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6958505480570127</v>
+        <v>-0.2840256949676022</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5662126418392089</v>
+        <v>0.5519682432169278</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2268092940441773</v>
+        <v>0.117545067345372</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6550746350654374</v>
+        <v>0.1939237456779671</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.8778073357694808</v>
+        <v>-0.3214156327718404</v>
       </c>
       <c r="R22" t="n">
-        <v>0.06759968326942034</v>
+        <v>0.1950753434080243</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.41078300907821</v>
+        <v>-0.3194381520089718</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3349568686907176</v>
+        <v>-0.3912225006267832</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3349732227966655</v>
+        <v>0.3912732278243599</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5506577145432272</v>
+        <v>0.542013704208078</v>
       </c>
       <c r="W22" t="n">
-        <v>3.126174166904829</v>
+        <v>2.655986284947881</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.8851223075915756</v>
+        <v>0.9459921460634119</v>
       </c>
       <c r="Y22" t="n">
-        <v>-1.695801514161563</v>
+        <v>0.5466177890118045</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.2228377494866959</v>
+        <v>-0.3282976588579792</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.2897031193118635</v>
+        <v>-0.5260346585574085</v>
       </c>
       <c r="AB22" t="n">
-        <v>-0.4103040720120749</v>
+        <v>-1.434134757038936</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.7856818076514827</v>
+        <v>1.786979097167515</v>
       </c>
       <c r="AD22" t="n">
-        <v>-0.3857641535195657</v>
+        <v>-0.7773385273215774</v>
       </c>
       <c r="AE22" t="n">
-        <v>-0.1691768197647332</v>
+        <v>0.2748686291770738</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.9280162535030884</v>
+        <v>-0.0464151930328829</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.460090044604693</v>
+        <v>0.7983230561800109</v>
       </c>
       <c r="AI22" t="n">
-        <v>-0.665686483716183</v>
+        <v>-0.08232939256079973</v>
       </c>
       <c r="AJ22" t="n">
-        <v>-0.4900895068317522</v>
+        <v>0.02121957666872552</v>
       </c>
       <c r="AK22" t="n">
         <v>0</v>
@@ -3613,16 +3613,16 @@
         <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>-0.08759759354818009</v>
+        <v>0.1336667933959463</v>
       </c>
       <c r="AN22" t="n">
-        <v>-0.4745039304362446</v>
+        <v>-0.268819007949477</v>
       </c>
       <c r="AO22" t="n">
         <v>-0.01846612535071925</v>
       </c>
       <c r="AP22" t="n">
-        <v>-0.2280494933795678</v>
+        <v>-1.020242224771838</v>
       </c>
       <c r="AQ22" t="n">
         <v>0</v>
@@ -3640,113 +3640,113 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>UN8LwZh9</t>
+          <t>pv9VXZo7</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.480282970429273</v>
+        <v>1.460586108766236</v>
       </c>
       <c r="C23" t="n">
-        <v>1.361009498750294</v>
+        <v>-1.29967799660281</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6574058441298335</v>
+        <v>1.211299507549033</v>
       </c>
       <c r="E23" t="n">
-        <v>1.647624247492205</v>
+        <v>1.631613246155598</v>
       </c>
       <c r="F23" t="n">
         <v>1.652750648314044</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.5360747801075261</v>
+        <v>-0.2902888717521175</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2820829880991219</v>
+        <v>0.5330547323283529</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4568655460959077</v>
+        <v>0.9526601499781225</v>
       </c>
       <c r="J23" t="n">
-        <v>0.05528261484633741</v>
+        <v>1.0396397230807</v>
       </c>
       <c r="K23" t="n">
-        <v>1.449543905993566</v>
+        <v>2.292786653183295</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.4905185570315357</v>
+        <v>-0.6634053289461076</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2840256949676022</v>
+        <v>-0.6958505480570127</v>
       </c>
       <c r="N23" t="n">
-        <v>0.5519682432169278</v>
+        <v>0.5662126418392089</v>
       </c>
       <c r="O23" t="n">
-        <v>0.117545067345372</v>
+        <v>-0.2268092940441773</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1939237456779671</v>
+        <v>0.6550746350654374</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.3214156327718404</v>
+        <v>-0.8778073357694808</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1950753434080243</v>
+        <v>0.06759968326942034</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3194381520089718</v>
+        <v>-0.41078300907821</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3912225006267832</v>
+        <v>0.3349568686907176</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3912732278243599</v>
+        <v>-0.3349732227966655</v>
       </c>
       <c r="V23" t="n">
-        <v>0.542013704208078</v>
+        <v>-0.5506577145432272</v>
       </c>
       <c r="W23" t="n">
-        <v>2.655986284947881</v>
+        <v>3.126174166904829</v>
       </c>
       <c r="X23" t="n">
-        <v>0.9459921460634119</v>
+        <v>-0.8851223075915756</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.5466177890118045</v>
+        <v>-1.695801514161563</v>
       </c>
       <c r="Z23" t="n">
-        <v>-0.3210473914272665</v>
+        <v>0.2314376337984577</v>
       </c>
       <c r="AA23" t="n">
-        <v>-0.5260346585574085</v>
+        <v>0.2897031193118635</v>
       </c>
       <c r="AB23" t="n">
-        <v>-1.386460395977134</v>
+        <v>-0.4344525068075364</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.764387148731166</v>
+        <v>0.7865780271182046</v>
       </c>
       <c r="AD23" t="n">
-        <v>-0.80615275614435</v>
+        <v>-0.418342189421366</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.2561295834403474</v>
+        <v>-0.1736334354195241</v>
       </c>
       <c r="AF23" t="n">
-        <v>-0.0464151930328829</v>
+        <v>0.9280162535030884</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.7513308265395638</v>
+        <v>0.4930772872698547</v>
       </c>
       <c r="AI23" t="n">
-        <v>-0.1542811790057136</v>
+        <v>-0.6676373413464145</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.1300412377320707</v>
+        <v>-0.4921493547190212</v>
       </c>
       <c r="AK23" t="n">
         <v>0</v>
@@ -3755,16 +3755,16 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.1462166792754468</v>
+        <v>-0.09337838513452637</v>
       </c>
       <c r="AN23" t="n">
-        <v>-0.3042865547296901</v>
+        <v>-0.4849296776153502</v>
       </c>
       <c r="AO23" t="n">
         <v>-0.01846612535071925</v>
       </c>
       <c r="AP23" t="n">
-        <v>-1.004657440363478</v>
+        <v>-0.262871616578315</v>
       </c>
       <c r="AQ23" t="n">
         <v>0</v>
@@ -3858,37 +3858,37 @@
         <v>0.374441859714095</v>
       </c>
       <c r="Z24" t="n">
-        <v>-0.274093278542586</v>
+        <v>-0.21141381237566</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.2394644933671027</v>
+        <v>0.2287645329358083</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.5204799259971108</v>
+        <v>0.5208196177461605</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.6598727675582747</v>
+        <v>0.6399956191843814</v>
       </c>
       <c r="AD24" t="n">
-        <v>-0.1509115833484221</v>
+        <v>-0.03650534562882454</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.5038915425676047</v>
+        <v>0.5597110085441134</v>
       </c>
       <c r="AF24" t="n">
-        <v>-0.4416256727033798</v>
+        <v>-0.4025260577122829</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.5172334178743991</v>
+        <v>0.560074153647467</v>
       </c>
       <c r="AI24" t="n">
-        <v>-0.07663441512751035</v>
+        <v>-0.01779101932173809</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.2092830120909182</v>
+        <v>0.1129744897336588</v>
       </c>
       <c r="AK24" t="n">
         <v>0</v>
@@ -3897,16 +3897,16 @@
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>-0.5185125662185737</v>
+        <v>-0.5248151696584812</v>
       </c>
       <c r="AN24" t="n">
-        <v>0.1803198485012025</v>
+        <v>0.2181055765939106</v>
       </c>
       <c r="AO24" t="n">
-        <v>0.412176755535375</v>
+        <v>0.4754680159831259</v>
       </c>
       <c r="AP24" t="n">
-        <v>-0.6512238780011977</v>
+        <v>-0.5502087219989276</v>
       </c>
       <c r="AQ24" t="n">
         <v>0</v>
@@ -3924,113 +3924,113 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>88KCueOd</t>
+          <t>QJcftbvR</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1.460586108766236</v>
       </c>
       <c r="C25" t="n">
-        <v>1.174870867388143</v>
+        <v>-0.3799341710486505</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5764761584141072</v>
+        <v>-1.471052671894316</v>
       </c>
       <c r="E25" t="n">
-        <v>1.631613246155598</v>
+        <v>1.647624247492205</v>
       </c>
       <c r="F25" t="n">
-        <v>1.635920238513152</v>
+        <v>1.652750648314044</v>
       </c>
       <c r="G25" t="n">
-        <v>1.675998395091151</v>
+        <v>-0.5360747801075261</v>
       </c>
       <c r="H25" t="n">
-        <v>2.540828686162201</v>
+        <v>0.2820829880991219</v>
       </c>
       <c r="I25" t="n">
-        <v>2.362185846052153</v>
+        <v>0.2478973019411075</v>
       </c>
       <c r="J25" t="n">
-        <v>2.023996831315062</v>
+        <v>0.5474611689635186</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.05362794769247212</v>
+        <v>0.5492702483658845</v>
       </c>
       <c r="L25" t="n">
-        <v>0.5509184261681463</v>
+        <v>-0.4287732813477603</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.716889893402402</v>
+        <v>-0.968203046372717</v>
       </c>
       <c r="N25" t="n">
-        <v>0.5875792397726297</v>
+        <v>-1.014915605233973</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.6737372949965706</v>
+        <v>0.04427818194334047</v>
       </c>
       <c r="P25" t="n">
-        <v>0.7967138368058747</v>
+        <v>0.3685022966603665</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.6336131994538496</v>
+        <v>-1.100364016968537</v>
       </c>
       <c r="R25" t="n">
-        <v>1.180114535388146</v>
+        <v>-0.05987597686918378</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7190719016868888</v>
+        <v>-0.02256736653394775</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3603255802825953</v>
+        <v>-0.9715317782909872</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3603442778401946</v>
+        <v>0.9716361119450926</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.5506577145432272</v>
+        <v>0.542013704208078</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.7333680641375323</v>
+        <v>1.775634505964657</v>
       </c>
       <c r="X25" t="n">
-        <v>0.4100562084082938</v>
+        <v>-1.182864495177752</v>
       </c>
       <c r="Y25" t="n">
-        <v>-1.498832251044984</v>
+        <v>-1.074590761255428</v>
       </c>
       <c r="Z25" t="n">
-        <v>-0.4206261005262469</v>
+        <v>-0.3665881634484794</v>
       </c>
       <c r="AA25" t="n">
-        <v>-0.242445394378151</v>
+        <v>0.0501858829790904</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.01293430879646798</v>
+        <v>-3.083135370012422</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.371397920020206</v>
+        <v>0.2433102370351675</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.08919409541292897</v>
+        <v>-2.487464194560586</v>
       </c>
       <c r="AE25" t="n">
-        <v>-0.01367938698978061</v>
+        <v>-1.188214446885589</v>
       </c>
       <c r="AF25" t="n">
-        <v>-0.1298108094157634</v>
+        <v>-3.833039485795577</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.1218221609542514</v>
+        <v>-1.048795603147271</v>
       </c>
       <c r="AI25" t="n">
-        <v>-0.6474371936361619</v>
+        <v>0.9631982169479947</v>
       </c>
       <c r="AJ25" t="n">
-        <v>-0.2862072938407841</v>
+        <v>-0.7177057830056623</v>
       </c>
       <c r="AK25" t="n">
         <v>0</v>
@@ -4039,16 +4039,16 @@
         <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.0424290989560156</v>
+        <v>-0.431299782618884</v>
       </c>
       <c r="AN25" t="n">
-        <v>-0.7678972717786806</v>
+        <v>-0.4326018226561666</v>
       </c>
       <c r="AO25" t="n">
-        <v>-0.608089210612115</v>
+        <v>0.07208373254110052</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.08696201264597442</v>
+        <v>-3.248284026456646</v>
       </c>
       <c r="AQ25" t="n">
         <v>0</v>
@@ -4066,17 +4066,17 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>p4vRzx2l</t>
+          <t>naJGvFw3</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1.460586108766236</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.4894274836146219</v>
+        <v>1.437654817546474</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.158111584292592</v>
+        <v>1.014593681056521</v>
       </c>
       <c r="E26" t="n">
         <v>1.631613246155598</v>
@@ -4085,94 +4085,94 @@
         <v>1.635920238513152</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.04450296339670891</v>
+        <v>-0.5360747801075261</v>
       </c>
       <c r="H26" t="n">
-        <v>0.784026476557584</v>
+        <v>0.2820829880991219</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2478973019411075</v>
+        <v>-2.571154090206953</v>
       </c>
       <c r="J26" t="n">
-        <v>0.5474611689635186</v>
+        <v>-1.421253047505206</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.2939724988238439</v>
+        <v>0.8629402557746243</v>
       </c>
       <c r="L26" t="n">
-        <v>0.2874719165840366</v>
+        <v>-0.3299808402537197</v>
       </c>
       <c r="M26" t="n">
-        <v>1.010590416493666</v>
+        <v>0.08184202839218681</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.6303168424323888</v>
+        <v>0.9508114046407932</v>
       </c>
       <c r="O26" t="n">
-        <v>0.02962480486293475</v>
+        <v>-0.358689687767834</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.3166361675724468</v>
+        <v>0.12145717734565</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.03085552120640614</v>
+        <v>-0.3492352179217224</v>
       </c>
       <c r="R26" t="n">
-        <v>-1.925656093443297</v>
+        <v>-0.3959481717800488</v>
       </c>
       <c r="S26" t="n">
-        <v>1.564549525044066</v>
+        <v>0.502665561614172</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5513624925505122</v>
+        <v>0.4205762703133042</v>
       </c>
       <c r="U26" t="n">
-        <v>0.5514280127866392</v>
+        <v>-0.4206005335685759</v>
       </c>
       <c r="V26" t="n">
-        <v>0.542013704208078</v>
+        <v>-0.004322005167574608</v>
       </c>
       <c r="W26" t="n">
-        <v>-1.830306388745606</v>
+        <v>0.7852387546085282</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.316848479591532</v>
+        <v>0.7226855053737792</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.8193444610193766</v>
+        <v>1.031465205914155</v>
       </c>
       <c r="Z26" t="n">
-        <v>-0.703126878873597</v>
+        <v>-1.880274682654802</v>
       </c>
       <c r="AA26" t="n">
-        <v>-0.3185748665090395</v>
+        <v>0.5390070159199171</v>
       </c>
       <c r="AB26" t="n">
-        <v>-1.196917040576059</v>
+        <v>-2.089772630523295</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.005424472072442</v>
+        <v>1.145017694642143</v>
       </c>
       <c r="AD26" t="n">
-        <v>-1.193909077937194</v>
+        <v>-1.807978638535318</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.419936418696227</v>
+        <v>-0.006241234428523871</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.4164304778921062</v>
+        <v>-0.2528193435805134</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.3485222299211759</v>
+        <v>-0.4230226092330096</v>
       </c>
       <c r="AI26" t="n">
-        <v>-0.5471242368125492</v>
+        <v>-0.727322457452654</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.5458741438687726</v>
+        <v>-0.3466822799939908</v>
       </c>
       <c r="AK26" t="n">
         <v>0</v>
@@ -4181,16 +4181,16 @@
         <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>-0.368649470313676</v>
+        <v>-0.7620595289847418</v>
       </c>
       <c r="AN26" t="n">
-        <v>0.02240873577196063</v>
+        <v>-0.3626779216342064</v>
       </c>
       <c r="AO26" t="n">
-        <v>0.06858383181078846</v>
+        <v>0.1909738080835704</v>
       </c>
       <c r="AP26" t="n">
-        <v>-1.650931824188136</v>
+        <v>-0.6109162208186861</v>
       </c>
       <c r="AQ26" t="n">
         <v>0</v>
@@ -4208,113 +4208,113 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>QJcftbvR</t>
+          <t>88KCueOd</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>1.460586108766236</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.3799341710486505</v>
+        <v>1.174870867388143</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.471052671894316</v>
+        <v>0.5764761584141072</v>
       </c>
       <c r="E27" t="n">
-        <v>1.647624247492205</v>
+        <v>1.631613246155598</v>
       </c>
       <c r="F27" t="n">
-        <v>1.652750648314044</v>
+        <v>1.635920238513152</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.5360747801075261</v>
+        <v>1.675998395091151</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2820829880991219</v>
+        <v>2.540828686162201</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2478973019411075</v>
+        <v>2.362185846052153</v>
       </c>
       <c r="J27" t="n">
-        <v>0.5474611689635186</v>
+        <v>2.023996831315062</v>
       </c>
       <c r="K27" t="n">
-        <v>0.5492702483658845</v>
+        <v>-0.05362794769247212</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.4287732813477603</v>
+        <v>0.5509184261681463</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.968203046372717</v>
+        <v>-1.716889893402402</v>
       </c>
       <c r="N27" t="n">
-        <v>-1.014915605233973</v>
+        <v>0.5875792397726297</v>
       </c>
       <c r="O27" t="n">
-        <v>0.04427818194334047</v>
+        <v>-0.6737372949965706</v>
       </c>
       <c r="P27" t="n">
-        <v>0.3685022966603665</v>
+        <v>0.7967138368058747</v>
       </c>
       <c r="Q27" t="n">
-        <v>-1.100364016968537</v>
+        <v>-0.6336131994538496</v>
       </c>
       <c r="R27" t="n">
-        <v>-0.05987597686918378</v>
+        <v>1.180114535388146</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.02256736653394775</v>
+        <v>-0.7190719016868888</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.9715317782909872</v>
+        <v>0.3603255802825953</v>
       </c>
       <c r="U27" t="n">
-        <v>0.9716361119450926</v>
+        <v>-0.3603442778401946</v>
       </c>
       <c r="V27" t="n">
-        <v>0.542013704208078</v>
+        <v>-0.5506577145432272</v>
       </c>
       <c r="W27" t="n">
-        <v>1.775634505964657</v>
+        <v>-0.7333680641375323</v>
       </c>
       <c r="X27" t="n">
-        <v>-1.182864495177752</v>
+        <v>0.4100562084082938</v>
       </c>
       <c r="Y27" t="n">
-        <v>-1.074590761255428</v>
+        <v>-1.498832251044984</v>
       </c>
       <c r="Z27" t="n">
-        <v>-0.3741637085207091</v>
+        <v>-0.4215959414942457</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.04492814380164605</v>
+        <v>-0.26877990020859</v>
       </c>
       <c r="AB27" t="n">
-        <v>-3.035996086506549</v>
+        <v>0.0008785490486319216</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.1713408064092825</v>
+        <v>1.293194125135821</v>
       </c>
       <c r="AD27" t="n">
-        <v>-2.464610127435719</v>
+        <v>-0.008628537004843407</v>
       </c>
       <c r="AE27" t="n">
-        <v>-1.240444080081316</v>
+        <v>0.04585454509953083</v>
       </c>
       <c r="AF27" t="n">
-        <v>-3.807140513818892</v>
+        <v>-0.1381503710540513</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>-1.010902340414044</v>
+        <v>0.1194482378533397</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.8582231198550112</v>
+        <v>-0.7287969518029614</v>
       </c>
       <c r="AJ27" t="n">
-        <v>-0.688669125267002</v>
+        <v>-0.2282859249907542</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
@@ -4323,16 +4323,16 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>-0.6185658133315399</v>
+        <v>0.03892377945526999</v>
       </c>
       <c r="AN27" t="n">
-        <v>-0.5296776503153264</v>
+        <v>-0.8234325720762287</v>
       </c>
       <c r="AO27" t="n">
-        <v>-0.2717530115400658</v>
+        <v>-0.6418295583525506</v>
       </c>
       <c r="AP27" t="n">
-        <v>-3.254004656901208</v>
+        <v>0.07641877316100572</v>
       </c>
       <c r="AQ27" t="n">
         <v>0</v>
@@ -4350,17 +4350,17 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>naJGvFw3</t>
+          <t>p4vRzx2l</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>1.460586108766236</v>
       </c>
       <c r="C28" t="n">
-        <v>1.437654817546474</v>
+        <v>-0.4894274836146219</v>
       </c>
       <c r="D28" t="n">
-        <v>1.014593681056521</v>
+        <v>-1.158111584292592</v>
       </c>
       <c r="E28" t="n">
         <v>1.631613246155598</v>
@@ -4369,94 +4369,94 @@
         <v>1.635920238513152</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.5360747801075261</v>
+        <v>-0.04450296339670891</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2820829880991219</v>
+        <v>0.784026476557584</v>
       </c>
       <c r="I28" t="n">
-        <v>-2.571154090206953</v>
+        <v>0.2478973019411075</v>
       </c>
       <c r="J28" t="n">
-        <v>-1.421253047505206</v>
+        <v>0.5474611689635186</v>
       </c>
       <c r="K28" t="n">
-        <v>0.8629402557746243</v>
+        <v>-0.2939724988238439</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.3299808402537197</v>
+        <v>0.2874719165840366</v>
       </c>
       <c r="M28" t="n">
-        <v>0.08184202839218681</v>
+        <v>1.010590416493666</v>
       </c>
       <c r="N28" t="n">
-        <v>0.9508114046407932</v>
+        <v>-0.6303168424323888</v>
       </c>
       <c r="O28" t="n">
-        <v>-0.358689687767834</v>
+        <v>0.02962480486293475</v>
       </c>
       <c r="P28" t="n">
-        <v>0.12145717734565</v>
+        <v>-0.3166361675724468</v>
       </c>
       <c r="Q28" t="n">
-        <v>-0.3492352179217224</v>
+        <v>-0.03085552120640614</v>
       </c>
       <c r="R28" t="n">
-        <v>-0.3959481717800488</v>
+        <v>-1.925656093443297</v>
       </c>
       <c r="S28" t="n">
-        <v>0.502665561614172</v>
+        <v>1.564549525044066</v>
       </c>
       <c r="T28" t="n">
-        <v>0.4205762703133042</v>
+        <v>-0.5513624925505122</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.4206005335685759</v>
+        <v>0.5514280127866392</v>
       </c>
       <c r="V28" t="n">
-        <v>-0.004322005167574608</v>
+        <v>0.542013704208078</v>
       </c>
       <c r="W28" t="n">
-        <v>0.7852387546085282</v>
+        <v>-1.830306388745606</v>
       </c>
       <c r="X28" t="n">
-        <v>0.7226855053737792</v>
+        <v>-1.316848479591532</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.031465205914155</v>
+        <v>0.8193444610193766</v>
       </c>
       <c r="Z28" t="n">
-        <v>-1.868168269152327</v>
+        <v>-0.7116097773669112</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.5480887724588086</v>
+        <v>-0.3239668282228406</v>
       </c>
       <c r="AB28" t="n">
-        <v>-2.056503396604502</v>
+        <v>-1.143919881866369</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.122573712641218</v>
+        <v>1.973164180207806</v>
       </c>
       <c r="AD28" t="n">
-        <v>-1.80541556558673</v>
+        <v>-1.238471288037965</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.06540117373106288</v>
+        <v>1.37577622658167</v>
       </c>
       <c r="AF28" t="n">
-        <v>-0.1923575217029255</v>
+        <v>0.4168474559740199</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>-0.42565843654293</v>
+        <v>0.2435256086405944</v>
       </c>
       <c r="AI28" t="n">
-        <v>-0.858992213248046</v>
+        <v>-0.5707796550056411</v>
       </c>
       <c r="AJ28" t="n">
-        <v>-0.2664325256318418</v>
+        <v>0.6552304742672531</v>
       </c>
       <c r="AK28" t="n">
         <v>0</v>
@@ -4465,16 +4465,16 @@
         <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>-0.8691828992083381</v>
+        <v>-0.2595053868567423</v>
       </c>
       <c r="AN28" t="n">
-        <v>-0.5069281474353803</v>
+        <v>0.04258159877588948</v>
       </c>
       <c r="AO28" t="n">
-        <v>-0.06390789710795783</v>
+        <v>0.07728882752694044</v>
       </c>
       <c r="AP28" t="n">
-        <v>-0.6103821375969777</v>
+        <v>-1.660265752055081</v>
       </c>
       <c r="AQ28" t="n">
         <v>0</v>
@@ -4568,37 +4568,37 @@
         <v>0.6808166276187049</v>
       </c>
       <c r="Z29" t="n">
-        <v>-1.172021157780643</v>
+        <v>-1.188540450967691</v>
       </c>
       <c r="AA29" t="n">
-        <v>-2.09641066161431</v>
+        <v>-2.092194221268118</v>
       </c>
       <c r="AB29" t="n">
-        <v>-0.4551264347283738</v>
+        <v>-0.2844973964619623</v>
       </c>
       <c r="AC29" t="n">
-        <v>-1.320279957820623</v>
+        <v>-1.481382925584106</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.5335029228951881</v>
+        <v>0.5629858899972003</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.569913003744088</v>
+        <v>1.520012405113332</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.8803713568616914</v>
+        <v>-0.917899384233989</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>-0.6661979389367781</v>
+        <v>-0.4992544596970565</v>
       </c>
       <c r="AI29" t="n">
-        <v>-1.271800720290645</v>
+        <v>-1.332056695393395</v>
       </c>
       <c r="AJ29" t="n">
-        <v>-1.18497387918198</v>
+        <v>-1.01176745429188</v>
       </c>
       <c r="AK29" t="n">
         <v>0</v>
@@ -4607,16 +4607,16 @@
         <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.6311881905940238</v>
+        <v>0.3256399131845875</v>
       </c>
       <c r="AN29" t="n">
-        <v>-0.0764693730626511</v>
+        <v>-0.219693561814546</v>
       </c>
       <c r="AO29" t="n">
-        <v>-0.3266942555418161</v>
+        <v>-0.2785613652317629</v>
       </c>
       <c r="AP29" t="n">
-        <v>-0.1639099712914155</v>
+        <v>-0.03130867687897517</v>
       </c>
       <c r="AQ29" t="n">
         <v>0</v>
@@ -4716,77 +4716,77 @@
         <v>-1.410912162121363</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.352110166866468</v>
+        <v>2.292666431066799</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.1820425089273958</v>
+        <v>0.2388423724721985</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.493020867568195</v>
+        <v>1.45213149127822</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.133473349204358</v>
+        <v>1.112993529645858</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.647712701071019</v>
+        <v>1.634933095041975</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>-0.1537596921387321</v>
       </c>
       <c r="AH30" t="n">
-        <v>-0.1948992445086559</v>
+        <v>-0.274782171141688</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.555917774538494</v>
+        <v>1.436634054095753</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.492502774350965</v>
+        <v>1.465739832233623</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>0.01061742878777838</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>-0.1919425708644779</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.8736083988702414</v>
+        <v>0.8878292865990215</v>
       </c>
       <c r="AN30" t="n">
-        <v>2.318563865794844</v>
+        <v>2.225729737214164</v>
       </c>
       <c r="AO30" t="n">
-        <v>0.04558964807329279</v>
+        <v>0.05141290020274904</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.486479766783199</v>
+        <v>1.480900330917774</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.485555101221584</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>-0.3945982191844501</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>-0.4638548220579912</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>-0.4380497800200917</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>IgfnrK9E</t>
+          <t>YyTMIXGq</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>1.480282970429273</v>
       </c>
       <c r="C31" t="n">
-        <v>1.218668192414532</v>
+        <v>-0.6646167837201761</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.2103471475559419</v>
+        <v>-1.29222919326476</v>
       </c>
       <c r="E31" t="n">
         <v>1.631613246155598</v>
@@ -4795,94 +4795,94 @@
         <v>1.635920238513152</v>
       </c>
       <c r="G31" t="n">
-        <v>-1.519218413529161</v>
+        <v>-0.7818606884629347</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.7218039888178022</v>
+        <v>0.03111124386989085</v>
       </c>
       <c r="I31" t="n">
-        <v>-2.571154090206953</v>
+        <v>-0.4568655460959077</v>
       </c>
       <c r="J31" t="n">
-        <v>-1.421253047505206</v>
+        <v>0.05528261484633741</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.1169544781138355</v>
+        <v>-1.951942537984326</v>
       </c>
       <c r="L31" t="n">
-        <v>0.3267643647464397</v>
+        <v>0.3451008405555603</v>
       </c>
       <c r="M31" t="n">
-        <v>0.8926840098922613</v>
+        <v>-0.1065068639423249</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.7449195040752853</v>
+        <v>-0.9152048148780071</v>
       </c>
       <c r="O31" t="n">
-        <v>1.026054446330566</v>
+        <v>-0.4978967700316939</v>
       </c>
       <c r="P31" t="n">
-        <v>0.5014574881461049</v>
+        <v>-1.150001703394089</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.2653247085711253</v>
+        <v>-0.1112232116393988</v>
       </c>
       <c r="R31" t="n">
-        <v>-1.195568221740383</v>
+        <v>0.3083870413090057</v>
       </c>
       <c r="S31" t="n">
-        <v>1.564549525044066</v>
+        <v>-0.08219525934303376</v>
       </c>
       <c r="T31" t="n">
-        <v>-0.7171239603383494</v>
+        <v>-0.1121666731161288</v>
       </c>
       <c r="U31" t="n">
-        <v>0.7172047929006086</v>
+        <v>0.1121916223455389</v>
       </c>
       <c r="V31" t="n">
-        <v>0.542013704208078</v>
+        <v>-0.5506577145432272</v>
       </c>
       <c r="W31" t="n">
-        <v>-1.393631898374949</v>
+        <v>-2.20795729393443</v>
       </c>
       <c r="X31" t="n">
-        <v>0.08930666996318497</v>
+        <v>0.03787847392557243</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.295925230676533</v>
+        <v>-0.2564107452327123</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.5882665724762903</v>
+        <v>-0.5514447786701204</v>
       </c>
       <c r="AA31" t="n">
-        <v>-1.541802195328287</v>
+        <v>0.2430823918654167</v>
       </c>
       <c r="AB31" t="n">
-        <v>-0.6996629979570972</v>
+        <v>0.2608755312667829</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.5287675654889397</v>
+        <v>-2.076420923385918</v>
       </c>
       <c r="AD31" t="n">
-        <v>-0.7003307858618673</v>
+        <v>0.05695188836674475</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.001727254722978689</v>
+        <v>-0.171309061659862</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.2664522103142141</v>
+        <v>-1.020846639568854</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>0.3245998493923951</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.6317019673452986</v>
+        <v>-1.5209059786513</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.642333741545523</v>
+        <v>0.3543955055376094</v>
       </c>
       <c r="AJ31" t="n">
-        <v>-0.01250400617116833</v>
+        <v>0.07962603227024302</v>
       </c>
       <c r="AK31" t="n">
         <v>0</v>
@@ -4891,44 +4891,44 @@
         <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>-0.02501976250130358</v>
+        <v>-0.2550904980685125</v>
       </c>
       <c r="AN31" t="n">
-        <v>0.3838850692836088</v>
+        <v>0.1426789541585833</v>
       </c>
       <c r="AO31" t="n">
-        <v>-0.2257911635863218</v>
+        <v>-0.01846612535071925</v>
       </c>
       <c r="AP31" t="n">
-        <v>-0.7065005104392005</v>
+        <v>0.2082776131303322</v>
       </c>
       <c r="AQ31" t="n">
         <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>0.933295249569322</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>0.8745735641897752</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>0.900743710814872</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>YyTMIXGq</t>
+          <t>nTbjsvPK</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.460586108766236</v>
+        <v>1.499979832092311</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.6646167837201761</v>
+        <v>-1.244931340319824</v>
       </c>
       <c r="D32" t="n">
-        <v>-1.29222919326476</v>
+        <v>-0.07622953858377449</v>
       </c>
       <c r="E32" t="n">
         <v>1.631613246155598</v>
@@ -4937,94 +4937,94 @@
         <v>1.635920238513152</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.7818606884629347</v>
+        <v>1.184426578380334</v>
       </c>
       <c r="H32" t="n">
-        <v>0.03111124386989085</v>
+        <v>2.038885197703739</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4568655460959077</v>
+        <v>-1.161628394132923</v>
       </c>
       <c r="J32" t="n">
-        <v>0.05528261484633741</v>
+        <v>-0.4368959392708438</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.951942537984326</v>
+        <v>-0.7094834177289274</v>
       </c>
       <c r="L32" t="n">
-        <v>0.3451008405555603</v>
+        <v>0.9399136629759325</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.1065068639423249</v>
+        <v>-0.3268750679737034</v>
       </c>
       <c r="N32" t="n">
-        <v>-0.9152048148780071</v>
+        <v>-0.551972650009843</v>
       </c>
       <c r="O32" t="n">
-        <v>-0.4978967700316939</v>
+        <v>-0.2121559169637704</v>
       </c>
       <c r="P32" t="n">
-        <v>-1.150001703394089</v>
+        <v>0.1033405352625707</v>
       </c>
       <c r="Q32" t="n">
-        <v>-0.1112232116393988</v>
+        <v>0.4358952963082814</v>
       </c>
       <c r="R32" t="n">
-        <v>0.3083870413090057</v>
+        <v>1.271536473467347</v>
       </c>
       <c r="S32" t="n">
-        <v>-0.08219525934303376</v>
+        <v>-1.394008901142927</v>
       </c>
       <c r="T32" t="n">
-        <v>-0.1121666731161288</v>
+        <v>0.3738027083157799</v>
       </c>
       <c r="U32" t="n">
-        <v>0.1121916223455389</v>
+        <v>-0.3738226508320691</v>
       </c>
       <c r="V32" t="n">
-        <v>-0.5506577145432272</v>
+        <v>2.181020832335036</v>
       </c>
       <c r="W32" t="n">
-        <v>-2.20795729393443</v>
+        <v>2.171792806507106</v>
       </c>
       <c r="X32" t="n">
-        <v>0.03787847392557243</v>
+        <v>0.3877255443393303</v>
       </c>
       <c r="Y32" t="n">
-        <v>-0.2564107452327123</v>
+        <v>-0.7791368665805581</v>
       </c>
       <c r="Z32" t="n">
-        <v>-0.5514447786701204</v>
+        <v>-0.9719602896518472</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.2430823918654167</v>
+        <v>-1.038992310371922</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.2292534968829236</v>
+        <v>0.3075406698795767</v>
       </c>
       <c r="AC32" t="n">
-        <v>-2.062923497323306</v>
+        <v>-1.101218148638216</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.05952513223973029</v>
+        <v>0.1376117523317982</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.1819638993059476</v>
+        <v>0.09007176209575624</v>
       </c>
       <c r="AF32" t="n">
-        <v>-1.020846639568854</v>
+        <v>0.7611679980936458</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>-0.6977007837184817</v>
       </c>
       <c r="AH32" t="n">
-        <v>-1.471657160037806</v>
+        <v>-0.9496028332326071</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.4130691294131728</v>
+        <v>-0.9981785036563707</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.01633352151383427</v>
+        <v>0.7156379852206713</v>
       </c>
       <c r="AK32" t="n">
         <v>0</v>
@@ -5033,44 +5033,44 @@
         <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>-0.2653030348121282</v>
+        <v>-0.02782814132158584</v>
       </c>
       <c r="AN32" t="n">
-        <v>0.1728089538352051</v>
+        <v>-0.9204287866722278</v>
       </c>
       <c r="AO32" t="n">
-        <v>-0.01846612535071925</v>
+        <v>-0.3680156557947782</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.1994556543025889</v>
+        <v>-0.330207890230681</v>
       </c>
       <c r="AQ32" t="n">
         <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>-1.843822055641612</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>-1.745463135304673</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>-1.776843270855056</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>nTbjsvPK</t>
+          <t>IgfnrK9E</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.460586108766236</v>
+        <v>1.480282970429273</v>
       </c>
       <c r="C33" t="n">
-        <v>-1.244931340319824</v>
+        <v>1.218668192414532</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.07622953858377449</v>
+        <v>-0.2103471475559419</v>
       </c>
       <c r="E33" t="n">
         <v>1.631613246155598</v>
@@ -5079,124 +5079,124 @@
         <v>1.635920238513152</v>
       </c>
       <c r="G33" t="n">
-        <v>1.184426578380334</v>
+        <v>-1.519218413529161</v>
       </c>
       <c r="H33" t="n">
-        <v>2.038885197703739</v>
+        <v>-0.7218039888178022</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.161628394132923</v>
+        <v>-2.571154090206953</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.4368959392708438</v>
+        <v>-1.421253047505206</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.7094834177289274</v>
+        <v>-0.1169544781138355</v>
       </c>
       <c r="L33" t="n">
-        <v>0.9399136629759325</v>
+        <v>0.3267643647464397</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.3268750679737034</v>
+        <v>0.8926840098922613</v>
       </c>
       <c r="N33" t="n">
-        <v>-0.551972650009843</v>
+        <v>-0.7449195040752853</v>
       </c>
       <c r="O33" t="n">
-        <v>-0.2121559169637704</v>
+        <v>1.026054446330566</v>
       </c>
       <c r="P33" t="n">
-        <v>0.1033405352625707</v>
+        <v>0.5014574881461049</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.4358952963082814</v>
+        <v>0.2653247085711253</v>
       </c>
       <c r="R33" t="n">
-        <v>1.271536473467347</v>
+        <v>-1.195568221740383</v>
       </c>
       <c r="S33" t="n">
-        <v>-1.394008901142927</v>
+        <v>1.564549525044066</v>
       </c>
       <c r="T33" t="n">
-        <v>0.3738027083157799</v>
+        <v>-0.7171239603383494</v>
       </c>
       <c r="U33" t="n">
-        <v>-0.3738226508320691</v>
+        <v>0.7172047929006086</v>
       </c>
       <c r="V33" t="n">
-        <v>2.181020832335036</v>
+        <v>0.542013704208078</v>
       </c>
       <c r="W33" t="n">
-        <v>2.171792806507106</v>
+        <v>-1.393631898374949</v>
       </c>
       <c r="X33" t="n">
-        <v>0.3877255443393303</v>
+        <v>0.08930666996318497</v>
       </c>
       <c r="Y33" t="n">
-        <v>-0.7791368665805581</v>
+        <v>2.295925230676533</v>
       </c>
       <c r="Z33" t="n">
-        <v>-0.9719602896518472</v>
+        <v>0.5882665724762903</v>
       </c>
       <c r="AA33" t="n">
-        <v>-1.038992310371922</v>
+        <v>-1.541802195328287</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.2996158207837178</v>
+        <v>-0.6755145631616356</v>
       </c>
       <c r="AC33" t="n">
-        <v>-1.108013212720559</v>
+        <v>0.527871346022218</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.1451400991938296</v>
+        <v>-0.6677527499600671</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.1081847669927557</v>
+        <v>0.006183870377769561</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.7857539218734326</v>
+        <v>-0.2664522103142141</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>-1.667646397882979</v>
       </c>
       <c r="AH33" t="n">
-        <v>-0.9353563083303457</v>
+        <v>0.598714724680137</v>
       </c>
       <c r="AI33" t="n">
-        <v>-0.9724937273251237</v>
+        <v>0.6442845991757545</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.7097267931376784</v>
+        <v>-0.01044415828389939</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>0.01061742878777838</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>-0.08663008949584218</v>
       </c>
       <c r="AM33" t="n">
-        <v>-0.005990195690846376</v>
+        <v>-0.0192389709149573</v>
       </c>
       <c r="AN33" t="n">
-        <v>-0.8878562957359272</v>
+        <v>0.3943108164627144</v>
       </c>
       <c r="AO33" t="n">
-        <v>-0.3230465601893191</v>
+        <v>-0.2257911635863218</v>
       </c>
       <c r="AP33" t="n">
-        <v>-0.3244042732817394</v>
+        <v>-0.6716783872404533</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.836605537184822</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>0.3266434110523702</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>0.3316261999571907</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>0.4544792138698842</v>
       </c>
     </row>
     <row r="34">
@@ -5206,7 +5206,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.480282970429273</v>
+        <v>1.499979832092311</v>
       </c>
       <c r="C34" t="n">
         <v>0.2770257043471778</v>
@@ -5284,61 +5284,61 @@
         <v>-0.3755167573217803</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.476582230059461</v>
+        <v>1.468398690968746</v>
       </c>
       <c r="AC34" t="n">
-        <v>-1.145535206496539</v>
+        <v>-1.077651093063931</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.897405884240954</v>
+        <v>0.8516367244448171</v>
       </c>
       <c r="AE34" t="n">
-        <v>-0.1256085932273676</v>
+        <v>-0.1413869942363254</v>
       </c>
       <c r="AF34" t="n">
         <v>-0.0464151930328829</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>0.06006922734753211</v>
       </c>
       <c r="AH34" t="n">
-        <v>-0.1927959920942039</v>
+        <v>-0.2593086294537026</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.7345468242813374</v>
+        <v>0.7249335723037577</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.1866380432762249</v>
+        <v>0.2266148581798783</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>0.01061742878777838</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>0.8611822428218796</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.4697242362194179</v>
+        <v>0.4839401993100649</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.092986795969704</v>
+        <v>1.102691330263124</v>
       </c>
       <c r="AO34" t="n">
         <v>-0.01846612535071925</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.9320615209307933</v>
+        <v>0.9538054194515887</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>-1.147323168502694</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>0.07724209966206788</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>0.003332444839814073</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>0.008214716924896233</v>
       </c>
     </row>
     <row r="35">
@@ -5348,7 +5348,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.480282970429273</v>
+        <v>1.460586108766236</v>
       </c>
       <c r="C35" t="n">
         <v>-1.004046052674687</v>
@@ -5426,31 +5426,31 @@
         <v>-0.3668358507266645</v>
       </c>
       <c r="AB35" t="n">
-        <v>-0.6838527205657003</v>
+        <v>-0.7635514329972339</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.1415146040493191</v>
+        <v>0.169570622590119</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.08565345464231756</v>
+        <v>0.0393307618452283</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.3042652304977658</v>
+        <v>0.347328717071186</v>
       </c>
       <c r="AF35" t="n">
-        <v>-0.3794844547712812</v>
+        <v>-0.4003600882312269</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>0.2694893031330487</v>
       </c>
       <c r="AH35" t="n">
-        <v>-0.4392030957457713</v>
+        <v>-0.4945847762168477</v>
       </c>
       <c r="AI35" t="n">
-        <v>-1.027256074026591</v>
+        <v>-1.037074493795872</v>
       </c>
       <c r="AJ35" t="n">
-        <v>-0.4786370900424211</v>
+        <v>-0.5387992542092146</v>
       </c>
       <c r="AK35" t="n">
         <v>0</v>
@@ -5459,28 +5459,28 @@
         <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>-0.04272013205646652</v>
+        <v>-0.02586630672996202</v>
       </c>
       <c r="AN35" t="n">
-        <v>-0.4228697625343149</v>
+        <v>-0.3804671396349834</v>
       </c>
       <c r="AO35" t="n">
-        <v>-1.219793436389483</v>
+        <v>-1.216050244077942</v>
       </c>
       <c r="AP35" t="n">
-        <v>-0.6692158520298569</v>
+        <v>-0.6877931334611849</v>
       </c>
       <c r="AQ35" t="n">
         <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>0.8793706417011484</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>0.8745735641897752</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>0.900743710814872</v>
       </c>
     </row>
     <row r="36">
@@ -5568,61 +5568,61 @@
         <v>-0.02625119067663739</v>
       </c>
       <c r="AB36" t="n">
-        <v>-1.836617996267092</v>
+        <v>-1.833064801516601</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.7716875511999169</v>
+        <v>0.7929333659674823</v>
       </c>
       <c r="AD36" t="n">
-        <v>-2.436267151443443</v>
+        <v>-2.439504895710504</v>
       </c>
       <c r="AE36" t="n">
-        <v>-2.559565604847168</v>
+        <v>-2.490827302736471</v>
       </c>
       <c r="AF36" t="n">
-        <v>-3.014882158181523</v>
+        <v>-3.007422883605054</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>-8.622597335812502</v>
       </c>
       <c r="AH36" t="n">
-        <v>-0.4843732469887087</v>
+        <v>-0.5271161842611564</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.33705337500038</v>
+        <v>1.361067106953935</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.1430707181451124</v>
+        <v>0.115773792166149</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>-3.473925317937968</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>-0.4928353747748656</v>
       </c>
       <c r="AM36" t="n">
-        <v>-1.078314627905164</v>
+        <v>-0.8740488818224066</v>
       </c>
       <c r="AN36" t="n">
-        <v>-0.6488866502849788</v>
+        <v>-0.5703620561171578</v>
       </c>
       <c r="AO36" t="n">
-        <v>-0.5349961128521761</v>
+        <v>-0.2964393822313832</v>
       </c>
       <c r="AP36" t="n">
-        <v>-2.223316038573963</v>
+        <v>-2.173021130444152</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>0.1386677142605952</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>-0.95406602581675</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>-0.9121020646221016</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>-0.4380497800200917</v>
       </c>
     </row>
     <row r="37">
@@ -5710,31 +5710,31 @@
         <v>-0.2625522325385428</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.4958340313823871</v>
+        <v>0.556441181998659</v>
       </c>
       <c r="AC37" t="n">
-        <v>-0.6785477228232807</v>
+        <v>-0.7056959547901444</v>
       </c>
       <c r="AD37" t="n">
-        <v>-0.1590819361791372</v>
+        <v>-0.1399741595412894</v>
       </c>
       <c r="AE37" t="n">
-        <v>-0.5950045611841239</v>
+        <v>-0.5612145362255884</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.6839914137871819</v>
+        <v>0.7500129434236293</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>0.1454905740495191</v>
       </c>
       <c r="AH37" t="n">
-        <v>-0.5161472321277576</v>
+        <v>-0.5408348487585123</v>
       </c>
       <c r="AI37" t="n">
-        <v>-0.2713881790725162</v>
+        <v>-0.4178092985379638</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.3297957577575947</v>
+        <v>0.3912230951026077</v>
       </c>
       <c r="AK37" t="n">
         <v>0</v>
@@ -5743,28 +5743,28 @@
         <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>-0.3689625638325895</v>
+        <v>-0.4012759854804906</v>
       </c>
       <c r="AN37" t="n">
-        <v>-0.445875147858969</v>
+        <v>-0.5148839140738999</v>
       </c>
       <c r="AO37" t="n">
-        <v>-0.0264206153243113</v>
+        <v>-0.1895667512854248</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.056628892306486</v>
+        <v>0.1148801061612033</v>
       </c>
       <c r="AQ37" t="n">
         <v>0</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>0.4277520508051955</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>0.4642063702930544</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>0.4544792138698842</v>
       </c>
     </row>
     <row r="38">
@@ -5852,61 +5852,61 @@
         <v>-0.2231687255615612</v>
       </c>
       <c r="AB38" t="n">
-        <v>-0.6289358467031163</v>
+        <v>-0.5923231178602955</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.128252792134485</v>
+        <v>1.05851507290551</v>
       </c>
       <c r="AD38" t="n">
-        <v>-0.7921497403831265</v>
+        <v>-0.8449327957242041</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.8080225128852526</v>
+        <v>0.74162147579559</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.2887710343521574</v>
+        <v>0.2746579300412086</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>0.4485985784759247</v>
       </c>
       <c r="AH38" t="n">
-        <v>-0.4065629151929905</v>
+        <v>-0.4295123831734877</v>
       </c>
       <c r="AI38" t="n">
-        <v>0.09469261806347824</v>
+        <v>0.1011534901074398</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.2543338249239699</v>
+        <v>0.329425602064042</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>0.01061742878777838</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>-0.8589216195325047</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.1400966549392938</v>
+        <v>0.1513585598074411</v>
       </c>
       <c r="AN38" t="n">
-        <v>0.5200393447644183</v>
+        <v>0.4729788955675427</v>
       </c>
       <c r="AO38" t="n">
-        <v>0.1612454984757698</v>
+        <v>0.1522005520939723</v>
       </c>
       <c r="AP38" t="n">
-        <v>-0.785332083739479</v>
+        <v>-0.7807010570009242</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>-0.7335851546888789</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>-0.5159285868878405</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>-0.4070347490569067</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>-0.4380497800200917</v>
       </c>
     </row>
     <row r="39">
@@ -5916,7 +5916,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.499979832092311</v>
+        <v>1.480282970429273</v>
       </c>
       <c r="C39" t="n">
         <v>-0.9164514026219103</v>
@@ -5994,77 +5994,77 @@
         <v>-1.818914772091917</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.9046242719981973</v>
+        <v>0.8966197982660409</v>
       </c>
       <c r="AC39" t="n">
-        <v>-1.167971693011984</v>
+        <v>-1.13666263377596</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.476444434072038</v>
+        <v>1.438336327484859</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.4601490344813668</v>
+        <v>0.408654021858913</v>
       </c>
       <c r="AF39" t="n">
-        <v>-0.1824141982111173</v>
+        <v>-0.279575437170019</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>0.16312594885251</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.3795021513693489</v>
+        <v>0.4202903829275873</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.001593427090918</v>
+        <v>0.9345335047420382</v>
       </c>
       <c r="AJ39" t="n">
-        <v>-0.1816455166721878</v>
+        <v>-0.1160027940875587</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>0.01061742878777838</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>-0.4025675336017495</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.4706598214756889</v>
+        <v>0.431517617595632</v>
       </c>
       <c r="AN39" t="n">
-        <v>0.919136776082488</v>
+        <v>0.8393910804372924</v>
       </c>
       <c r="AO39" t="n">
-        <v>-0.6766384492003864</v>
+        <v>-0.7462400417201496</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.104715281086343</v>
+        <v>0.9555861147124765</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>-0.5455224211371448</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>-1.641604776135962</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>-1.568689574856855</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>-1.776843270855056</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>b9cFuRmG</t>
+          <t>4nbBt7Y9</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.499979832092311</v>
+        <v>1.539373555418387</v>
       </c>
       <c r="C40" t="n">
-        <v>1.350060167493697</v>
+        <v>1.087276217335366</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.5143470612261882</v>
+        <v>0.8894172460158313</v>
       </c>
       <c r="E40" t="n">
         <v>1.631613246155598</v>
@@ -6073,140 +6073,140 @@
         <v>1.635920238513152</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.273432505173752</v>
+        <v>-2.748147955306204</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.4708322445885712</v>
+        <v>-1.976662709963957</v>
       </c>
       <c r="I40" t="n">
-        <v>2.362185846052153</v>
+        <v>-1.161628394132923</v>
       </c>
       <c r="J40" t="n">
-        <v>2.023996831315062</v>
+        <v>-0.4368959392708438</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.6768943260500981</v>
+        <v>2.130423142854837</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.774546825176904</v>
+        <v>-1.37920948919445</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.1375844311775199</v>
+        <v>1.034651987489398</v>
       </c>
       <c r="N40" t="n">
-        <v>1.014911198441057</v>
+        <v>-0.4387805538149328</v>
       </c>
       <c r="O40" t="n">
-        <v>-0.02898870345869104</v>
+        <v>0.6657383706212889</v>
       </c>
       <c r="P40" t="n">
-        <v>0.7440108780187354</v>
+        <v>-0.07547307490808047</v>
       </c>
       <c r="Q40" t="n">
-        <v>-0.3492352179217224</v>
+        <v>1.968732359030947</v>
       </c>
       <c r="R40" t="n">
-        <v>1.469831944794065</v>
+        <v>-0.2738529778161261</v>
       </c>
       <c r="S40" t="n">
-        <v>-1.324231579770592</v>
+        <v>0.2681865758337614</v>
       </c>
       <c r="T40" t="n">
-        <v>-0.7495555518620567</v>
+        <v>-1.021193296295623</v>
       </c>
       <c r="U40" t="n">
-        <v>0.7496393803142112</v>
+        <v>1.021302217465573</v>
       </c>
       <c r="V40" t="n">
-        <v>-0.004322005167574608</v>
+        <v>0.542013704208078</v>
       </c>
       <c r="W40" t="n">
-        <v>0.2130100982694332</v>
+        <v>0.2758923681968079</v>
       </c>
       <c r="X40" t="n">
-        <v>1.124637458615118</v>
+        <v>-1.358851395340296</v>
       </c>
       <c r="Y40" t="n">
-        <v>-1.013984834142634</v>
+        <v>0.4275704321831026</v>
       </c>
       <c r="Z40" t="n">
-        <v>-0.9865759081232948</v>
+        <v>-0.2604630634818657</v>
       </c>
       <c r="AA40" t="n">
-        <v>-0.6245573114596641</v>
+        <v>-1.308939694390376</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.5257179380192084</v>
+        <v>-0.1434512524818183</v>
       </c>
       <c r="AC40" t="n">
-        <v>-2.025105441785813</v>
+        <v>0.363397630680537</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.421005072308726</v>
+        <v>-0.3687894457487578</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.3030934001743888</v>
+        <v>0.4975657633589202</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.04115020416914154</v>
+        <v>0.4422020398993153</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.087880915084344</v>
       </c>
       <c r="AH40" t="n">
-        <v>-0.6350504020042681</v>
+        <v>0.09616807548700837</v>
       </c>
       <c r="AI40" t="n">
-        <v>-0.00150611250404661</v>
+        <v>0.5993093758830801</v>
       </c>
       <c r="AJ40" t="n">
-        <v>-1.544580135468082</v>
+        <v>0.2656515951316534</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>0.01061742878777838</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>-2.508817160974464</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.7209183637947231</v>
+        <v>-0.01515115610938558</v>
       </c>
       <c r="AN40" t="n">
-        <v>0.6589097054274148</v>
+        <v>0.6086724149742115</v>
       </c>
       <c r="AO40" t="n">
-        <v>0.3107190399483702</v>
+        <v>0.7214514247448093</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.8592955748166187</v>
+        <v>-0.2691410362984012</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0</v>
+        <v>-2.075099320691247</v>
       </c>
       <c r="AR40" t="n">
-        <v>0</v>
+        <v>0.973738705470452</v>
       </c>
       <c r="AS40" t="n">
-        <v>0</v>
+        <v>0.9629603444136843</v>
       </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>0.900743710814872</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>4nbBt7Y9</t>
+          <t>fiHVGBod</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.480282970429273</v>
+        <v>1.460586108766236</v>
       </c>
       <c r="C41" t="n">
-        <v>1.087276217335366</v>
+        <v>0.6055056420450919</v>
       </c>
       <c r="D41" t="n">
-        <v>0.8894172460158313</v>
+        <v>-0.2282294954188976</v>
       </c>
       <c r="E41" t="n">
         <v>1.631613246155598</v>
@@ -6215,10 +6215,10 @@
         <v>1.635920238513152</v>
       </c>
       <c r="G41" t="n">
-        <v>-2.748147955306204</v>
+        <v>-0.5360747801075261</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.976662709963957</v>
+        <v>0.2820829880991219</v>
       </c>
       <c r="I41" t="n">
         <v>-1.161628394132923</v>
@@ -6227,128 +6227,128 @@
         <v>-0.4368959392708438</v>
       </c>
       <c r="K41" t="n">
-        <v>2.130423142854837</v>
+        <v>0.5529735542384789</v>
       </c>
       <c r="L41" t="n">
-        <v>-1.37920948919445</v>
+        <v>0.1145851446694654</v>
       </c>
       <c r="M41" t="n">
-        <v>1.034651987489398</v>
+        <v>1.324826999742257</v>
       </c>
       <c r="N41" t="n">
-        <v>-0.4387805538149328</v>
+        <v>-1.607353093387929</v>
       </c>
       <c r="O41" t="n">
-        <v>0.6657383706212889</v>
+        <v>1.721423795055304</v>
       </c>
       <c r="P41" t="n">
-        <v>-0.07547307490808047</v>
+        <v>-1.762374150665113</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.968732359030947</v>
+        <v>1.092325103481255</v>
       </c>
       <c r="R41" t="n">
-        <v>-0.2738529778161261</v>
+        <v>0.1487205579030774</v>
       </c>
       <c r="S41" t="n">
-        <v>0.2681865758337614</v>
+        <v>-0.1938389735387695</v>
       </c>
       <c r="T41" t="n">
-        <v>-1.021193296295623</v>
+        <v>-0.6094510764796416</v>
       </c>
       <c r="U41" t="n">
-        <v>1.021302217465573</v>
+        <v>0.609521962687448</v>
       </c>
       <c r="V41" t="n">
-        <v>0.542013704208078</v>
+        <v>-0.5506577145432272</v>
       </c>
       <c r="W41" t="n">
-        <v>0.2758923681968079</v>
+        <v>0.6531859877610452</v>
       </c>
       <c r="X41" t="n">
-        <v>-1.358851395340296</v>
+        <v>-0.02031659001172584</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.4275704321831026</v>
+        <v>0.8703085360914985</v>
       </c>
       <c r="Z41" t="n">
-        <v>-0.2604630634818657</v>
+        <v>-0.3795098653130567</v>
       </c>
       <c r="AA41" t="n">
-        <v>-1.308939694390376</v>
+        <v>-1.327720994668488</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.08929457787130017</v>
+        <v>-1.451690896455762</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.247346232083288</v>
+        <v>-1.699146211310978</v>
       </c>
       <c r="AD41" t="n">
-        <v>-0.3790503074886458</v>
+        <v>-0.5455770633464956</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.3652527117888629</v>
+        <v>0.2305537767835373</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.443971622808675</v>
+        <v>-0.2298855490752219</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>-1.557425305364286</v>
       </c>
       <c r="AH41" t="n">
-        <v>0.1368089405404221</v>
+        <v>-0.1690809316696515</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.4767368328446814</v>
+        <v>-0.4734540495116342</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.492658550641404</v>
+        <v>-0.9858506802560143</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>-1.073462536860231</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>-0.7816924665288384</v>
       </c>
       <c r="AM41" t="n">
-        <v>-0.3566255041205278</v>
+        <v>-0.1758157404692354</v>
       </c>
       <c r="AN41" t="n">
-        <v>0.4077993085691881</v>
+        <v>-0.07832748583041058</v>
       </c>
       <c r="AO41" t="n">
-        <v>0.6392383636230837</v>
+        <v>0.1370807962521798</v>
       </c>
       <c r="AP41" t="n">
-        <v>-0.09589929663508828</v>
+        <v>-1.099849567528508</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0</v>
+        <v>0.5076288867525661</v>
       </c>
       <c r="AR41" t="n">
-        <v>0</v>
+        <v>-1.560717864333702</v>
       </c>
       <c r="AS41" t="n">
-        <v>0</v>
+        <v>-1.455049428854686</v>
       </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>-1.330578773910068</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>fiHVGBod</t>
+          <t>b9cFuRmG</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>1.460586108766236</v>
       </c>
       <c r="C42" t="n">
-        <v>0.6055056420450919</v>
+        <v>1.350060167493697</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2282294954188976</v>
+        <v>-0.5143470612261882</v>
       </c>
       <c r="E42" t="n">
         <v>1.631613246155598</v>
@@ -6357,124 +6357,124 @@
         <v>1.635920238513152</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.5360747801075261</v>
+        <v>-1.273432505173752</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2820829880991219</v>
+        <v>-0.4708322445885712</v>
       </c>
       <c r="I42" t="n">
-        <v>-1.161628394132923</v>
+        <v>2.362185846052153</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.4368959392708438</v>
+        <v>2.023996831315062</v>
       </c>
       <c r="K42" t="n">
-        <v>0.5529735542384789</v>
+        <v>-0.6768943260500981</v>
       </c>
       <c r="L42" t="n">
-        <v>0.1145851446694654</v>
+        <v>-0.774546825176904</v>
       </c>
       <c r="M42" t="n">
-        <v>1.324826999742257</v>
+        <v>-0.1375844311775199</v>
       </c>
       <c r="N42" t="n">
-        <v>-1.607353093387929</v>
+        <v>1.014911198441057</v>
       </c>
       <c r="O42" t="n">
-        <v>1.721423795055304</v>
+        <v>-0.02898870345869104</v>
       </c>
       <c r="P42" t="n">
-        <v>-1.762374150665113</v>
+        <v>0.7440108780187354</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.092325103481255</v>
+        <v>-0.3492352179217224</v>
       </c>
       <c r="R42" t="n">
-        <v>0.1487205579030774</v>
+        <v>1.469831944794065</v>
       </c>
       <c r="S42" t="n">
-        <v>-0.1938389735387695</v>
+        <v>-1.324231579770592</v>
       </c>
       <c r="T42" t="n">
-        <v>-0.6094510764796416</v>
+        <v>-0.7495555518620567</v>
       </c>
       <c r="U42" t="n">
-        <v>0.609521962687448</v>
+        <v>0.7496393803142112</v>
       </c>
       <c r="V42" t="n">
-        <v>-0.5506577145432272</v>
+        <v>-0.004322005167574608</v>
       </c>
       <c r="W42" t="n">
-        <v>0.6531859877610452</v>
+        <v>0.2130100982694332</v>
       </c>
       <c r="X42" t="n">
-        <v>-0.02031659001172584</v>
+        <v>1.124637458615118</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.8703085360914985</v>
+        <v>-1.013984834142634</v>
       </c>
       <c r="Z42" t="n">
-        <v>-0.3795098653130567</v>
+        <v>-0.9865759081232948</v>
       </c>
       <c r="AA42" t="n">
-        <v>-1.327720994668488</v>
+        <v>-0.6245573114596641</v>
       </c>
       <c r="AB42" t="n">
-        <v>-1.528504835135946</v>
+        <v>0.4965404736457786</v>
       </c>
       <c r="AC42" t="n">
-        <v>-1.683408236581562</v>
+        <v>-2.093411800900055</v>
       </c>
       <c r="AD42" t="n">
-        <v>-0.6719225464380421</v>
+        <v>1.372215147966046</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.251319724310799</v>
+        <v>0.3351710233697077</v>
       </c>
       <c r="AF42" t="n">
-        <v>-0.2993818960609549</v>
+        <v>-0.005134362923356356</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>0.3273553767053625</v>
       </c>
       <c r="AH42" t="n">
-        <v>-0.2250935012030153</v>
+        <v>-0.5050873049570925</v>
       </c>
       <c r="AI42" t="n">
-        <v>-0.4965673781628891</v>
+        <v>-0.004653327260971591</v>
       </c>
       <c r="AJ42" t="n">
-        <v>-0.977443347697832</v>
+        <v>-1.564124356087645</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>-0.4410825568988927</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>-0.9712549329923824</v>
       </c>
       <c r="AM42" t="n">
-        <v>-0.1908626220703185</v>
+        <v>0.6781538927487382</v>
       </c>
       <c r="AN42" t="n">
-        <v>-0.110238939538054</v>
+        <v>0.5879576468024907</v>
       </c>
       <c r="AO42" t="n">
-        <v>0.1423251577949885</v>
+        <v>0.2910004209255026</v>
       </c>
       <c r="AP42" t="n">
-        <v>-1.144189074880863</v>
+        <v>0.8182948518820899</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>-1.217533255695341</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>-0.482225706970232</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>-0.3944080661677768</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>-0.4380497800200917</v>
       </c>
     </row>
     <row r="43">
@@ -6562,31 +6562,31 @@
         <v>0.9116249387362088</v>
       </c>
       <c r="AB43" t="n">
-        <v>-1.552954421061282</v>
+        <v>-1.583800845567409</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.203149256105941</v>
+        <v>1.175290138647653</v>
       </c>
       <c r="AD43" t="n">
-        <v>-0.3929077211063465</v>
+        <v>-0.4234802013970003</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.7533122825685737</v>
+        <v>0.818675364716094</v>
       </c>
       <c r="AF43" t="n">
-        <v>-1.213953822393215</v>
+        <v>-1.330707685329248</v>
       </c>
       <c r="AG43" t="n">
         <v>-0.4348234780613991</v>
       </c>
       <c r="AH43" t="n">
-        <v>0.3678253806561984</v>
+        <v>0.3862582062832889</v>
       </c>
       <c r="AI43" t="n">
-        <v>-1.503364427993472</v>
+        <v>-1.460873869851351</v>
       </c>
       <c r="AJ43" t="n">
-        <v>-1.648010090419853</v>
+        <v>-1.683108847359528</v>
       </c>
       <c r="AK43" t="n">
         <v>0.01061742878777838</v>
@@ -6595,16 +6595,16 @@
         <v>-0.2340675634119321</v>
       </c>
       <c r="AM43" t="n">
-        <v>-1.050860503578206</v>
+        <v>-1.001223898544189</v>
       </c>
       <c r="AN43" t="n">
-        <v>-0.6575625482865234</v>
+        <v>-0.5961413809644734</v>
       </c>
       <c r="AO43" t="n">
-        <v>-0.9491418290453336</v>
+        <v>-0.7827835170475432</v>
       </c>
       <c r="AP43" t="n">
-        <v>-0.9648399357163697</v>
+        <v>-0.9986907521387013</v>
       </c>
       <c r="AQ43" t="n">
         <v>-0.07912684192884509</v>

--- a/p6_deployment/data/usa/data_preparation/df_selected_nan.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_selected_nan.xlsx
@@ -583,104 +583,104 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>4MWOCVE5</t>
+          <t>p0lFJwSk</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.483966760054599</v>
+        <v>1.523221128940959</v>
       </c>
       <c r="C2" t="n">
-        <v>1.661578698630194</v>
+        <v>1.796276090876211</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.526134286574629</v>
+        <v>1.681677775882537</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.422626085876581</v>
+        <v>1.559675568221917</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.217808000568637</v>
+        <v>-0.6396316550302068</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.06008312689689155</v>
+        <v>-0.7683510198033546</v>
       </c>
       <c r="H2" t="n">
         <v>0.1061354269506152</v>
       </c>
       <c r="I2" t="n">
-        <v>0.002388347654169154</v>
+        <v>-1.750214561086118</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.3851624882491146</v>
+        <v>1.417755348268819</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1867325749102173</v>
+        <v>-1.392123535954986</v>
       </c>
       <c r="L2" t="n">
-        <v>1.513468361174149</v>
+        <v>1.401026831356332</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7030818657775054</v>
+        <v>0.3170537807281484</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.6223271250011215</v>
+        <v>0.6878073804414545</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.876385760212817</v>
+        <v>-1.179511007623464</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3767466635384011</v>
+        <v>-0.1057097041209094</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.790777086421238</v>
+        <v>-1.023932191010059</v>
       </c>
       <c r="R2" t="n">
-        <v>1.251408595809386</v>
+        <v>0.281696009093404</v>
       </c>
       <c r="S2" t="n">
-        <v>1.231801824566291</v>
+        <v>0.7204239916427559</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7964517347242879</v>
+        <v>0.09791122172358556</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2447039058502886</v>
+        <v>0.09689285331691563</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.09555384907278464</v>
+        <v>0.4582206862103052</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1762339710073909</v>
+        <v>0.03839799201789595</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3898242770490824</v>
+        <v>-0.7662614198190578</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.2800688101155647</v>
+        <v>-0.2080540386247028</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.007226553706498623</v>
+        <v>-1.110329421810902</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.4834969719065945</v>
+        <v>0.09510279864063508</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9964403108955493</v>
+        <v>-0.7662659756734006</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.3703013575275353</v>
+        <v>0.3200285056776944</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.8130563856881742</v>
+        <v>0.3270426631156532</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.4366641388732654</v>
+        <v>0.02507691226130642</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CEEHEipg</t>
+          <t>MHXbihN8</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -696,1162 +696,1162 @@
         <v>0.06852474117266777</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7283185731850932</v>
+        <v>-0.5152725433742703</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.354183106277411</v>
+        <v>-1.798981542304008</v>
       </c>
       <c r="H3" t="n">
         <v>0.1061354269506152</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2198646210015037</v>
+        <v>-0.03087272944601135</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.9597467845898153</v>
+        <v>0.6490892451641471</v>
       </c>
       <c r="K3" t="n">
-        <v>1.092432979592582</v>
+        <v>-1.529202516123128</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6057372610824002</v>
+        <v>1.17145870797829</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4168761587484068</v>
+        <v>-0.2167134479820736</v>
       </c>
       <c r="N3" t="n">
         <v>0.03274012772016646</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1185726416861976</v>
+        <v>0.6496930715787196</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1145421158974712</v>
+        <v>0.4816284825947726</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.978196524241133</v>
+        <v>-2.037343185188492</v>
       </c>
       <c r="R3" t="n">
-        <v>1.013728979901029</v>
+        <v>-0.06430072386083203</v>
       </c>
       <c r="S3" t="n">
-        <v>0.560364293784274</v>
+        <v>-0.02091748143798162</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7867941320720586</v>
+        <v>0.5878478560941583</v>
       </c>
       <c r="U3" t="n">
-        <v>1.819915500185461</v>
+        <v>-0.9472330897979383</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3945366146527498</v>
+        <v>0.09272949292346588</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.7967647028593495</v>
+        <v>-0.4012684581700228</v>
       </c>
       <c r="X3" t="n">
-        <v>0.182218718491224</v>
+        <v>-0.06888264342039287</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.072370458528634</v>
+        <v>-0.7634947019057289</v>
       </c>
       <c r="Z3" t="n">
-        <v>-3.17864729950666</v>
+        <v>1.268236137539219</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.02876370105885261</v>
+        <v>0.2412114471578012</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.629738328509061</v>
+        <v>0.5724111856164764</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.01449942981565437</v>
+        <v>-0.1962948998985086</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.110471340955203</v>
+        <v>0.2934445526161206</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.4596567250938447</v>
+        <v>0.05223815056334007</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>6yELDBaa</t>
+          <t>vNmJIcsd</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.523221128940959</v>
+        <v>1.483966760054599</v>
       </c>
       <c r="C4" t="n">
-        <v>1.644741524599442</v>
+        <v>1.796276090876211</v>
       </c>
       <c r="D4" t="n">
-        <v>1.681677775882537</v>
+        <v>-3.928738307393684</v>
       </c>
       <c r="E4" t="n">
-        <v>1.559675568221917</v>
+        <v>-2.416726637242747</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.681084692248852</v>
+        <v>-0.5152725433742709</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.909384670250813</v>
+        <v>1.629221037803427</v>
       </c>
       <c r="H4" t="n">
         <v>0.1061354269506152</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2556842424940063</v>
+        <v>-0.9442730775048184</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.7094834021836434</v>
+        <v>-0.4234681080051613</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7326006566512105</v>
+        <v>-1.649146623770252</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.4847113249632992</v>
+        <v>-1.075029356506836</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2834343515708514</v>
+        <v>-0.7504806766922955</v>
       </c>
       <c r="N4" t="n">
         <v>0.03274012772016646</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2838522557382829</v>
+        <v>-0.6673338654468529</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2892528874695603</v>
+        <v>-1.170260167543083</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.283566412659066</v>
+        <v>-0.1692796133668106</v>
       </c>
       <c r="R4" t="n">
-        <v>1.025253324424908</v>
+        <v>-1.243215061723229</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2379950257441436</v>
+        <v>-0.7727497586854777</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1726011843172429</v>
+        <v>-0.184989409077211</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.04490202784682933</v>
+        <v>-1.001301339938657</v>
       </c>
       <c r="V4" t="n">
-        <v>0.05396527545364961</v>
+        <v>0.001356694601756084</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.06330198116066868</v>
+        <v>-0.4650489895401747</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3410542440674359</v>
+        <v>-0.07253734887906005</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.6925677157635993</v>
+        <v>-0.7596661077261673</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.8000817401565388</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.2265532624287937</v>
+        <v>0.4887538476955162</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.107294082732847</v>
+        <v>-0.1581098499988858</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.02677498439411105</v>
+        <v>0.6906627797449385</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4639070236512572</v>
+        <v>-1.23689230950666</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.4162932101467402</v>
+        <v>-0.3823416622691982</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>YNFDFXUn</t>
+          <t>69kBKJCq</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.523221128940959</v>
+        <v>1.483966760054599</v>
       </c>
       <c r="C5" t="n">
-        <v>1.762601742814707</v>
+        <v>1.796276090876211</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2790737550634819</v>
+        <v>-3.928738307393684</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5655750168557507</v>
+        <v>-2.416726637242747</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.261427213309888</v>
+        <v>-2.888458924141723</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6853804540396712</v>
+        <v>-0.1174264792766263</v>
       </c>
       <c r="H5" t="n">
         <v>0.1061354269506152</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3353395121322805</v>
+        <v>-0.06669235093851392</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3451979950995101</v>
+        <v>0.7920968922533882</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.512067643602111</v>
+        <v>-0.4325706747779944</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9500894461494639</v>
+        <v>0.343373691507495</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.383515706954018</v>
+        <v>-0.31679480336524</v>
       </c>
       <c r="N5" t="n">
         <v>0.6878073804414545</v>
       </c>
       <c r="O5" t="n">
-        <v>1.271622458507462</v>
+        <v>0.4667726636585009</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1512507525672014</v>
+        <v>-0.2158356141300999</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.236292511369562</v>
+        <v>0.9442627150389926</v>
       </c>
       <c r="R5" t="n">
-        <v>0.06436914218235219</v>
+        <v>-0.3534216464626441</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.176146591404172</v>
+        <v>-0.9306852316008702</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8173884403959609</v>
+        <v>-0.07257807155632953</v>
       </c>
       <c r="U5" t="n">
         <v>-0.04490202784682933</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1010361109527122</v>
+        <v>-0.8708381984691103</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01599100911412608</v>
+        <v>0.413197264476452</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6159602464299222</v>
+        <v>-1.665550509155773</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.9113090965813093</v>
+        <v>-0.1516326507153722</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.5787968449739664</v>
+        <v>-0.8828144552643686</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.7517269099738718</v>
+        <v>-0.584471681667935</v>
       </c>
       <c r="AB5" t="n">
-        <v>-1.33552725934396</v>
+        <v>-1.698481372717935</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.368527134050978</v>
+        <v>-0.02677498439411105</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.1525633814444522</v>
+        <v>-0.3166017469337956</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.6879055931670766</v>
+        <v>-1.794726053974947</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>nXtecjFI</t>
+          <t>h29zRLZF</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.503593944497779</v>
+        <v>1.483966760054599</v>
       </c>
       <c r="C6" t="n">
-        <v>1.779438916845459</v>
+        <v>1.644741524599442</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.824832276165101</v>
+        <v>0.2790737550634819</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9255758101934981</v>
+        <v>0.5655750168557507</v>
       </c>
       <c r="F6" t="n">
-        <v>1.059942870934257</v>
+        <v>1.246481538418161</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4428887495399905</v>
+        <v>1.6943134918561</v>
       </c>
       <c r="H6" t="n">
         <v>0.1061354269506152</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.10841077601114</v>
+        <v>-1.248739860191087</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2915701274410444</v>
+        <v>-1.56752928471909</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.846197657761956</v>
+        <v>-1.117965575618703</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8599019691080897</v>
+        <v>-1.517767880164489</v>
       </c>
       <c r="M6" t="n">
-        <v>1.15106507558787</v>
+        <v>0.3170537807281485</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6223271250011215</v>
+        <v>0.03274012772016646</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.43559957871177</v>
+        <v>-0.5941657022787655</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1512507525672014</v>
+        <v>0.3715025725855821</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.193113199955527</v>
+        <v>0.9232314124968243</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.9082134307796658</v>
+        <v>0.03304082697183836</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.781742705790877</v>
+        <v>-1.325791071014117</v>
       </c>
       <c r="T6" t="n">
-        <v>-2.160964064762916</v>
+        <v>-1.390737824881058</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2248669452026333</v>
+        <v>0.9476621402993899</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.579614120158562</v>
       </c>
       <c r="W6" t="n">
-        <v>1.190838343445623</v>
+        <v>-0.4653114644759761</v>
       </c>
       <c r="X6" t="n">
-        <v>1.614536983602509</v>
+        <v>1.089023772061538</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5189489782508077</v>
+        <v>1.044376769912081</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-1.110329421810902</v>
       </c>
       <c r="AA6" t="n">
-        <v>-1.131120011961818</v>
+        <v>-0.763784989862936</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.5968328414855412</v>
+        <v>-0.2838319923481954</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.4702854444066482</v>
+        <v>0.6900230893871984</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.1012807999951509</v>
+        <v>0.02749643954033134</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>-0.3755513526936898</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>0zoadAUO</t>
+          <t>nP8vQukM</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1.483966760054599</v>
       </c>
       <c r="C7" t="n">
-        <v>1.661578698630194</v>
+        <v>1.813113264906963</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.526134286574629</v>
+        <v>0.2790737550634819</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.422626085876581</v>
+        <v>0.5655750168557507</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9148572406689977</v>
+        <v>0.5284557151666243</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.08488025225029006</v>
+        <v>0.03290609317835558</v>
       </c>
       <c r="H7" t="n">
         <v>0.1061354269506152</v>
       </c>
       <c r="I7" t="n">
-        <v>1.115355158314059</v>
+        <v>-0.3302224233476369</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5843517109805574</v>
+        <v>-0.9342097047524505</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2783568220888351</v>
+        <v>-0.5170211179172961</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.05837052440407798</v>
+        <v>-0.1555855970590657</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2834343515708513</v>
+        <v>-0.9649407239419381</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6223271250011215</v>
+        <v>0.6878073804414545</v>
       </c>
       <c r="O7" t="n">
-        <v>0.832613479498938</v>
+        <v>0.3256626346914755</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5183371192645029</v>
+        <v>-0.934276074666247</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1681629070371384</v>
+        <v>-1.72410705971514</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2590522438477087</v>
+        <v>-0.6518398326770986</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.074739868032639</v>
+        <v>-0.7288447658434934</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9223471169603354</v>
+        <v>-0.7140680230383498</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4062635031287252</v>
+        <v>-0.6774289409169202</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6631172642650484</v>
+        <v>0.2671684715376392</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.01797526696413472</v>
+        <v>-0.4926321015082786</v>
       </c>
       <c r="X7" t="n">
-        <v>1.522208847410985</v>
+        <v>1.114652093035179</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.8664323926595794</v>
+        <v>0.6638811601032131</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.119166752075489</v>
+        <v>-0.01917487485875038</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.798270122276394</v>
+        <v>0.6934485245974957</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.02677498439411105</v>
+        <v>0.1899480927216371</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.3582579979461665</v>
+        <v>-0.6310737498137667</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.299830620056624</v>
+        <v>0.8874462283508745</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EwZtLg7P</t>
+          <t>QF7rPa4S</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.601729866713678</v>
+        <v>1.483966760054599</v>
       </c>
       <c r="C8" t="n">
-        <v>1.695253046691699</v>
+        <v>1.644741524599442</v>
       </c>
       <c r="D8" t="n">
-        <v>2.382979786292065</v>
+        <v>-0.4222282553460458</v>
       </c>
       <c r="E8" t="n">
-        <v>2.056725843905</v>
+        <v>0.06852474117266777</v>
       </c>
       <c r="F8" t="n">
-        <v>1.638804926380342</v>
+        <v>1.401930427988082</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8465617688367658</v>
+        <v>0.001909686486606733</v>
       </c>
       <c r="H8" t="n">
         <v>0.1061354269506152</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1559010111934643</v>
+        <v>0.3989627284640149</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5086353060586425</v>
+        <v>-0.3340883285743854</v>
       </c>
       <c r="K8" t="n">
-        <v>0.321363716146785</v>
+        <v>-0.5353799099041007</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.3488444764334376</v>
+        <v>-1.239006587491152</v>
       </c>
       <c r="M8" t="n">
-        <v>1.132001960276791</v>
+        <v>0.08353061816742612</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6878073804414545</v>
+        <v>0.03274012772016646</v>
       </c>
       <c r="O8" t="n">
-        <v>0.03821627938827522</v>
+        <v>0.6131089899946759</v>
       </c>
       <c r="P8" t="n">
-        <v>1.215801215989375</v>
+        <v>-0.2525442507998303</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.8670349516909448</v>
+        <v>0.07611660257887688</v>
       </c>
       <c r="R8" t="n">
-        <v>-1.448798250384302</v>
+        <v>-1.421807770202222</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.436517925179122</v>
+        <v>-0.7807123442083087</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8910695717578538</v>
+        <v>0.2138615138387444</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1183769262205144</v>
+        <v>-0.04490202784682933</v>
       </c>
       <c r="V8" t="n">
-        <v>2.720389662841727</v>
+        <v>0.1004823364174291</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6165902883652297</v>
+        <v>-1.227508661668065</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5160072778522966</v>
+        <v>-0.7511220589734975</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.09244961153886791</v>
+        <v>-0.3951126400779428</v>
       </c>
       <c r="Z8" t="n">
-        <v>-1.592936926606579</v>
+        <v>1.113112296712037</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.4576808316229175</v>
+        <v>-0.2625478708192879</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.637579567488483</v>
+        <v>-0.7440570011671689</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.1680800681414922</v>
+        <v>-0.02677498439411105</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.6617485315108924</v>
+        <v>-0.9043965720493623</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.333782167934166</v>
+        <v>0.8806559187753661</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>GnL8GDFt</t>
+          <t>b3GRSs53</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1.483966760054599</v>
       </c>
       <c r="C9" t="n">
-        <v>1.695253046691699</v>
+        <v>1.661578698630194</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.928738307393684</v>
+        <v>-2.526134286574629</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.416726637242747</v>
+        <v>-1.422626085876581</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0385626153598482</v>
+        <v>-0.4634562468509636</v>
       </c>
       <c r="G9" t="n">
-        <v>1.065086436013596</v>
+        <v>-0.05233402522395434</v>
       </c>
       <c r="H9" t="n">
         <v>0.1061354269506152</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9899864830903012</v>
+        <v>1.294453265776571</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2089566373712994</v>
+        <v>-0.4234681080051613</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6469262940461213</v>
+        <v>0.492712441356962</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.2879386477821205</v>
+        <v>-0.09116597060094145</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.084898748467851</v>
+        <v>-0.9172829356642398</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6223271250011215</v>
+        <v>0.03274012772016646</v>
       </c>
       <c r="O9" t="n">
-        <v>1.198454295339375</v>
+        <v>1.893551845436204</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.243677440882543</v>
+        <v>0.1145421158974711</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.7053495997294634</v>
+        <v>-0.5683160085033706</v>
       </c>
       <c r="R9" t="n">
-        <v>1.025477098104978</v>
+        <v>1.104830175429235</v>
       </c>
       <c r="S9" t="n">
-        <v>0.337594347912847</v>
+        <v>0.02470991465539037</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5006649004141999</v>
+        <v>-0.3851690204693275</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8574290341042796</v>
+        <v>0.5222774968081527</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1237408668993189</v>
+        <v>-0.2777456711809211</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2887322369103084</v>
+        <v>-0.7934981547409526</v>
       </c>
       <c r="X9" t="n">
-        <v>0.2930734704093744</v>
+        <v>1.455731797909213</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5997328321189384</v>
+        <v>1.344319481534102</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.8690256694130636</v>
+        <v>-0.2312943237902055</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.008883702838903598</v>
+        <v>1.377194271453114</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.005969658494704508</v>
+        <v>0.9047238298678376</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.176648914211166</v>
+        <v>1.639323523966385</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.412048434094738</v>
+        <v>0.5640658028293519</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.3551804239671645</v>
+        <v>-1.237920668783258</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>zPi4VA0k</t>
+          <t>jix3jCxF</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.483966760054599</v>
+        <v>1.503593944497779</v>
       </c>
       <c r="C10" t="n">
-        <v>1.661578698630194</v>
+        <v>1.644741524599442</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.123530265755573</v>
+        <v>2.382979786292065</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4285255345104151</v>
+        <v>2.056725843905</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5521431650058496</v>
+        <v>-0.6707214329441907</v>
       </c>
       <c r="G10" t="n">
-        <v>0.09954836756561619</v>
+        <v>-0.9202334125929251</v>
       </c>
       <c r="H10" t="n">
         <v>0.1061354269506152</v>
       </c>
       <c r="I10" t="n">
-        <v>0.345233296225262</v>
+        <v>0.7571589433890372</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1485624803518036</v>
+        <v>0.3809499068718205</v>
       </c>
       <c r="K10" t="n">
-        <v>1.495102483836499</v>
+        <v>0.9639214356849493</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7634726176366362</v>
+        <v>0.4007657223520058</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6840187504664259</v>
+        <v>-1.250887453608129</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6878073804414545</v>
+        <v>0.03274012772016646</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8502542733670714</v>
+        <v>0.7960293979148941</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2980852992461221</v>
+        <v>-0.8031738008457822</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.797809677473571</v>
+        <v>0.1282295646302896</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.7082219201480936</v>
+        <v>-0.09307162558477694</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1640789481541513</v>
+        <v>1.022246382328506</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1983865059948353</v>
+        <v>0.874890965739216</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8189964147989531</v>
+        <v>-1.217932408383269</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2423041009228034</v>
+        <v>-0.04848301357372199</v>
       </c>
       <c r="W10" t="n">
-        <v>1.453437517334249</v>
+        <v>0.1518907849896035</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.4963695176083084</v>
+        <v>0.07730321976556032</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.2937649470267438</v>
+        <v>-1.342619947803645</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.268236137539219</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.1368493106106353</v>
+        <v>-0.2033992782109885</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.9713732337207051</v>
+        <v>0.7833089246794277</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.08490872464408027</v>
+        <v>-0.4136882592100152</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.3009258366204587</v>
+        <v>-0.9260460020043371</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.9187761187343625</v>
+        <v>-0.3891319718447066</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>GvBXzXxS</t>
+          <t>h6Py6Kcj</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.503593944497779</v>
+        <v>1.483966760054599</v>
       </c>
       <c r="C11" t="n">
-        <v>1.745764568783955</v>
+        <v>1.813113264906963</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4222282553460458</v>
+        <v>-1.824832276165101</v>
       </c>
       <c r="E11" t="n">
-        <v>0.06852474117266777</v>
+        <v>-0.9255758101934981</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.011228524383065</v>
+        <v>-0.411639950327657</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.8117459891718036</v>
+        <v>0.02903154234188727</v>
       </c>
       <c r="H11" t="n">
         <v>0.1061354269506152</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.021029409274466</v>
+        <v>-0.7204004431766794</v>
       </c>
       <c r="J11" t="n">
-        <v>1.00660836288725</v>
+        <v>-0.02125910056667061</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4007487686675326</v>
+        <v>-0.9209145416269993</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3773404036399608</v>
+        <v>-0.1116631244739811</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1547583232210656</v>
+        <v>-1.000684065150212</v>
       </c>
       <c r="N11" t="n">
         <v>-0.6223271250011215</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.04017818114896145</v>
+        <v>0.7960293979148942</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.0952215222152725</v>
+        <v>0.5734000742690978</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.538454632406981</v>
+        <v>-0.7240345022522559</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.1549290642912551</v>
+        <v>1.027491061225658</v>
       </c>
       <c r="S11" t="n">
-        <v>0.39686413344129</v>
+        <v>1.694575305663331</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6665356621792508</v>
+        <v>1.365715340819539</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4423573765633892</v>
+        <v>1.489060777470052</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.209077628805818</v>
+        <v>5.334205469377911</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2689427965787533</v>
+        <v>1.310449259095027</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.4682673760208808</v>
+        <v>-0.9633715986131233</v>
       </c>
       <c r="Y11" t="n">
-        <v>-1.165915601054642</v>
+        <v>-0.2081780416750507</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>0.3271515031876489</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.6487992261647478</v>
+        <v>0.2993854576144386</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.7003240099855749</v>
+        <v>0.02365939229770242</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.7232492542035774</v>
+        <v>0.4858532400911893</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.9351626116039107</v>
+        <v>0.9537723089949509</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.4434544484487738</v>
+        <v>-0.2329548516080132</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>QHhnaCp6</t>
+          <t>tS5WR1K9</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1.483966760054599</v>
       </c>
       <c r="C12" t="n">
-        <v>1.728927394753203</v>
+        <v>1.678415872660947</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.526134286574629</v>
+        <v>2.382979786292065</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.422626085876581</v>
+        <v>2.056725843905</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1525584677111228</v>
+        <v>-0.04892587466450898</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1103971099077283</v>
+        <v>-0.1608214486450753</v>
       </c>
       <c r="H12" t="n">
         <v>0.1061354269506152</v>
       </c>
       <c r="I12" t="n">
-        <v>0.219864621001504</v>
+        <v>1.384002319507826</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1128105685794929</v>
+        <v>-0.24470854914361</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4070380787518733</v>
+        <v>0.9639214356849493</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.3371318170774151</v>
+        <v>-0.6650862790460462</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9175419130271478</v>
+        <v>-0.4168761587484069</v>
       </c>
       <c r="N12" t="n">
         <v>0.03274012772016646</v>
       </c>
       <c r="O12" t="n">
-        <v>0.06434776623402061</v>
+        <v>1.344790621675549</v>
       </c>
       <c r="P12" t="n">
-        <v>1.215801215989375</v>
+        <v>-0.0690010674511794</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.4544119628767151</v>
+        <v>0.548948674334682</v>
       </c>
       <c r="R12" t="n">
-        <v>-1.102610599409365</v>
+        <v>0.3434468889046089</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.01927544252492076</v>
+        <v>1.025947485910327</v>
       </c>
       <c r="T12" t="n">
-        <v>1.567351647246737</v>
+        <v>1.352499390658764</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6314172181150502</v>
+        <v>-0.6894242149547646</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1038049836291277</v>
+        <v>-0.2284597375407262</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.123128357193341</v>
+        <v>-0.3940375906999675</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.029381378576173</v>
+        <v>-1.31754861104743</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.6690973798266586</v>
+        <v>-0.9981394739308546</v>
       </c>
       <c r="Z12" t="n">
-        <v>-0.09685366173998149</v>
+        <v>-1.162037368753296</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0.1417731077674285</v>
+        <v>0.1689288215325391</v>
       </c>
       <c r="AB12" t="n">
-        <v>-1.150519612222651</v>
+        <v>-0.4150886370985252</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.1956248607067912</v>
+        <v>0.233406976942668</v>
       </c>
       <c r="AD12" t="n">
-        <v>-1.326665198482281</v>
+        <v>-0.2400724936542807</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.3823416622691982</v>
+        <v>-1.339775312415884</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>dYh0Wjoq</t>
+          <t>AszX60rp</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.503593944497779</v>
+        <v>1.483966760054599</v>
       </c>
       <c r="C13" t="n">
-        <v>1.762601742814707</v>
+        <v>1.644741524599442</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.123530265755573</v>
+        <v>-3.227436296984157</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.4285255345104151</v>
+        <v>-1.919676361559664</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4174207940452523</v>
+        <v>2.171772547762925</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05615339819716722</v>
+        <v>-1.330935801258599</v>
       </c>
       <c r="H13" t="n">
         <v>0.1061354269506152</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.9442730775048178</v>
+        <v>-1.238505682621801</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.4234681080051613</v>
+        <v>0.5597094657333715</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.449705547299012</v>
+        <v>-1.239133602731614</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.6240919712999675</v>
+        <v>0.7111511952866038</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2503328771393708</v>
+        <v>1.75155320788687</v>
       </c>
       <c r="N13" t="n">
-        <v>0.03274012772016646</v>
+        <v>0.6878073804414545</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.8502542733670715</v>
+        <v>-2.365880510420309</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1145421158974716</v>
+        <v>1.582887582686676</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.614380144602388</v>
+        <v>-1.666565664116711</v>
       </c>
       <c r="R13" t="n">
-        <v>-1.160418800095438</v>
+        <v>-1.174977409162228</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.521132885411884</v>
+        <v>-0.8074541207923825</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2492348795272606</v>
+        <v>-0.1217639536329982</v>
       </c>
       <c r="U13" t="n">
-        <v>1.52665790505135</v>
+        <v>0.5754505772445572</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3906601929057682</v>
+        <v>0.4609895588867206</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.6637079564323989</v>
+        <v>-0.5832010099538496</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.0558425507297558</v>
+        <v>0.510549638574552</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.5318101612896292</v>
+        <v>-0.01712809203866304</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.3864181646173873</v>
+        <v>-2.764983723967508</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.2982577228805653</v>
+        <v>-0.5251533278461826</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.3846157237626209</v>
+        <v>0.08839427173778927</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.5510202644514072</v>
+        <v>-0.02677498439411105</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.02811213632946136</v>
+        <v>-1.218586240687426</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.06998742179581131</v>
+        <v>0.5003985825468952</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>48ijbWaC</t>
+          <t>KCHNTNkc</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1.483966760054599</v>
       </c>
       <c r="C14" t="n">
-        <v>1.712090220722451</v>
+        <v>1.813113264906963</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9803757654730096</v>
+        <v>-1.824832276165101</v>
       </c>
       <c r="E14" t="n">
-        <v>1.062625292538834</v>
+        <v>-0.9255758101934981</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5003268684825429</v>
+        <v>-0.3080073572810432</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05615339819716722</v>
+        <v>-1.14805700177728</v>
       </c>
       <c r="H14" t="n">
         <v>0.1061354269506152</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2816100798935269</v>
+        <v>-0.01296291869976031</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4345777745302852</v>
+        <v>-0.9776227404759704</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.135100448139721</v>
+        <v>0.1414475546760992</v>
       </c>
       <c r="L14" t="n">
-        <v>1.302640492765742</v>
+        <v>-0.9438475717193834</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.04991118901012934</v>
+        <v>-0.7838411284866843</v>
       </c>
       <c r="N14" t="n">
         <v>-0.6223271250011215</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.106342844455377</v>
+        <v>-0.3746612127745034</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1512507525672016</v>
+        <v>-0.6196306174971314</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.8510598472525728</v>
+        <v>-0.7730455022767985</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.5433628772883087</v>
+        <v>-1.078235252115466</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2022173619696834</v>
+        <v>0.08221820076785558</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2705982922653879</v>
+        <v>1.601891087578369</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7452111909277725</v>
+        <v>-0.04490202784682933</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9676932586707476</v>
+        <v>-0.0158103159920197</v>
       </c>
       <c r="W14" t="n">
-        <v>0.4860752028857794</v>
+        <v>-0.3510152812622611</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7252769621066011</v>
+        <v>-0.5957945176155214</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.4869865000823892</v>
+        <v>-1.077005413953567</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.164820243654431</v>
+        <v>-1.379210745911351</v>
       </c>
       <c r="AA14" t="n">
-        <v>-1.235308853093855</v>
+        <v>0.2270472283736784</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.7419236453829487</v>
+        <v>0.4974640630510251</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.4796923641350136</v>
+        <v>0.258018473653278</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.4406634189975551</v>
+        <v>-0.9797761218007922</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.5886726070285044</v>
+        <v>-0.5385187825058916</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Iigr0hVa</t>
+          <t>WdOu5vDd</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.503593944497779</v>
+        <v>1.660611420043218</v>
       </c>
       <c r="C15" t="n">
-        <v>1.678415872660947</v>
+        <v>1.644741524599442</v>
       </c>
       <c r="D15" t="n">
         <v>0.2790737550634819</v>
@@ -1860,82 +1860,82 @@
         <v>0.5655750168557507</v>
       </c>
       <c r="F15" t="n">
-        <v>0.925220499973659</v>
+        <v>-1.832886940681215</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4575568648553166</v>
+        <v>-1.478168733044406</v>
       </c>
       <c r="H15" t="n">
         <v>0.1061354269506152</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6317902681652792</v>
+        <v>-0.8803094676967784</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.08382494616821337</v>
+        <v>0.674626325001512</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5098473138779801</v>
+        <v>-1.190176824100134</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.2879386477821205</v>
+        <v>0.5354613049462648</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9840038392530175</v>
+        <v>0.2026750888616723</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6878073804414545</v>
+        <v>-1.27739437772241</v>
       </c>
       <c r="O15" t="n">
-        <v>2.222808579692598</v>
+        <v>-0.6934653522925985</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6651716659434233</v>
+        <v>1.163360306461189</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.04662803482436768</v>
+        <v>-0.5515654135582746</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6226844739697702</v>
+        <v>0.1447101092648823</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5501836525233182</v>
+        <v>0.6044408753486523</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.007031481815372</v>
+        <v>1.04523389725813</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1351351340419396</v>
+        <v>-0.1635418526589192</v>
       </c>
       <c r="V15" t="n">
-        <v>0.4476989700399264</v>
+        <v>-2.872733143517479</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.2461765990658629</v>
+        <v>0.02754831611973357</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.4640646931484005</v>
+        <v>0.2614264353706175</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.374968344548557</v>
+        <v>-0.1608708779664591</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0.5243060231304379</v>
+        <v>0.8201005973718043</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0.3780478421616726</v>
+        <v>-0.02641538188580293</v>
       </c>
       <c r="AB15" t="n">
-        <v>-1.03267691584742</v>
+        <v>1.042698579424242</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.4112461527580867</v>
+        <v>0.4127634556659716</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.9805668692608354</v>
+        <v>-0.4041773787173583</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.4528664155183363</v>
+        <v>-1.86941945930554</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/usa/data_preparation/df_selected_nan.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_selected_nan.xlsx
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.523221128940959</v>
+        <v>1.483966760054599</v>
       </c>
       <c r="C2" t="n">
         <v>1.796276090876211</v>
@@ -635,43 +635,43 @@
         <v>-1.023932191010059</v>
       </c>
       <c r="R2" t="n">
-        <v>0.281696009093404</v>
+        <v>0.3043042547073486</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7204239916427559</v>
+        <v>0.7201285983991353</v>
       </c>
       <c r="T2" t="n">
-        <v>0.09791122172358556</v>
+        <v>0.1353355754465175</v>
       </c>
       <c r="U2" t="n">
-        <v>0.09689285331691563</v>
+        <v>0.1205253335108742</v>
       </c>
       <c r="V2" t="n">
         <v>0.4582206862103052</v>
       </c>
       <c r="W2" t="n">
-        <v>0.03839799201789595</v>
+        <v>0.07782592902246702</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.7662614198190578</v>
+        <v>-0.7513420192997596</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.2080540386247028</v>
+        <v>-0.1801843530584994</v>
       </c>
       <c r="Z2" t="n">
         <v>-1.110329421810902</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.09510279864063508</v>
+        <v>0.1460681215128956</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.7662659756734006</v>
+        <v>-0.7277109975625162</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.3200285056776944</v>
+        <v>0.330363511015098</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.3270426631156532</v>
+        <v>0.4046355283087306</v>
       </c>
       <c r="AE2" t="n">
         <v>0.02507691226130642</v>
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.483966760054599</v>
+        <v>1.680238604486398</v>
       </c>
       <c r="C3" t="n">
         <v>1.644741524599442</v>
@@ -720,7 +720,7 @@
         <v>-0.2167134479820736</v>
       </c>
       <c r="N3" t="n">
-        <v>0.03274012772016646</v>
+        <v>0.6878073804414545</v>
       </c>
       <c r="O3" t="n">
         <v>0.6496930715787196</v>
@@ -732,13 +732,13 @@
         <v>-2.037343185188492</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.06430072386083203</v>
+        <v>-0.07101393426308462</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.02091748143798162</v>
+        <v>-0.03843256317725809</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5878478560941583</v>
+        <v>0.6207316453914619</v>
       </c>
       <c r="U3" t="n">
         <v>-0.9472330897979383</v>
@@ -747,28 +747,28 @@
         <v>0.09272949292346588</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.4012684581700228</v>
+        <v>-0.3169492281018934</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.06888264342039287</v>
+        <v>-0.05610186118388617</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.7634947019057289</v>
+        <v>-0.7739109581351464</v>
       </c>
       <c r="Z3" t="n">
         <v>1.268236137539219</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.2412114471578012</v>
+        <v>0.2207868342578734</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.5724111856164764</v>
+        <v>0.5756186926329664</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.1962948998985086</v>
+        <v>-0.2301988829993881</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.2934445526161206</v>
+        <v>0.2866765879111786</v>
       </c>
       <c r="AE3" t="n">
         <v>0.05223815056334007</v>
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.483966760054599</v>
+        <v>1.503593944497779</v>
       </c>
       <c r="C4" t="n">
         <v>1.796276090876211</v>
@@ -829,43 +829,43 @@
         <v>-0.1692796133668106</v>
       </c>
       <c r="R4" t="n">
-        <v>-1.243215061723229</v>
+        <v>-1.276843273090074</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7727497586854777</v>
+        <v>-0.7892852643006886</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.184989409077211</v>
+        <v>-0.2589365137094655</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.001301339938657</v>
+        <v>-1.013654681858227</v>
       </c>
       <c r="V4" t="n">
         <v>0.001356694601756084</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.4650489895401747</v>
+        <v>-0.3788308234626806</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.07253734887906005</v>
+        <v>0.03051932885565126</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.7596661077261673</v>
+        <v>-0.9001176460259201</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.4887538476955162</v>
+        <v>0.4952875019084239</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.1581098499988858</v>
+        <v>-0.1752493810691365</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.6906627797449385</v>
+        <v>0.6451380835957142</v>
       </c>
       <c r="AD4" t="n">
-        <v>-1.23689230950666</v>
+        <v>-1.181277462237505</v>
       </c>
       <c r="AE4" t="n">
         <v>-0.3823416622691982</v>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.483966760054599</v>
+        <v>1.601729866713678</v>
       </c>
       <c r="C5" t="n">
         <v>1.796276090876211</v>
@@ -926,13 +926,13 @@
         <v>0.9442627150389926</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.3534216464626441</v>
+        <v>-0.5361523920414405</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9306852316008702</v>
+        <v>-0.9641411228516643</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.07257807155632953</v>
+        <v>-0.09619826439819477</v>
       </c>
       <c r="U5" t="n">
         <v>-0.04490202784682933</v>
@@ -941,28 +941,28 @@
         <v>-0.8708381984691103</v>
       </c>
       <c r="W5" t="n">
-        <v>0.413197264476452</v>
+        <v>0.4124992604179042</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.665550509155773</v>
+        <v>-1.627446576067294</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.1516326507153722</v>
+        <v>-0.2664222744245303</v>
       </c>
       <c r="Z5" t="n">
         <v>-0.8828144552643686</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.584471681667935</v>
+        <v>-0.5209119135938471</v>
       </c>
       <c r="AB5" t="n">
-        <v>-1.698481372717935</v>
+        <v>-1.69943162980959</v>
       </c>
       <c r="AC5" t="n">
         <v>-0.02677498439411105</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.3166017469337956</v>
+        <v>-0.4038724286410119</v>
       </c>
       <c r="AE5" t="n">
         <v>-1.794726053974947</v>
@@ -1023,43 +1023,43 @@
         <v>0.9232314124968243</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03304082697183836</v>
+        <v>0.03236950593161363</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.325791071014117</v>
+        <v>-1.32371115505758</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.390737824881058</v>
+        <v>-1.511631061630343</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9476621402993899</v>
+        <v>1.146174973928634</v>
       </c>
       <c r="V6" t="n">
         <v>1.579614120158562</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.4653114644759761</v>
+        <v>-0.7087387840739581</v>
       </c>
       <c r="X6" t="n">
-        <v>1.089023772061538</v>
+        <v>1.005695823233066</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.044376769912081</v>
+        <v>1.088645858887095</v>
       </c>
       <c r="Z6" t="n">
         <v>-1.110329421810902</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.763784989862936</v>
+        <v>-0.9190485603720054</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.2838319923481954</v>
+        <v>-0.411894001314411</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.6900230893871984</v>
+        <v>0.3643111261830542</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.02749643954033134</v>
+        <v>0.003634663979921561</v>
       </c>
       <c r="AE6" t="n">
         <v>-0.3755513526936898</v>
@@ -1068,201 +1068,201 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>nP8vQukM</t>
+          <t>QF7rPa4S</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1.483966760054599</v>
       </c>
       <c r="C7" t="n">
-        <v>1.813113264906963</v>
+        <v>1.644741524599442</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2790737550634819</v>
+        <v>-0.4222282553460458</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5655750168557507</v>
+        <v>0.06852474117266777</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5284557151666243</v>
+        <v>1.401930427988082</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03290609317835558</v>
+        <v>0.001909686486606733</v>
       </c>
       <c r="H7" t="n">
         <v>0.1061354269506152</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3302224233476369</v>
+        <v>0.3989627284640149</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9342097047524505</v>
+        <v>-0.3340883285743854</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5170211179172961</v>
+        <v>-0.5353799099041007</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1555855970590657</v>
+        <v>-1.239006587491152</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9649407239419381</v>
+        <v>0.08353061816742612</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6878073804414545</v>
+        <v>0.03274012772016646</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3256626346914755</v>
+        <v>0.6131089899946759</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.934276074666247</v>
+        <v>-0.2525442507998303</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.72410705971514</v>
+        <v>0.07611660257887688</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.6518398326770986</v>
+        <v>-1.437152251121662</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7288447658434934</v>
+        <v>-0.7445092957918567</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7140680230383498</v>
+        <v>0.1868518357974684</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6774289409169202</v>
+        <v>-0.04490202784682933</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2671684715376392</v>
+        <v>0.1004823364174291</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.4926321015082786</v>
+        <v>-1.318578573658425</v>
       </c>
       <c r="X7" t="n">
-        <v>1.114652093035179</v>
+        <v>-0.7152157101601512</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.6638811601032131</v>
+        <v>-0.4542620950949788</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.113112296712037</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.01917487485875038</v>
+        <v>-0.2979541545332711</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.6934485245974957</v>
+        <v>-0.7405806954368386</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.1899480927216371</v>
+        <v>-0.02677498439411105</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.6310737498137667</v>
+        <v>-0.8705419771731141</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.8874462283508745</v>
+        <v>0.8806559187753661</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>QF7rPa4S</t>
+          <t>nP8vQukM</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1.483966760054599</v>
       </c>
       <c r="C8" t="n">
-        <v>1.644741524599442</v>
+        <v>1.813113264906963</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4222282553460458</v>
+        <v>0.2790737550634819</v>
       </c>
       <c r="E8" t="n">
-        <v>0.06852474117266777</v>
+        <v>0.5655750168557507</v>
       </c>
       <c r="F8" t="n">
-        <v>1.401930427988082</v>
+        <v>0.5284557151666243</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001909686486606733</v>
+        <v>0.03290609317835558</v>
       </c>
       <c r="H8" t="n">
         <v>0.1061354269506152</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3989627284640149</v>
+        <v>-0.3302224233476369</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3340883285743854</v>
+        <v>-0.9342097047524505</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5353799099041007</v>
+        <v>-0.5170211179172961</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.239006587491152</v>
+        <v>-0.1555855970590657</v>
       </c>
       <c r="M8" t="n">
-        <v>0.08353061816742612</v>
+        <v>-0.9649407239419381</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03274012772016646</v>
+        <v>0.6878073804414545</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6131089899946759</v>
+        <v>0.3256626346914755</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2525442507998303</v>
+        <v>-0.934276074666247</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.07611660257887688</v>
+        <v>-1.72410705971514</v>
       </c>
       <c r="R8" t="n">
-        <v>-1.421807770202222</v>
+        <v>-0.5834112620953971</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7807123442083087</v>
+        <v>-0.7364641739215413</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2138615138387444</v>
+        <v>-0.587436004168353</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.04490202784682933</v>
+        <v>-0.6230623008747609</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1004823364174291</v>
+        <v>0.2671684715376392</v>
       </c>
       <c r="W8" t="n">
-        <v>-1.227508661668065</v>
+        <v>-0.7429279386996475</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.7511220589734975</v>
+        <v>1.179244854967686</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.3951126400779428</v>
+        <v>0.6856359452490264</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.113112296712037</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.2625478708192879</v>
+        <v>0.1146939466324631</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.7440570011671689</v>
+        <v>0.9185289886741114</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.02677498439411105</v>
+        <v>0.218629272941475</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.9043965720493623</v>
+        <v>-0.5876329208029185</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.8806559187753661</v>
+        <v>0.8874462283508745</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>b3GRSs53</t>
+          <t>AszX60rp</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1272,88 +1272,88 @@
         <v>1.661578698630194</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.526134286574629</v>
+        <v>-3.227436296984157</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.422626085876581</v>
+        <v>-1.919676361559664</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4634562468509636</v>
+        <v>2.171772547762925</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.05233402522395434</v>
+        <v>-1.330935801258599</v>
       </c>
       <c r="H9" t="n">
         <v>0.1061354269506152</v>
       </c>
       <c r="I9" t="n">
-        <v>1.294453265776571</v>
+        <v>-1.238505682621801</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4234681080051613</v>
+        <v>0.5597094657333715</v>
       </c>
       <c r="K9" t="n">
-        <v>0.492712441356962</v>
+        <v>-1.239133602731614</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.09116597060094145</v>
+        <v>0.7111511952866038</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9172829356642398</v>
+        <v>1.75155320788687</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03274012772016646</v>
+        <v>0.6878073804414545</v>
       </c>
       <c r="O9" t="n">
-        <v>1.893551845436204</v>
+        <v>-2.365880510420309</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1145421158974711</v>
+        <v>1.582887582686676</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.5683160085033706</v>
+        <v>-1.666565664116711</v>
       </c>
       <c r="R9" t="n">
-        <v>1.104830175429235</v>
+        <v>-0.4201008751802612</v>
       </c>
       <c r="S9" t="n">
-        <v>0.02470991465539037</v>
+        <v>-0.9191127668802798</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3851690204693275</v>
+        <v>-0.2583564586701814</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5222774968081527</v>
+        <v>0.4062635031287241</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2777456711809211</v>
+        <v>0.04012091207157237</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.7934981547409526</v>
+        <v>-0.03665682213128051</v>
       </c>
       <c r="X9" t="n">
-        <v>1.455731797909213</v>
+        <v>0.9884022312182792</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.344319481534102</v>
+        <v>0.5105436381545739</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.2312943237902055</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.377194271453114</v>
+        <v>-0.2025387440117078</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9047238298678376</v>
+        <v>0.3451260836617123</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.639323523966385</v>
+        <v>-0.02677498439411105</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.5640658028293519</v>
+        <v>-1.560977776537957</v>
       </c>
       <c r="AE9" t="n">
-        <v>-1.237920668783258</v>
+        <v>-0.4162932101467402</v>
       </c>
     </row>
     <row r="10">
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.503593944497779</v>
+        <v>1.660611420043218</v>
       </c>
       <c r="C10" t="n">
         <v>1.644741524599442</v>
@@ -1411,347 +1411,347 @@
         <v>0.1282295646302896</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.09307162558477694</v>
+        <v>-0.5342254520185762</v>
       </c>
       <c r="S10" t="n">
-        <v>1.022246382328506</v>
+        <v>0.371529818782691</v>
       </c>
       <c r="T10" t="n">
-        <v>0.874890965739216</v>
+        <v>1.313470851476471</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.217932408383269</v>
+        <v>-1.39839862077349</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.04848301357372199</v>
+        <v>0.08442287489421954</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1518907849896035</v>
+        <v>-2.060651813687859</v>
       </c>
       <c r="X10" t="n">
-        <v>0.07730321976556032</v>
+        <v>-0.3559298857002285</v>
       </c>
       <c r="Y10" t="n">
-        <v>-1.342619947803645</v>
+        <v>-1.012833835397349</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.268236137539219</v>
+        <v>0.7511566681152793</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.2033992782109885</v>
+        <v>0.7680955613235039</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.7833089246794277</v>
+        <v>0.9543105705026151</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.4136882592100152</v>
+        <v>0.6060993668223089</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.9260460020043371</v>
+        <v>-1.264315323638004</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.3891319718447066</v>
+        <v>0.05902846013884847</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>h6Py6Kcj</t>
+          <t>tS5WR1K9</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1.483966760054599</v>
       </c>
       <c r="C11" t="n">
-        <v>1.813113264906963</v>
+        <v>1.829950438937715</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.824832276165101</v>
+        <v>2.382979786292065</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9255758101934981</v>
+        <v>2.056725843905</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.411639950327657</v>
+        <v>-0.04892587466450898</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02903154234188727</v>
+        <v>-0.1608214486450753</v>
       </c>
       <c r="H11" t="n">
         <v>0.1061354269506152</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7204004431766794</v>
+        <v>1.384002319507826</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.02125910056667061</v>
+        <v>-0.24470854914361</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9209145416269993</v>
+        <v>0.9639214356849493</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1116631244739811</v>
+        <v>-0.6650862790460462</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.000684065150212</v>
+        <v>-0.4168761587484069</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6223271250011215</v>
+        <v>0.03274012772016646</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7960293979148942</v>
+        <v>1.344790621675549</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5734000742690978</v>
+        <v>-0.0690010674511794</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.7240345022522559</v>
+        <v>0.548948674334682</v>
       </c>
       <c r="R11" t="n">
-        <v>1.027491061225658</v>
+        <v>1.949662396815196</v>
       </c>
       <c r="S11" t="n">
-        <v>1.694575305663331</v>
+        <v>2.276294957929073</v>
       </c>
       <c r="T11" t="n">
-        <v>1.365715340819539</v>
+        <v>0.3729337500182974</v>
       </c>
       <c r="U11" t="n">
-        <v>1.489060777470052</v>
+        <v>-0.04490202784682933</v>
       </c>
       <c r="V11" t="n">
-        <v>5.334205469377911</v>
+        <v>-0.1398558118954318</v>
       </c>
       <c r="W11" t="n">
-        <v>1.310449259095027</v>
+        <v>0.249757563466352</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.9633715986131233</v>
+        <v>-1.033814883964865</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.2081780416750507</v>
+        <v>-0.3878584616324584</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.3271515031876489</v>
+        <v>-0.7311378109000137</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.2993854576144386</v>
+        <v>0.1543263473942428</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.02365939229770242</v>
+        <v>-0.5271592005582144</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.4858532400911893</v>
+        <v>0.9225365424305189</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.9537723089949509</v>
+        <v>0.3284123702583202</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.2329548516080132</v>
+        <v>-0.8644536421302952</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>tS5WR1K9</t>
+          <t>KCHNTNkc</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.483966760054599</v>
+        <v>1.503593944497779</v>
       </c>
       <c r="C12" t="n">
         <v>1.678415872660947</v>
       </c>
       <c r="D12" t="n">
-        <v>2.382979786292065</v>
+        <v>-1.824832276165101</v>
       </c>
       <c r="E12" t="n">
-        <v>2.056725843905</v>
+        <v>-0.9255758101934981</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.04892587466450898</v>
+        <v>-0.3080073572810432</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1608214486450753</v>
+        <v>-1.14805700177728</v>
       </c>
       <c r="H12" t="n">
         <v>0.1061354269506152</v>
       </c>
       <c r="I12" t="n">
-        <v>1.384002319507826</v>
+        <v>-0.01296291869976031</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.24470854914361</v>
+        <v>-0.9776227404759704</v>
       </c>
       <c r="K12" t="n">
-        <v>0.9639214356849493</v>
+        <v>0.1414475546760992</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6650862790460462</v>
+        <v>-0.9438475717193834</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.4168761587484069</v>
+        <v>-0.7838411284866843</v>
       </c>
       <c r="N12" t="n">
-        <v>0.03274012772016646</v>
+        <v>-0.6223271250011215</v>
       </c>
       <c r="O12" t="n">
-        <v>1.344790621675549</v>
+        <v>-0.3746612127745034</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.0690010674511794</v>
+        <v>-0.6196306174971314</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.548948674334682</v>
+        <v>-0.7730455022767985</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3434468889046089</v>
+        <v>-0.04751769785519794</v>
       </c>
       <c r="S12" t="n">
-        <v>1.025947485910327</v>
+        <v>0.7229261461769398</v>
       </c>
       <c r="T12" t="n">
-        <v>1.352499390658764</v>
+        <v>0.7255462990154675</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6894242149547646</v>
+        <v>-0.04490202784682933</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.2284597375407262</v>
+        <v>1.78174182553689</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3940375906999675</v>
+        <v>0.9398798449539625</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.31754861104743</v>
+        <v>-0.4847966626481747</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.9981394739308546</v>
+        <v>-0.9425241058487988</v>
       </c>
       <c r="Z12" t="n">
-        <v>-1.162037368753296</v>
+        <v>-1.420577103465266</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.1689288215325391</v>
+        <v>-2.152541011349165</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.4150886370985252</v>
+        <v>-1.08295159404348</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.233406976942668</v>
+        <v>-0.02677498439411105</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0.2400724936542807</v>
+        <v>-0.01776902439945716</v>
       </c>
       <c r="AE12" t="n">
-        <v>-1.339775312415884</v>
+        <v>0.8263334421712988</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>AszX60rp</t>
+          <t>WdOu5vDd</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.483966760054599</v>
+        <v>1.503593944497779</v>
       </c>
       <c r="C13" t="n">
-        <v>1.644741524599442</v>
+        <v>1.661578698630194</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.227436296984157</v>
+        <v>0.2790737550634819</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.919676361559664</v>
+        <v>0.5655750168557507</v>
       </c>
       <c r="F13" t="n">
-        <v>2.171772547762925</v>
+        <v>-1.832886940681215</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.330935801258599</v>
+        <v>-1.478168733044406</v>
       </c>
       <c r="H13" t="n">
         <v>0.1061354269506152</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.238505682621801</v>
+        <v>-0.8803094676967784</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5597094657333715</v>
+        <v>0.674626325001512</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.239133602731614</v>
+        <v>-1.190176824100134</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7111511952866038</v>
+        <v>0.5354613049462648</v>
       </c>
       <c r="M13" t="n">
-        <v>1.75155320788687</v>
+        <v>0.2026750888616723</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6878073804414545</v>
+        <v>-0.6223271250011215</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.365880510420309</v>
+        <v>-0.6934653522925985</v>
       </c>
       <c r="P13" t="n">
-        <v>1.582887582686676</v>
+        <v>1.163360306461189</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.666565664116711</v>
+        <v>-0.5515654135582746</v>
       </c>
       <c r="R13" t="n">
-        <v>-1.174977409162228</v>
+        <v>0.8785323815223183</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8074541207923825</v>
+        <v>0.5587222548712183</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1217639536329982</v>
+        <v>1.294276216752835</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5754505772445572</v>
+        <v>-0.04490202784682933</v>
       </c>
       <c r="V13" t="n">
-        <v>0.4609895588867206</v>
+        <v>-0.8680693257926948</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.5832010099538496</v>
+        <v>-2.147940007393813</v>
       </c>
       <c r="X13" t="n">
-        <v>0.510549638574552</v>
+        <v>1.143957393924675</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.01712809203866304</v>
+        <v>0.5222619264126657</v>
       </c>
       <c r="Z13" t="n">
-        <v>-2.764983723967508</v>
+        <v>0.189756101312145</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.5251533278461826</v>
+        <v>0.3089711703330622</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.08839427173778927</v>
+        <v>2.143732023690407</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.02677498439411105</v>
+        <v>0.7869206100269995</v>
       </c>
       <c r="AD13" t="n">
-        <v>-1.218586240687426</v>
+        <v>0.05244547609732189</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.5003985825468952</v>
+        <v>-0.4502447580242822</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>KCHNTNkc</t>
+          <t>h6Py6Kcj</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.483966760054599</v>
+        <v>1.503593944497779</v>
       </c>
       <c r="C14" t="n">
         <v>1.813113264906963</v>
@@ -1763,179 +1763,179 @@
         <v>-0.9255758101934981</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3080073572810432</v>
+        <v>-0.411639950327657</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.14805700177728</v>
+        <v>0.02903154234188727</v>
       </c>
       <c r="H14" t="n">
         <v>0.1061354269506152</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.01296291869976031</v>
+        <v>-0.7204004431766794</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.9776227404759704</v>
+        <v>-0.02125910056667061</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1414475546760992</v>
+        <v>-0.9209145416269993</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.9438475717193834</v>
+        <v>-0.1116631244739811</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7838411284866843</v>
+        <v>-1.000684065150212</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6223271250011215</v>
+        <v>-1.27739437772241</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3746612127745034</v>
+        <v>0.7960293979148942</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.6196306174971314</v>
+        <v>0.5734000742690978</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.7730455022767985</v>
+        <v>-0.7240345022522559</v>
       </c>
       <c r="R14" t="n">
-        <v>-1.078235252115466</v>
+        <v>1.916096344803933</v>
       </c>
       <c r="S14" t="n">
-        <v>0.08221820076785558</v>
+        <v>2.046409510101061</v>
       </c>
       <c r="T14" t="n">
-        <v>1.601891087578369</v>
+        <v>1.828882339425962</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.04490202784682933</v>
+        <v>3.113256688982048</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.0158103159920197</v>
+        <v>5.467111357845852</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.3510152812622611</v>
+        <v>1.458153495083015</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5957945176155214</v>
+        <v>-0.9911134667513445</v>
       </c>
       <c r="Y14" t="n">
-        <v>-1.077005413953567</v>
+        <v>0.1589949904118232</v>
       </c>
       <c r="Z14" t="n">
-        <v>-1.379210745911351</v>
+        <v>0.5236417015687457</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.2270472283736784</v>
+        <v>0.1893266406538567</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.4974640630510251</v>
+        <v>0.471208617369014</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.258018473653278</v>
+        <v>-0.02677498439411105</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.9797761218007922</v>
+        <v>2.216674522937108</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.5385187825058916</v>
+        <v>0.2491571282530839</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>WdOu5vDd</t>
+          <t>b3GRSs53</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.660611420043218</v>
+        <v>1.523221128940959</v>
       </c>
       <c r="C15" t="n">
-        <v>1.644741524599442</v>
+        <v>1.661578698630194</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2790737550634819</v>
+        <v>-2.526134286574629</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5655750168557507</v>
+        <v>-1.422626085876581</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.832886940681215</v>
+        <v>-0.4634562468509636</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.478168733044406</v>
+        <v>-0.05233402522395434</v>
       </c>
       <c r="H15" t="n">
         <v>0.1061354269506152</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.8803094676967784</v>
+        <v>1.294453265776571</v>
       </c>
       <c r="J15" t="n">
-        <v>0.674626325001512</v>
+        <v>-0.4234681080051613</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.190176824100134</v>
+        <v>0.492712441356962</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5354613049462648</v>
+        <v>-0.09116597060094145</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2026750888616723</v>
+        <v>-0.9172829356642398</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.27739437772241</v>
+        <v>0.03274012772016646</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6934653522925985</v>
+        <v>1.893551845436204</v>
       </c>
       <c r="P15" t="n">
-        <v>1.163360306461189</v>
+        <v>0.1145421158974711</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.5515654135582746</v>
+        <v>-0.5683160085033706</v>
       </c>
       <c r="R15" t="n">
-        <v>0.1447101092648823</v>
+        <v>1.272374058454519</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6044408753486523</v>
+        <v>-0.6976199623856705</v>
       </c>
       <c r="T15" t="n">
-        <v>1.04523389725813</v>
+        <v>-0.8811157185926014</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1635418526589192</v>
+        <v>0.9476621402993888</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.872733143517479</v>
+        <v>-0.0811557111554243</v>
       </c>
       <c r="W15" t="n">
-        <v>0.02754831611973357</v>
+        <v>-0.03665682213128051</v>
       </c>
       <c r="X15" t="n">
-        <v>0.2614264353706175</v>
+        <v>1.308662860319682</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.1608708779664591</v>
+        <v>1.83037010455668</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.8201005973718043</v>
+        <v>-0.07617048296302362</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0.02641538188580293</v>
+        <v>0.82557845384158</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.042698579424242</v>
+        <v>0.3084592243692785</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.4127634556659716</v>
+        <v>0.685208660724361</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.4041773787173583</v>
+        <v>0.3205947443607139</v>
       </c>
       <c r="AE15" t="n">
-        <v>-1.86941945930554</v>
+        <v>-0.395922281420215</v>
       </c>
     </row>
   </sheetData>
